--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10014" uniqueCount="2592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10059" uniqueCount="2594">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 07:22 BST</t>
+    <t>Snapshot: 07 September 2026, 07:29 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4278,6 +4278,12 @@
   </si>
   <si>
     <t>Record-board title and proof context</t>
+  </si>
+  <si>
+    <t>Full responsive searchable/sortable record browser with exact category/period/proof/details and submissions count; real mobile hub route. course-records-browser.log PASS15s both surfaces x6sizes, real isolated course, no-verified-leader/filter reset/details/exactboardhref/nooverflow.390 screenshot inspected; types/lint pass. Backend11targeted tests and period-bound regression pass; verified leader excludes inactive/unverified results.</t>
+  </si>
+  <si>
+    <t>Positive verified-leader browser fixture, actual downstream board/submission navigation (P56/P57 still outstanding), server error recovery, 80course source limit beyond loaded scope, physical keyboard/AT/zoom/theme and shared sticky-nav overlap remain open. No full acceptance.</t>
   </si>
   <si>
     <t>Users can tell which course, category and period a record covers.</t>
@@ -7969,8 +7975,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L306" totalsRowShown="0">
-  <autoFilter ref="A1:L306"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L309" totalsRowShown="0">
+  <autoFilter ref="A1:L309"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8364,11 +8370,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8403,11 +8409,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -20151,16 +20157,25 @@
         <v>42</v>
       </c>
       <c r="E307" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F307" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G307" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I307" s="4" t="s">
+        <v>1420</v>
       </c>
       <c r="J307" s="4" t="s">
-        <v>1419</v>
+        <v>1421</v>
       </c>
       <c r="K307" s="4" t="s">
-        <v>1420</v>
+        <v>1422</v>
       </c>
       <c r="L307" s="6" t="s">
         <v>39</v>
@@ -20168,28 +20183,37 @@
     </row>
     <row r="308" spans="1:12" ht="72" customHeight="1">
       <c r="A308" s="4" t="s">
-        <v>1421</v>
+        <v>1423</v>
       </c>
       <c r="B308" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C308" s="4" t="s">
-        <v>1422</v>
+        <v>1424</v>
       </c>
       <c r="D308" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E308" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F308" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>1420</v>
       </c>
       <c r="J308" s="4" t="s">
-        <v>1423</v>
+        <v>1425</v>
       </c>
       <c r="K308" s="4" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="L308" s="6" t="s">
         <v>88</v>
@@ -20197,28 +20221,37 @@
     </row>
     <row r="309" spans="1:12" ht="72" customHeight="1">
       <c r="A309" s="4" t="s">
-        <v>1425</v>
+        <v>1427</v>
       </c>
       <c r="B309" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C309" s="4" t="s">
-        <v>1426</v>
+        <v>1428</v>
       </c>
       <c r="D309" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E309" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F309" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G309" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I309" s="4" t="s">
+        <v>1420</v>
       </c>
       <c r="J309" s="4" t="s">
-        <v>1427</v>
+        <v>1429</v>
       </c>
       <c r="K309" s="4" t="s">
-        <v>1428</v>
+        <v>1430</v>
       </c>
       <c r="L309" s="6" t="s">
         <v>165</v>
@@ -20226,13 +20259,13 @@
     </row>
     <row r="310" spans="1:12" ht="72" customHeight="1">
       <c r="A310" s="4" t="s">
-        <v>1429</v>
+        <v>1431</v>
       </c>
       <c r="B310" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C310" s="4" t="s">
-        <v>1431</v>
+        <v>1433</v>
       </c>
       <c r="D310" s="4" t="s">
         <v>42</v>
@@ -20244,10 +20277,10 @@
         <v>9</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1432</v>
+        <v>1434</v>
       </c>
       <c r="K310" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="L310" s="6" t="s">
         <v>88</v>
@@ -20255,13 +20288,13 @@
     </row>
     <row r="311" spans="1:12" ht="72" customHeight="1">
       <c r="A311" s="4" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="B311" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C311" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="D311" s="4" t="s">
         <v>42</v>
@@ -20273,10 +20306,10 @@
         <v>9</v>
       </c>
       <c r="J311" s="4" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="K311" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="L311" s="6" t="s">
         <v>141</v>
@@ -20284,13 +20317,13 @@
     </row>
     <row r="312" spans="1:12" ht="72" customHeight="1">
       <c r="A312" s="4" t="s">
-        <v>1437</v>
+        <v>1439</v>
       </c>
       <c r="B312" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>1438</v>
+        <v>1440</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>42</v>
@@ -20302,10 +20335,10 @@
         <v>9</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="K312" s="4" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="L312" s="6" t="s">
         <v>165</v>
@@ -20313,13 +20346,13 @@
     </row>
     <row r="313" spans="1:12" ht="72" customHeight="1">
       <c r="A313" s="4" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>42</v>
@@ -20331,10 +20364,10 @@
         <v>9</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="K313" s="4" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="L313" s="6" t="s">
         <v>39</v>
@@ -20342,13 +20375,13 @@
     </row>
     <row r="314" spans="1:12" ht="72" customHeight="1">
       <c r="A314" s="4" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>42</v>
@@ -20360,10 +20393,10 @@
         <v>9</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K314" s="4" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="L314" s="6" t="s">
         <v>518</v>
@@ -20371,13 +20404,13 @@
     </row>
     <row r="315" spans="1:12" ht="72" customHeight="1">
       <c r="A315" s="4" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>42</v>
@@ -20389,10 +20422,10 @@
         <v>9</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="K315" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="L315" s="6" t="s">
         <v>1045</v>
@@ -20400,13 +20433,13 @@
     </row>
     <row r="316" spans="1:12" ht="72" customHeight="1">
       <c r="A316" s="4" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>42</v>
@@ -20418,10 +20451,10 @@
         <v>9</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K316" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="L316" s="6" t="s">
         <v>88</v>
@@ -20429,13 +20462,13 @@
     </row>
     <row r="317" spans="1:12" ht="72" customHeight="1">
       <c r="A317" s="4" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>42</v>
@@ -20447,10 +20480,10 @@
         <v>9</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="K317" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="L317" s="6" t="s">
         <v>116</v>
@@ -20458,13 +20491,13 @@
     </row>
     <row r="318" spans="1:12" ht="72" customHeight="1">
       <c r="A318" s="4" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>42</v>
@@ -20476,10 +20509,10 @@
         <v>9</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="K318" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>141</v>
@@ -20487,13 +20520,13 @@
     </row>
     <row r="319" spans="1:12" ht="72" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>42</v>
@@ -20505,10 +20538,10 @@
         <v>9</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L319" s="6" t="s">
         <v>165</v>
@@ -20516,13 +20549,13 @@
     </row>
     <row r="320" spans="1:12" ht="72" customHeight="1">
       <c r="A320" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>42</v>
@@ -20534,10 +20567,10 @@
         <v>9</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="K320" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>165</v>
@@ -20545,13 +20578,13 @@
     </row>
     <row r="321" spans="1:12" ht="72" customHeight="1">
       <c r="A321" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>42</v>
@@ -20563,10 +20596,10 @@
         <v>9</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L321" s="6" t="s">
         <v>165</v>
@@ -20574,13 +20607,13 @@
     </row>
     <row r="322" spans="1:12" ht="72" customHeight="1">
       <c r="A322" s="4" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>42</v>
@@ -20592,10 +20625,10 @@
         <v>9</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="K322" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>518</v>
@@ -20603,13 +20636,13 @@
     </row>
     <row r="323" spans="1:12" ht="72" customHeight="1">
       <c r="A323" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>42</v>
@@ -20621,10 +20654,10 @@
         <v>9</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="K323" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="L323" s="6" t="s">
         <v>81</v>
@@ -20632,13 +20665,13 @@
     </row>
     <row r="324" spans="1:12" ht="72" customHeight="1">
       <c r="A324" s="4" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>42</v>
@@ -20650,10 +20683,10 @@
         <v>9</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>39</v>
@@ -20661,13 +20694,13 @@
     </row>
     <row r="325" spans="1:12" ht="72" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>42</v>
@@ -20679,10 +20712,10 @@
         <v>9</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="K325" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>88</v>
@@ -20690,13 +20723,13 @@
     </row>
     <row r="326" spans="1:12" ht="72" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>42</v>
@@ -20708,10 +20741,10 @@
         <v>9</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K326" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L326" s="6" t="s">
         <v>159</v>
@@ -20719,13 +20752,13 @@
     </row>
     <row r="327" spans="1:12" ht="72" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>42</v>
@@ -20737,10 +20770,10 @@
         <v>9</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="K327" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>103</v>
@@ -20748,13 +20781,13 @@
     </row>
     <row r="328" spans="1:12" ht="72" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>42</v>
@@ -20766,10 +20799,10 @@
         <v>9</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K328" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>518</v>
@@ -20777,13 +20810,13 @@
     </row>
     <row r="329" spans="1:12" ht="72" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>42</v>
@@ -20795,10 +20828,10 @@
         <v>9</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="L329" s="6" t="s">
         <v>88</v>
@@ -20806,13 +20839,13 @@
     </row>
     <row r="330" spans="1:12" ht="72" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>42</v>
@@ -20824,10 +20857,10 @@
         <v>9</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>625</v>
@@ -20835,13 +20868,13 @@
     </row>
     <row r="331" spans="1:12" ht="72" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>42</v>
@@ -20853,10 +20886,10 @@
         <v>9</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -20864,13 +20897,13 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>42</v>
@@ -20882,10 +20915,10 @@
         <v>9</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -20893,13 +20926,13 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
@@ -20911,10 +20944,10 @@
         <v>9</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -20922,13 +20955,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -20940,10 +20973,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -20951,13 +20984,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -20969,10 +21002,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -20980,13 +21013,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -20998,10 +21031,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21009,13 +21042,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21027,10 +21060,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21038,13 +21071,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21056,10 +21089,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21067,13 +21100,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21085,10 +21118,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21096,13 +21129,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21114,10 +21147,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21125,13 +21158,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21143,10 +21176,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21154,13 +21187,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21172,10 +21205,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21183,13 +21216,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21201,10 +21234,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21212,13 +21245,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21230,10 +21263,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21241,13 +21274,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21259,10 +21292,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21270,13 +21303,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21288,10 +21321,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21299,13 +21332,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21317,10 +21350,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21328,13 +21361,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21346,10 +21379,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21357,13 +21390,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21375,10 +21408,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21386,13 +21419,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21404,10 +21437,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21415,13 +21448,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21433,24 +21466,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21462,10 +21495,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21473,13 +21506,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21491,10 +21524,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21502,13 +21535,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21520,10 +21553,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21531,13 +21564,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21549,10 +21582,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21560,13 +21593,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21578,10 +21611,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21589,13 +21622,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21607,10 +21640,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21618,13 +21651,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21636,10 +21669,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21647,13 +21680,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21665,10 +21698,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21676,13 +21709,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21694,10 +21727,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21705,13 +21738,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21723,10 +21756,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21734,13 +21767,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21752,10 +21785,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -21763,13 +21796,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -21781,10 +21814,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -21792,13 +21825,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -21810,10 +21843,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -21821,13 +21854,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -21839,10 +21872,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -21850,13 +21883,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -21868,10 +21901,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -21879,13 +21912,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -21897,10 +21930,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -21908,13 +21941,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -21926,10 +21959,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -21937,13 +21970,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -21955,10 +21988,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -21966,13 +21999,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -21984,10 +22017,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -21995,13 +22028,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22013,10 +22046,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22024,13 +22057,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22042,10 +22075,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22053,13 +22086,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22071,10 +22104,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22082,13 +22115,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22100,10 +22133,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22111,13 +22144,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22129,10 +22162,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22140,13 +22173,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22158,10 +22191,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22169,13 +22202,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22187,10 +22220,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22198,13 +22231,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22216,10 +22249,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22227,13 +22260,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22245,10 +22278,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22256,13 +22289,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22274,10 +22307,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22285,13 +22318,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22303,10 +22336,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22314,13 +22347,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22332,24 +22365,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22361,10 +22394,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22372,13 +22405,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22390,10 +22423,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22401,13 +22434,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22419,10 +22452,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22430,13 +22463,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22448,10 +22481,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22459,13 +22492,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22477,10 +22510,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22488,13 +22521,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22506,10 +22539,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22517,13 +22550,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22535,10 +22568,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22546,13 +22579,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22564,24 +22597,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22593,10 +22626,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22604,13 +22637,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22622,24 +22655,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22651,10 +22684,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22662,13 +22695,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22680,10 +22713,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22691,13 +22724,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22709,24 +22742,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22738,10 +22771,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22749,13 +22782,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -22767,10 +22800,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -22778,13 +22811,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -22796,10 +22829,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -22807,13 +22840,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -22825,10 +22858,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -22836,13 +22869,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -22854,10 +22887,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -22865,13 +22898,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -22883,10 +22916,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -22894,13 +22927,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -22912,10 +22945,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -22923,13 +22956,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -22941,24 +22974,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -22970,10 +23003,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -22981,13 +23014,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -22999,10 +23032,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23010,13 +23043,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23028,10 +23061,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23039,13 +23072,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23057,10 +23090,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23068,13 +23101,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23086,10 +23119,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23097,13 +23130,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23115,10 +23148,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23126,13 +23159,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23144,10 +23177,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23155,13 +23188,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23173,24 +23206,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23202,10 +23235,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23213,13 +23246,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23231,10 +23264,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23242,13 +23275,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23260,10 +23293,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23271,13 +23304,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23289,10 +23322,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23300,13 +23333,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23318,10 +23351,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23329,13 +23362,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23347,10 +23380,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23358,13 +23391,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23376,10 +23409,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23387,13 +23420,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23405,10 +23438,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23416,13 +23449,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23434,10 +23467,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23445,13 +23478,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23463,10 +23496,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23474,13 +23507,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23492,10 +23525,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23503,13 +23536,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23521,10 +23554,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23532,13 +23565,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23550,10 +23583,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23561,13 +23594,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23579,10 +23612,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23590,13 +23623,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23608,10 +23641,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23619,13 +23652,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23637,10 +23670,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23648,13 +23681,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23666,10 +23699,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23677,13 +23710,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23695,10 +23728,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23706,13 +23739,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23724,10 +23757,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23735,13 +23768,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23753,10 +23786,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -23764,13 +23797,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -23782,10 +23815,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -23793,13 +23826,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -23811,10 +23844,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -23822,13 +23855,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -23840,10 +23873,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -23851,13 +23884,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -23869,10 +23902,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -23880,13 +23913,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -23898,10 +23931,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -23909,13 +23942,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -23927,10 +23960,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -23938,13 +23971,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -23956,10 +23989,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -23967,13 +24000,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -23985,10 +24018,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -23996,13 +24029,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24014,10 +24047,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24025,13 +24058,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24043,10 +24076,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24054,13 +24087,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24072,10 +24105,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24083,13 +24116,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24101,10 +24134,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24112,13 +24145,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24130,10 +24163,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24141,13 +24174,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24159,10 +24192,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24170,13 +24203,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24188,10 +24221,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24199,13 +24232,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24217,10 +24250,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24228,13 +24261,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24246,10 +24279,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24257,13 +24290,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24275,10 +24308,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24286,13 +24319,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24304,10 +24337,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24315,13 +24348,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24333,10 +24366,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24344,13 +24377,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24362,10 +24395,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24373,13 +24406,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24391,10 +24424,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24402,13 +24435,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24420,10 +24453,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24431,13 +24464,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24449,10 +24482,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24460,13 +24493,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24478,24 +24511,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24507,10 +24540,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24518,13 +24551,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24536,10 +24569,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24547,13 +24580,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24565,10 +24598,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24576,13 +24609,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24594,10 +24627,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24605,13 +24638,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24623,10 +24656,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24634,13 +24667,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24652,10 +24685,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24663,13 +24696,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24681,10 +24714,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24692,13 +24725,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24710,10 +24743,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24721,13 +24754,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24739,10 +24772,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24750,13 +24783,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -24768,10 +24801,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -24779,13 +24812,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -24797,10 +24830,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -24808,13 +24841,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -24826,10 +24859,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -24837,13 +24870,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -24855,10 +24888,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -24866,13 +24899,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -24884,10 +24917,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -24895,13 +24928,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -24913,10 +24946,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -24924,13 +24957,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -24942,10 +24975,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -24953,13 +24986,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -24971,10 +25004,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -24982,13 +25015,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25000,10 +25033,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25011,13 +25044,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25029,10 +25062,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25040,13 +25073,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25058,10 +25091,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25069,13 +25102,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25087,10 +25120,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25098,13 +25131,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25116,10 +25149,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25127,13 +25160,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25145,10 +25178,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25156,13 +25189,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25174,10 +25207,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25185,13 +25218,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25203,10 +25236,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25214,13 +25247,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25232,10 +25265,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25243,13 +25276,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25261,10 +25294,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25272,13 +25305,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25290,10 +25323,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25301,13 +25334,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25319,10 +25352,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25330,13 +25363,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25348,10 +25381,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25359,13 +25392,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25377,10 +25410,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25388,13 +25421,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25406,10 +25439,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25417,13 +25450,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25435,10 +25468,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25446,13 +25479,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25464,10 +25497,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25475,13 +25508,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25493,10 +25526,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25504,13 +25537,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25522,10 +25555,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25533,13 +25566,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25551,10 +25584,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26085,7 +26118,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L306"/>
+  <dimension ref="A1:L309"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -37716,8 +37749,122 @@
         <v>116</v>
       </c>
     </row>
+    <row r="307" spans="1:12" ht="72" customHeight="1">
+      <c r="A307" s="4" t="s">
+        <v>1416</v>
+      </c>
+      <c r="B307" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C307" s="4" t="s">
+        <v>1418</v>
+      </c>
+      <c r="D307" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E307" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F307" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G307" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H307" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I307" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J307" s="4" t="s">
+        <v>1421</v>
+      </c>
+      <c r="K307" s="4" t="s">
+        <v>1422</v>
+      </c>
+      <c r="L307" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="308" spans="1:12" ht="72" customHeight="1">
+      <c r="A308" s="4" t="s">
+        <v>1423</v>
+      </c>
+      <c r="B308" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C308" s="4" t="s">
+        <v>1424</v>
+      </c>
+      <c r="D308" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E308" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F308" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G308" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H308" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I308" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J308" s="4" t="s">
+        <v>1425</v>
+      </c>
+      <c r="K308" s="4" t="s">
+        <v>1426</v>
+      </c>
+      <c r="L308" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="309" spans="1:12" ht="72" customHeight="1">
+      <c r="A309" s="4" t="s">
+        <v>1427</v>
+      </c>
+      <c r="B309" s="4" t="s">
+        <v>1417</v>
+      </c>
+      <c r="C309" s="4" t="s">
+        <v>1428</v>
+      </c>
+      <c r="D309" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E309" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F309" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G309" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="H309" s="4" t="s">
+        <v>1419</v>
+      </c>
+      <c r="I309" s="4" t="s">
+        <v>1420</v>
+      </c>
+      <c r="J309" s="4" t="s">
+        <v>1429</v>
+      </c>
+      <c r="K309" s="4" t="s">
+        <v>1430</v>
+      </c>
+      <c r="L309" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F306">
+  <conditionalFormatting sqref="E2:F309">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -38040,11 +38187,14 @@
     <hyperlink ref="L304" r:id="rId303"/>
     <hyperlink ref="L305" r:id="rId304"/>
     <hyperlink ref="L306" r:id="rId305"/>
+    <hyperlink ref="L307" r:id="rId306"/>
+    <hyperlink ref="L308" r:id="rId307"/>
+    <hyperlink ref="L309" r:id="rId308"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId306"/>
+    <tablePart r:id="rId309"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38061,3128 +38211,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>1424</v>
+        <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>1430</v>
+        <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1433</v>
+        <v>1435</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2493</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2494</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2196</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2495</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2491</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2492</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2194</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2493</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2162</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2489</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2541</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2016</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2221</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2538</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2539</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2014</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2540</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2541</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2219</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2542</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2536</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2543</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2537</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2584</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2137</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2138</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2136</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2164</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2582</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2135</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2583</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2136</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2134</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2162</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2580</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2581</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2141</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2139</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2137</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2142</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2140</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2145</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2143</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2581</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2148</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2579</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2146</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10059" uniqueCount="2594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10104" uniqueCount="2596">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 07:29 BST</t>
+    <t>Snapshot: 07 September 2026, 07:35 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4323,6 +4323,12 @@
   </si>
   <si>
     <t>Course-specific record table</t>
+  </si>
+  <si>
+    <t>Full responsive course category table/details, controlled URL scope tabs, exact eligible submission links. course-record-scopes-browser.log PASS33.3s both surfaces x6sizes, reload/BackForward, category search/reset/sort, every selected targetcheckedagainstfixturecourse ID. Types/scoped lint pass;390 capture inspected. Backend12targeted tests verify active verified leader only and retain pending attempts separately.</t>
+  </si>
+  <si>
+    <t>Positive verified leader/previous-round suggestion UI, actual submission destination P57, server error/permission UI, physical keyboard/AT/zoom/theme and shared fixed-navigation overlap remain unverified. No full acceptance.</t>
   </si>
   <si>
     <t>Records are restricted to the selected course.</t>
@@ -7975,8 +7981,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L309" totalsRowShown="0">
-  <autoFilter ref="A1:L309"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L312" totalsRowShown="0">
+  <autoFilter ref="A1:L312"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8370,11 +8376,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8409,11 +8415,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -20271,16 +20277,25 @@
         <v>42</v>
       </c>
       <c r="E310" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F310" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G310" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I310" s="4" t="s">
+        <v>1435</v>
       </c>
       <c r="J310" s="4" t="s">
-        <v>1434</v>
+        <v>1436</v>
       </c>
       <c r="K310" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="L310" s="6" t="s">
         <v>88</v>
@@ -20288,28 +20303,37 @@
     </row>
     <row r="311" spans="1:12" ht="72" customHeight="1">
       <c r="A311" s="4" t="s">
-        <v>1436</v>
+        <v>1438</v>
       </c>
       <c r="B311" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C311" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I311" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J311" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="K311" s="4" t="s">
         <v>1437</v>
-      </c>
-      <c r="D311" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E311" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F311" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J311" s="4" t="s">
-        <v>1438</v>
-      </c>
-      <c r="K311" s="4" t="s">
-        <v>1435</v>
       </c>
       <c r="L311" s="6" t="s">
         <v>141</v>
@@ -20317,28 +20341,37 @@
     </row>
     <row r="312" spans="1:12" ht="72" customHeight="1">
       <c r="A312" s="4" t="s">
-        <v>1439</v>
+        <v>1441</v>
       </c>
       <c r="B312" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C312" s="4" t="s">
-        <v>1440</v>
+        <v>1442</v>
       </c>
       <c r="D312" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E312" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F312" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H312" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>1435</v>
       </c>
       <c r="J312" s="4" t="s">
-        <v>1441</v>
+        <v>1443</v>
       </c>
       <c r="K312" s="4" t="s">
-        <v>1442</v>
+        <v>1444</v>
       </c>
       <c r="L312" s="6" t="s">
         <v>165</v>
@@ -20346,13 +20379,13 @@
     </row>
     <row r="313" spans="1:12" ht="72" customHeight="1">
       <c r="A313" s="4" t="s">
-        <v>1443</v>
+        <v>1445</v>
       </c>
       <c r="B313" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C313" s="4" t="s">
-        <v>1445</v>
+        <v>1447</v>
       </c>
       <c r="D313" s="4" t="s">
         <v>42</v>
@@ -20364,10 +20397,10 @@
         <v>9</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1446</v>
+        <v>1448</v>
       </c>
       <c r="K313" s="4" t="s">
-        <v>1447</v>
+        <v>1449</v>
       </c>
       <c r="L313" s="6" t="s">
         <v>39</v>
@@ -20375,13 +20408,13 @@
     </row>
     <row r="314" spans="1:12" ht="72" customHeight="1">
       <c r="A314" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="B314" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>42</v>
@@ -20393,10 +20426,10 @@
         <v>9</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="K314" s="4" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="L314" s="6" t="s">
         <v>518</v>
@@ -20404,13 +20437,13 @@
     </row>
     <row r="315" spans="1:12" ht="72" customHeight="1">
       <c r="A315" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="B315" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>42</v>
@@ -20422,10 +20455,10 @@
         <v>9</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="K315" s="4" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="L315" s="6" t="s">
         <v>1045</v>
@@ -20433,13 +20466,13 @@
     </row>
     <row r="316" spans="1:12" ht="72" customHeight="1">
       <c r="A316" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="B316" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>42</v>
@@ -20451,10 +20484,10 @@
         <v>9</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="K316" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="L316" s="6" t="s">
         <v>88</v>
@@ -20462,13 +20495,13 @@
     </row>
     <row r="317" spans="1:12" ht="72" customHeight="1">
       <c r="A317" s="4" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="B317" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C317" s="4" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="D317" s="4" t="s">
         <v>42</v>
@@ -20480,10 +20513,10 @@
         <v>9</v>
       </c>
       <c r="J317" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="K317" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="L317" s="6" t="s">
         <v>116</v>
@@ -20491,13 +20524,13 @@
     </row>
     <row r="318" spans="1:12" ht="72" customHeight="1">
       <c r="A318" s="4" t="s">
-        <v>1463</v>
+        <v>1465</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>42</v>
@@ -20509,10 +20542,10 @@
         <v>9</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="K318" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>141</v>
@@ -20520,13 +20553,13 @@
     </row>
     <row r="319" spans="1:12" ht="72" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>42</v>
@@ -20538,10 +20571,10 @@
         <v>9</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L319" s="6" t="s">
         <v>165</v>
@@ -20549,13 +20582,13 @@
     </row>
     <row r="320" spans="1:12" ht="72" customHeight="1">
       <c r="A320" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>42</v>
@@ -20567,10 +20600,10 @@
         <v>9</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="K320" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>165</v>
@@ -20578,13 +20611,13 @@
     </row>
     <row r="321" spans="1:12" ht="72" customHeight="1">
       <c r="A321" s="4" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>42</v>
@@ -20596,10 +20629,10 @@
         <v>9</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L321" s="6" t="s">
         <v>165</v>
@@ -20607,13 +20640,13 @@
     </row>
     <row r="322" spans="1:12" ht="72" customHeight="1">
       <c r="A322" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>42</v>
@@ -20625,10 +20658,10 @@
         <v>9</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="K322" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>518</v>
@@ -20636,13 +20669,13 @@
     </row>
     <row r="323" spans="1:12" ht="72" customHeight="1">
       <c r="A323" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>42</v>
@@ -20654,10 +20687,10 @@
         <v>9</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="K323" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="L323" s="6" t="s">
         <v>81</v>
@@ -20665,13 +20698,13 @@
     </row>
     <row r="324" spans="1:12" ht="72" customHeight="1">
       <c r="A324" s="4" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>42</v>
@@ -20683,10 +20716,10 @@
         <v>9</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>39</v>
@@ -20694,13 +20727,13 @@
     </row>
     <row r="325" spans="1:12" ht="72" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>42</v>
@@ -20712,10 +20745,10 @@
         <v>9</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="K325" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>88</v>
@@ -20723,13 +20756,13 @@
     </row>
     <row r="326" spans="1:12" ht="72" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>42</v>
@@ -20741,10 +20774,10 @@
         <v>9</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K326" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="L326" s="6" t="s">
         <v>159</v>
@@ -20752,13 +20785,13 @@
     </row>
     <row r="327" spans="1:12" ht="72" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>42</v>
@@ -20770,10 +20803,10 @@
         <v>9</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="K327" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>103</v>
@@ -20781,13 +20814,13 @@
     </row>
     <row r="328" spans="1:12" ht="72" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>42</v>
@@ -20799,10 +20832,10 @@
         <v>9</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K328" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>518</v>
@@ -20810,13 +20843,13 @@
     </row>
     <row r="329" spans="1:12" ht="72" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>42</v>
@@ -20828,10 +20861,10 @@
         <v>9</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="L329" s="6" t="s">
         <v>88</v>
@@ -20839,13 +20872,13 @@
     </row>
     <row r="330" spans="1:12" ht="72" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>42</v>
@@ -20857,10 +20890,10 @@
         <v>9</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>625</v>
@@ -20868,13 +20901,13 @@
     </row>
     <row r="331" spans="1:12" ht="72" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>42</v>
@@ -20886,10 +20919,10 @@
         <v>9</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -20897,13 +20930,13 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>42</v>
@@ -20915,10 +20948,10 @@
         <v>9</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -20926,13 +20959,13 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
@@ -20944,10 +20977,10 @@
         <v>9</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -20955,13 +20988,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -20973,10 +21006,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -20984,13 +21017,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -21002,10 +21035,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21013,13 +21046,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -21031,10 +21064,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21042,13 +21075,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21060,10 +21093,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21071,13 +21104,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21089,10 +21122,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21100,13 +21133,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21118,10 +21151,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21129,13 +21162,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21147,10 +21180,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21158,13 +21191,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21176,10 +21209,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21187,13 +21220,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21205,10 +21238,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21216,13 +21249,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21234,10 +21267,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21245,13 +21278,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21263,10 +21296,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21274,13 +21307,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21292,10 +21325,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21303,13 +21336,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21321,10 +21354,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21332,13 +21365,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21350,10 +21383,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21361,13 +21394,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21379,10 +21412,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21390,13 +21423,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21408,10 +21441,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21419,13 +21452,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21437,10 +21470,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21448,13 +21481,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21466,24 +21499,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21495,10 +21528,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21506,13 +21539,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21524,10 +21557,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21535,13 +21568,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21553,10 +21586,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21564,13 +21597,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21582,10 +21615,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21593,13 +21626,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21611,10 +21644,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21622,13 +21655,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21640,10 +21673,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21651,13 +21684,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21669,10 +21702,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21680,13 +21713,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21698,10 +21731,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21709,13 +21742,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21727,10 +21760,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21738,13 +21771,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21756,10 +21789,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21767,13 +21800,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21785,10 +21818,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -21796,13 +21829,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -21814,10 +21847,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -21825,13 +21858,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -21843,10 +21876,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -21854,13 +21887,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -21872,10 +21905,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -21883,13 +21916,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -21901,10 +21934,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -21912,13 +21945,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -21930,10 +21963,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -21941,13 +21974,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -21959,10 +21992,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -21970,13 +22003,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -21988,10 +22021,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -21999,13 +22032,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22017,10 +22050,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22028,13 +22061,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22046,10 +22079,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22057,13 +22090,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22075,10 +22108,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22086,13 +22119,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22104,10 +22137,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22115,13 +22148,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22133,10 +22166,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22144,13 +22177,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22162,10 +22195,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22173,13 +22206,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22191,10 +22224,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22202,13 +22235,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22220,10 +22253,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22231,13 +22264,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22249,10 +22282,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22260,13 +22293,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22278,10 +22311,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22289,13 +22322,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22307,10 +22340,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22318,13 +22351,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22336,10 +22369,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22347,13 +22380,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22365,24 +22398,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22394,10 +22427,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22405,13 +22438,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22423,10 +22456,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22434,13 +22467,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22452,10 +22485,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22463,13 +22496,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22481,10 +22514,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22492,13 +22525,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22510,10 +22543,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22521,13 +22554,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22539,10 +22572,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22550,13 +22583,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22568,10 +22601,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22579,13 +22612,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22597,24 +22630,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22626,10 +22659,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22637,13 +22670,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22655,24 +22688,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22684,10 +22717,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22695,13 +22728,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22713,10 +22746,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22724,13 +22757,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22742,24 +22775,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22771,10 +22804,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22782,13 +22815,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -22800,10 +22833,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -22811,13 +22844,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -22829,10 +22862,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -22840,13 +22873,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -22858,10 +22891,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -22869,13 +22902,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -22887,10 +22920,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -22898,13 +22931,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -22916,10 +22949,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -22927,13 +22960,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -22945,10 +22978,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -22956,13 +22989,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -22974,24 +23007,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23003,10 +23036,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23014,13 +23047,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23032,10 +23065,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23043,13 +23076,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23061,10 +23094,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23072,13 +23105,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23090,10 +23123,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23101,13 +23134,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23119,10 +23152,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23130,13 +23163,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23148,10 +23181,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23159,13 +23192,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23177,10 +23210,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23188,13 +23221,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23206,24 +23239,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23235,10 +23268,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23246,13 +23279,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23264,10 +23297,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23275,13 +23308,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23293,10 +23326,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23304,13 +23337,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23322,10 +23355,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23333,13 +23366,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23351,10 +23384,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23362,13 +23395,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23380,10 +23413,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23391,13 +23424,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23409,10 +23442,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23420,13 +23453,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23438,10 +23471,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23449,13 +23482,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23467,10 +23500,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23478,13 +23511,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23496,10 +23529,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23507,13 +23540,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23525,10 +23558,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23536,13 +23569,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23554,10 +23587,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23565,13 +23598,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23583,10 +23616,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23594,13 +23627,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23612,10 +23645,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23623,13 +23656,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23641,10 +23674,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23652,13 +23685,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23670,10 +23703,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23681,13 +23714,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23699,10 +23732,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23710,13 +23743,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23728,10 +23761,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23739,13 +23772,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23757,10 +23790,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23768,13 +23801,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23786,10 +23819,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -23797,13 +23830,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -23815,10 +23848,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -23826,13 +23859,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -23844,10 +23877,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -23855,13 +23888,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -23873,10 +23906,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -23884,13 +23917,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -23902,10 +23935,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -23913,13 +23946,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -23931,10 +23964,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -23942,13 +23975,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -23960,10 +23993,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -23971,13 +24004,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -23989,10 +24022,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24000,13 +24033,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24018,10 +24051,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24029,13 +24062,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24047,10 +24080,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24058,13 +24091,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24076,10 +24109,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24087,13 +24120,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24105,10 +24138,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24116,13 +24149,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24134,10 +24167,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24145,13 +24178,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24163,10 +24196,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24174,13 +24207,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24192,10 +24225,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24203,13 +24236,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24221,10 +24254,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24232,13 +24265,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24250,10 +24283,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24261,13 +24294,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24279,10 +24312,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24290,13 +24323,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24308,10 +24341,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24319,13 +24352,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24337,10 +24370,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24348,13 +24381,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24366,10 +24399,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24377,13 +24410,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24395,10 +24428,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24406,13 +24439,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24424,10 +24457,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24435,13 +24468,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24453,10 +24486,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24464,13 +24497,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24482,10 +24515,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24493,13 +24526,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24511,24 +24544,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24540,10 +24573,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24551,13 +24584,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24569,10 +24602,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24580,13 +24613,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24598,10 +24631,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24609,13 +24642,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24627,10 +24660,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24638,13 +24671,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24656,10 +24689,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24667,13 +24700,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24685,10 +24718,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24696,13 +24729,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24714,10 +24747,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24725,13 +24758,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24743,10 +24776,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24754,13 +24787,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24772,10 +24805,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24783,13 +24816,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -24801,10 +24834,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -24812,13 +24845,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -24830,10 +24863,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -24841,13 +24874,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -24859,10 +24892,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -24870,13 +24903,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -24888,10 +24921,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -24899,13 +24932,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -24917,10 +24950,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -24928,13 +24961,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -24946,10 +24979,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -24957,13 +24990,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -24975,10 +25008,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -24986,13 +25019,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25004,10 +25037,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25015,13 +25048,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25033,10 +25066,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25044,13 +25077,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25062,10 +25095,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25073,13 +25106,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25091,10 +25124,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25102,13 +25135,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25120,10 +25153,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25131,13 +25164,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25149,10 +25182,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25160,13 +25193,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25178,10 +25211,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25189,13 +25222,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25207,10 +25240,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25218,13 +25251,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25236,10 +25269,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25247,13 +25280,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25265,10 +25298,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25276,13 +25309,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25294,10 +25327,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25305,13 +25338,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25323,10 +25356,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25334,13 +25367,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25352,10 +25385,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25363,13 +25396,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25381,10 +25414,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25392,13 +25425,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25410,10 +25443,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25421,13 +25454,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25439,10 +25472,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25450,13 +25483,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25468,10 +25501,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25479,13 +25512,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25497,10 +25530,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25508,13 +25541,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25526,10 +25559,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25537,13 +25570,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25555,10 +25588,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25566,13 +25599,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25584,10 +25617,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26118,7 +26151,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L309"/>
+  <dimension ref="A1:L312"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -37863,8 +37896,122 @@
         <v>165</v>
       </c>
     </row>
+    <row r="310" spans="1:12" ht="72" customHeight="1">
+      <c r="A310" s="4" t="s">
+        <v>1431</v>
+      </c>
+      <c r="B310" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C310" s="4" t="s">
+        <v>1433</v>
+      </c>
+      <c r="D310" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E310" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F310" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G310" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H310" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I310" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J310" s="4" t="s">
+        <v>1436</v>
+      </c>
+      <c r="K310" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="L310" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="311" spans="1:12" ht="72" customHeight="1">
+      <c r="A311" s="4" t="s">
+        <v>1438</v>
+      </c>
+      <c r="B311" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C311" s="4" t="s">
+        <v>1439</v>
+      </c>
+      <c r="D311" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E311" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F311" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G311" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H311" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I311" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J311" s="4" t="s">
+        <v>1440</v>
+      </c>
+      <c r="K311" s="4" t="s">
+        <v>1437</v>
+      </c>
+      <c r="L311" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="312" spans="1:12" ht="72" customHeight="1">
+      <c r="A312" s="4" t="s">
+        <v>1441</v>
+      </c>
+      <c r="B312" s="4" t="s">
+        <v>1432</v>
+      </c>
+      <c r="C312" s="4" t="s">
+        <v>1442</v>
+      </c>
+      <c r="D312" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E312" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F312" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G312" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="H312" s="4" t="s">
+        <v>1434</v>
+      </c>
+      <c r="I312" s="4" t="s">
+        <v>1435</v>
+      </c>
+      <c r="J312" s="4" t="s">
+        <v>1443</v>
+      </c>
+      <c r="K312" s="4" t="s">
+        <v>1444</v>
+      </c>
+      <c r="L312" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F309">
+  <conditionalFormatting sqref="E2:F312">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -38190,11 +38337,14 @@
     <hyperlink ref="L307" r:id="rId306"/>
     <hyperlink ref="L308" r:id="rId307"/>
     <hyperlink ref="L309" r:id="rId308"/>
+    <hyperlink ref="L310" r:id="rId309"/>
+    <hyperlink ref="L311" r:id="rId310"/>
+    <hyperlink ref="L312" r:id="rId311"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId309"/>
+    <tablePart r:id="rId312"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38211,3128 +38361,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>1435</v>
+        <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>1444</v>
+        <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1464</v>
+        <v>1466</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2495</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2496</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2198</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2497</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2166</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2493</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2494</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2196</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2495</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2164</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2491</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2543</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2018</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2223</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2540</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2541</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2016</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2542</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2543</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2221</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2544</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2538</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2545</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2539</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2586</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2139</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2138</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2166</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2584</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2137</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2585</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2138</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2136</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2164</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2582</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2583</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2143</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2141</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2139</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2144</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2142</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2147</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2145</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2583</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2150</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2581</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2148</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10104" uniqueCount="2596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10179" uniqueCount="2598">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 07:35 BST</t>
+    <t>Snapshot: 07 September 2026, 07:55 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4280,7 +4280,7 @@
     <t>Record-board title and proof context</t>
   </si>
   <si>
-    <t>Full responsive searchable/sortable record browser with exact category/period/proof/details and submissions count; real mobile hub route. course-records-browser.log PASS15s both surfaces x6sizes, real isolated course, no-verified-leader/filter reset/details/exactboardhref/nooverflow.390 screenshot inspected; types/lint pass. Backend11targeted tests and period-bound regression pass; verified leader excludes inactive/unverified results.</t>
+    <t>Full responsive searchable/sortable record browser with exact category/period/proof/details and submissions count; real mobile hub route. course-records-browser.log PASS15s both surfaces x6sizes, real isolated course, no-verified-leader/filter reset/details/exactboardhref/nooverflow.390 screenshot inspected; types/lint pass. Backend11targeted tests and period-bound regression pass; verified leader excludes inactive/unverified results. P57 regression correction: generated result status verified now accepted alongside active while verificationStatus remains verified; targeted database regression passed.</t>
   </si>
   <si>
     <t>Positive verified-leader browser fixture, actual downstream board/submission navigation (P56/P57 still outstanding), server error recovery, 80course source limit beyond loaded scope, physical keyboard/AT/zoom/theme and shared sticky-nav overlap remain open. No full acceptance.</t>
@@ -4325,7 +4325,7 @@
     <t>Course-specific record table</t>
   </si>
   <si>
-    <t>Full responsive course category table/details, controlled URL scope tabs, exact eligible submission links. course-record-scopes-browser.log PASS33.3s both surfaces x6sizes, reload/BackForward, category search/reset/sort, every selected targetcheckedagainstfixturecourse ID. Types/scoped lint pass;390 capture inspected. Backend12targeted tests verify active verified leader only and retain pending attempts separately.</t>
+    <t>Full responsive course category table/details, controlled URL scope tabs, exact eligible submission links. course-record-scopes-browser.log PASS33.3s both surfaces x6sizes, reload/BackForward, category search/reset/sort, every selected targetcheckedagainstfixturecourse ID. Types/scoped lint pass;390 capture inspected. Backend12targeted tests verify active verified leader only and retain pending attempts separately. P57 regression correction: generated result status verified now accepted alongside active while verificationStatus remains verified; targeted database regression passed.</t>
   </si>
   <si>
     <t>Positive verified leader/previous-round suggestion UI, actual submission destination P57, server error/permission UI, physical keyboard/AT/zoom/theme and shared fixed-navigation overlap remain unverified. No full acceptance.</t>
@@ -4365,6 +4365,12 @@
   </si>
   <si>
     <t>Record identity, champion and personal best</t>
+  </si>
+  <si>
+    <t>Full responsive record identity, ranked/proof context, locked selected-round score, full proof preview/retry/remove, review-before-submit and owned numeric receipt. Isolated proof/draft matrix PASS17.8s; actual record-detail-browser-final.log PASS26.0s both surfaces x6 sizes: 12 distinct requestIds and saved receipts, explicit pre-existing auto-synced attempt, unchanged source round. Types/lint pass; mobile screenshot inspected. Backend31files110tests pass including retry rollback, private-course denial and generated verified status regression.</t>
+  </si>
+  <si>
+    <t>Full signed real OCR/positive proof verification, tournament uploader consumer browser regression, all eligible-round filtering (currently calculable rounds, server checks), historical &gt;20 attempt receipts, AT/zoom/theme/keyboard and shared fixed navigation overlap remain outstanding. Existing rule auto-ranks manual-only scorecards as Bronze; UI explicitly distinguishes this from image verification. No full acceptance.</t>
   </si>
   <si>
     <t>Gross/net/other categories and proof status are never conflated.</t>
@@ -7981,8 +7987,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L312" totalsRowShown="0">
-  <autoFilter ref="A1:L312"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L317" totalsRowShown="0">
+  <autoFilter ref="A1:L317"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8376,11 +8382,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8415,11 +8421,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>181</v>
+        <v>176</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -20391,16 +20397,25 @@
         <v>42</v>
       </c>
       <c r="E313" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F313" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G313" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H313" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I313" s="4" t="s">
+        <v>1449</v>
       </c>
       <c r="J313" s="4" t="s">
-        <v>1448</v>
+        <v>1450</v>
       </c>
       <c r="K313" s="4" t="s">
-        <v>1449</v>
+        <v>1451</v>
       </c>
       <c r="L313" s="6" t="s">
         <v>39</v>
@@ -20408,28 +20423,37 @@
     </row>
     <row r="314" spans="1:12" ht="72" customHeight="1">
       <c r="A314" s="4" t="s">
-        <v>1450</v>
+        <v>1452</v>
       </c>
       <c r="B314" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C314" s="4" t="s">
-        <v>1451</v>
+        <v>1453</v>
       </c>
       <c r="D314" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E314" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F314" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G314" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>1449</v>
       </c>
       <c r="J314" s="4" t="s">
-        <v>1452</v>
+        <v>1454</v>
       </c>
       <c r="K314" s="4" t="s">
-        <v>1453</v>
+        <v>1455</v>
       </c>
       <c r="L314" s="6" t="s">
         <v>518</v>
@@ -20437,28 +20461,37 @@
     </row>
     <row r="315" spans="1:12" ht="72" customHeight="1">
       <c r="A315" s="4" t="s">
-        <v>1454</v>
+        <v>1456</v>
       </c>
       <c r="B315" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C315" s="4" t="s">
-        <v>1455</v>
+        <v>1457</v>
       </c>
       <c r="D315" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E315" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F315" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G315" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I315" s="4" t="s">
+        <v>1449</v>
       </c>
       <c r="J315" s="4" t="s">
-        <v>1456</v>
+        <v>1458</v>
       </c>
       <c r="K315" s="4" t="s">
-        <v>1457</v>
+        <v>1459</v>
       </c>
       <c r="L315" s="6" t="s">
         <v>1045</v>
@@ -20466,28 +20499,37 @@
     </row>
     <row r="316" spans="1:12" ht="72" customHeight="1">
       <c r="A316" s="4" t="s">
-        <v>1458</v>
+        <v>1460</v>
       </c>
       <c r="B316" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C316" s="4" t="s">
-        <v>1459</v>
+        <v>1461</v>
       </c>
       <c r="D316" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E316" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F316" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G316" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>1449</v>
       </c>
       <c r="J316" s="4" t="s">
-        <v>1460</v>
+        <v>1462</v>
       </c>
       <c r="K316" s="4" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="L316" s="6" t="s">
         <v>88</v>
@@ -20495,28 +20537,37 @@
     </row>
     <row r="317" spans="1:12" ht="72" customHeight="1">
       <c r="A317" s="4" t="s">
-        <v>1462</v>
+        <v>1464</v>
       </c>
       <c r="B317" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C317" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G317" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I317" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J317" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K317" s="4" t="s">
         <v>1463</v>
-      </c>
-      <c r="D317" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E317" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F317" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J317" s="4" t="s">
-        <v>1464</v>
-      </c>
-      <c r="K317" s="4" t="s">
-        <v>1461</v>
       </c>
       <c r="L317" s="6" t="s">
         <v>116</v>
@@ -20524,13 +20575,13 @@
     </row>
     <row r="318" spans="1:12" ht="72" customHeight="1">
       <c r="A318" s="4" t="s">
-        <v>1465</v>
+        <v>1467</v>
       </c>
       <c r="B318" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C318" s="4" t="s">
-        <v>1467</v>
+        <v>1469</v>
       </c>
       <c r="D318" s="4" t="s">
         <v>42</v>
@@ -20542,10 +20593,10 @@
         <v>9</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1468</v>
+        <v>1470</v>
       </c>
       <c r="K318" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>141</v>
@@ -20553,13 +20604,13 @@
     </row>
     <row r="319" spans="1:12" ht="72" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="B319" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C319" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="D319" s="4" t="s">
         <v>42</v>
@@ -20571,10 +20622,10 @@
         <v>9</v>
       </c>
       <c r="J319" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="K319" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L319" s="6" t="s">
         <v>165</v>
@@ -20582,13 +20633,13 @@
     </row>
     <row r="320" spans="1:12" ht="72" customHeight="1">
       <c r="A320" s="4" t="s">
-        <v>1473</v>
+        <v>1475</v>
       </c>
       <c r="B320" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1474</v>
+        <v>1476</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>42</v>
@@ -20600,10 +20651,10 @@
         <v>9</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="K320" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>165</v>
@@ -20611,13 +20662,13 @@
     </row>
     <row r="321" spans="1:12" ht="72" customHeight="1">
       <c r="A321" s="4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="B321" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>42</v>
@@ -20629,10 +20680,10 @@
         <v>9</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L321" s="6" t="s">
         <v>165</v>
@@ -20640,13 +20691,13 @@
     </row>
     <row r="322" spans="1:12" ht="72" customHeight="1">
       <c r="A322" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="B322" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>42</v>
@@ -20658,10 +20709,10 @@
         <v>9</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="K322" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>518</v>
@@ -20669,13 +20720,13 @@
     </row>
     <row r="323" spans="1:12" ht="72" customHeight="1">
       <c r="A323" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="B323" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>42</v>
@@ -20687,10 +20738,10 @@
         <v>9</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="K323" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="L323" s="6" t="s">
         <v>81</v>
@@ -20698,13 +20749,13 @@
     </row>
     <row r="324" spans="1:12" ht="72" customHeight="1">
       <c r="A324" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>42</v>
@@ -20716,10 +20767,10 @@
         <v>9</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>39</v>
@@ -20727,13 +20778,13 @@
     </row>
     <row r="325" spans="1:12" ht="72" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>42</v>
@@ -20745,10 +20796,10 @@
         <v>9</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K325" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>88</v>
@@ -20756,13 +20807,13 @@
     </row>
     <row r="326" spans="1:12" ht="72" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>42</v>
@@ -20774,10 +20825,10 @@
         <v>9</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="K326" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="L326" s="6" t="s">
         <v>159</v>
@@ -20785,13 +20836,13 @@
     </row>
     <row r="327" spans="1:12" ht="72" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>42</v>
@@ -20803,10 +20854,10 @@
         <v>9</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K327" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>103</v>
@@ -20814,13 +20865,13 @@
     </row>
     <row r="328" spans="1:12" ht="72" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>42</v>
@@ -20832,10 +20883,10 @@
         <v>9</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="K328" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>518</v>
@@ -20843,13 +20894,13 @@
     </row>
     <row r="329" spans="1:12" ht="72" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>42</v>
@@ -20861,10 +20912,10 @@
         <v>9</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L329" s="6" t="s">
         <v>88</v>
@@ -20872,13 +20923,13 @@
     </row>
     <row r="330" spans="1:12" ht="72" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>42</v>
@@ -20890,10 +20941,10 @@
         <v>9</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>625</v>
@@ -20901,13 +20952,13 @@
     </row>
     <row r="331" spans="1:12" ht="72" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>42</v>
@@ -20919,10 +20970,10 @@
         <v>9</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -20930,13 +20981,13 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>42</v>
@@ -20948,10 +20999,10 @@
         <v>9</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -20959,13 +21010,13 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
@@ -20977,10 +21028,10 @@
         <v>9</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -20988,13 +21039,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -21006,10 +21057,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -21017,13 +21068,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -21035,10 +21086,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21046,13 +21097,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -21064,10 +21115,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21075,13 +21126,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21093,10 +21144,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21104,13 +21155,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21122,10 +21173,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21133,13 +21184,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21151,10 +21202,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21162,13 +21213,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21180,10 +21231,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21191,13 +21242,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21209,10 +21260,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21220,13 +21271,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21238,10 +21289,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21249,13 +21300,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21267,10 +21318,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21278,13 +21329,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21296,10 +21347,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21307,13 +21358,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21325,10 +21376,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21336,13 +21387,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21354,10 +21405,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21365,13 +21416,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21383,10 +21434,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21394,13 +21445,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21412,10 +21463,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21423,13 +21474,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21441,10 +21492,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21452,13 +21503,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21470,10 +21521,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21481,13 +21532,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21499,24 +21550,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21528,10 +21579,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21539,13 +21590,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21557,10 +21608,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21568,13 +21619,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21586,10 +21637,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21597,13 +21648,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21615,10 +21666,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21626,13 +21677,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21644,10 +21695,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21655,13 +21706,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21673,10 +21724,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21684,13 +21735,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21702,10 +21753,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21713,13 +21764,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21731,10 +21782,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21742,13 +21793,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21760,10 +21811,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21771,13 +21822,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21789,10 +21840,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21800,13 +21851,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21818,10 +21869,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -21829,13 +21880,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -21847,10 +21898,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -21858,13 +21909,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -21876,10 +21927,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -21887,13 +21938,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -21905,10 +21956,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -21916,13 +21967,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -21934,10 +21985,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -21945,13 +21996,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -21963,10 +22014,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -21974,13 +22025,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -21992,10 +22043,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22003,13 +22054,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22021,10 +22072,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22032,13 +22083,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22050,10 +22101,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22061,13 +22112,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22079,10 +22130,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22090,13 +22141,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22108,10 +22159,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22119,13 +22170,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22137,10 +22188,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22148,13 +22199,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22166,10 +22217,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22177,13 +22228,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22195,10 +22246,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22206,13 +22257,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22224,10 +22275,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22235,13 +22286,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22253,10 +22304,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22264,13 +22315,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22282,10 +22333,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22293,13 +22344,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22311,10 +22362,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22322,13 +22373,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22340,10 +22391,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22351,13 +22402,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22369,10 +22420,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22380,13 +22431,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22398,24 +22449,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22427,10 +22478,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22438,13 +22489,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22456,10 +22507,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22467,13 +22518,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22485,10 +22536,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22496,13 +22547,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22514,10 +22565,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22525,13 +22576,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22543,10 +22594,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22554,13 +22605,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22572,10 +22623,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22583,13 +22634,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22601,10 +22652,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22612,13 +22663,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22630,24 +22681,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22659,10 +22710,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22670,13 +22721,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22688,24 +22739,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22717,10 +22768,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22728,13 +22779,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22746,10 +22797,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22757,13 +22808,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22775,24 +22826,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22804,10 +22855,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22815,13 +22866,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -22833,10 +22884,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -22844,13 +22895,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -22862,10 +22913,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -22873,13 +22924,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -22891,10 +22942,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -22902,13 +22953,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -22920,10 +22971,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -22931,13 +22982,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -22949,10 +23000,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -22960,13 +23011,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -22978,10 +23029,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -22989,13 +23040,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23007,24 +23058,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23036,10 +23087,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23047,13 +23098,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23065,10 +23116,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23076,13 +23127,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23094,10 +23145,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23105,13 +23156,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23123,10 +23174,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23134,13 +23185,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23152,10 +23203,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23163,13 +23214,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23181,10 +23232,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23192,13 +23243,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23210,10 +23261,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23221,13 +23272,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23239,24 +23290,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23268,10 +23319,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23279,13 +23330,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23297,10 +23348,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23308,13 +23359,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23326,10 +23377,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23337,13 +23388,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23355,10 +23406,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23366,13 +23417,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23384,10 +23435,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23395,13 +23446,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23413,10 +23464,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23424,13 +23475,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23442,10 +23493,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23453,13 +23504,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23471,10 +23522,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23482,13 +23533,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23500,10 +23551,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23511,13 +23562,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23529,10 +23580,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23540,13 +23591,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23558,10 +23609,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23569,13 +23620,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23587,10 +23638,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23598,13 +23649,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23616,10 +23667,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23627,13 +23678,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23645,10 +23696,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23656,13 +23707,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23674,10 +23725,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23685,13 +23736,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23703,10 +23754,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23714,13 +23765,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23732,10 +23783,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23743,13 +23794,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23761,10 +23812,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23772,13 +23823,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23790,10 +23841,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23801,13 +23852,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23819,10 +23870,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -23830,13 +23881,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -23848,10 +23899,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -23859,13 +23910,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -23877,10 +23928,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -23888,13 +23939,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -23906,10 +23957,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -23917,13 +23968,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -23935,10 +23986,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -23946,13 +23997,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -23964,10 +24015,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -23975,13 +24026,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -23993,10 +24044,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24004,13 +24055,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24022,10 +24073,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24033,13 +24084,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24051,10 +24102,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24062,13 +24113,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24080,10 +24131,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24091,13 +24142,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24109,10 +24160,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24120,13 +24171,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24138,10 +24189,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24149,13 +24200,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24167,10 +24218,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24178,13 +24229,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24196,10 +24247,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24207,13 +24258,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24225,10 +24276,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24236,13 +24287,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24254,10 +24305,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24265,13 +24316,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24283,10 +24334,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24294,13 +24345,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24312,10 +24363,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24323,13 +24374,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24341,10 +24392,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24352,13 +24403,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24370,10 +24421,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24381,13 +24432,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24399,10 +24450,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24410,13 +24461,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24428,10 +24479,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24439,13 +24490,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24457,10 +24508,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24468,13 +24519,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24486,10 +24537,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24497,13 +24548,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24515,10 +24566,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24526,13 +24577,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24544,24 +24595,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24573,10 +24624,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24584,13 +24635,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24602,10 +24653,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24613,13 +24664,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24631,10 +24682,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24642,13 +24693,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24660,10 +24711,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24671,13 +24722,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24689,10 +24740,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24700,13 +24751,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24718,10 +24769,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24729,13 +24780,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24747,10 +24798,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24758,13 +24809,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24776,10 +24827,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24787,13 +24838,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24805,10 +24856,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24816,13 +24867,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -24834,10 +24885,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -24845,13 +24896,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -24863,10 +24914,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -24874,13 +24925,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -24892,10 +24943,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -24903,13 +24954,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -24921,10 +24972,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -24932,13 +24983,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -24950,10 +25001,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -24961,13 +25012,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -24979,10 +25030,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -24990,13 +25041,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25008,10 +25059,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25019,13 +25070,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25037,10 +25088,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25048,13 +25099,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25066,10 +25117,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25077,13 +25128,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25095,10 +25146,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25106,13 +25157,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25124,10 +25175,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25135,13 +25186,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25153,10 +25204,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25164,13 +25215,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25182,10 +25233,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25193,13 +25244,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25211,10 +25262,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25222,13 +25273,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25240,10 +25291,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25251,13 +25302,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25269,10 +25320,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25280,13 +25331,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25298,10 +25349,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25309,13 +25360,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25327,10 +25378,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25338,13 +25389,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25356,10 +25407,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25367,13 +25418,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25385,10 +25436,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25396,13 +25447,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25414,10 +25465,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25425,13 +25476,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25443,10 +25494,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25454,13 +25505,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25472,10 +25523,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25483,13 +25534,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25501,10 +25552,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25512,13 +25563,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25530,10 +25581,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25541,13 +25592,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25559,10 +25610,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25570,13 +25621,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25588,10 +25639,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25599,13 +25650,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25617,10 +25668,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26151,7 +26202,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L312"/>
+  <dimension ref="A1:L317"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -38010,8 +38061,198 @@
         <v>165</v>
       </c>
     </row>
+    <row r="313" spans="1:12" ht="72" customHeight="1">
+      <c r="A313" s="4" t="s">
+        <v>1445</v>
+      </c>
+      <c r="B313" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C313" s="4" t="s">
+        <v>1447</v>
+      </c>
+      <c r="D313" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E313" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F313" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G313" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H313" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I313" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J313" s="4" t="s">
+        <v>1450</v>
+      </c>
+      <c r="K313" s="4" t="s">
+        <v>1451</v>
+      </c>
+      <c r="L313" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="314" spans="1:12" ht="72" customHeight="1">
+      <c r="A314" s="4" t="s">
+        <v>1452</v>
+      </c>
+      <c r="B314" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C314" s="4" t="s">
+        <v>1453</v>
+      </c>
+      <c r="D314" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E314" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F314" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G314" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H314" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I314" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J314" s="4" t="s">
+        <v>1454</v>
+      </c>
+      <c r="K314" s="4" t="s">
+        <v>1455</v>
+      </c>
+      <c r="L314" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="315" spans="1:12" ht="72" customHeight="1">
+      <c r="A315" s="4" t="s">
+        <v>1456</v>
+      </c>
+      <c r="B315" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C315" s="4" t="s">
+        <v>1457</v>
+      </c>
+      <c r="D315" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E315" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F315" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G315" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H315" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I315" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J315" s="4" t="s">
+        <v>1458</v>
+      </c>
+      <c r="K315" s="4" t="s">
+        <v>1459</v>
+      </c>
+      <c r="L315" s="6" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="316" spans="1:12" ht="72" customHeight="1">
+      <c r="A316" s="4" t="s">
+        <v>1460</v>
+      </c>
+      <c r="B316" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C316" s="4" t="s">
+        <v>1461</v>
+      </c>
+      <c r="D316" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E316" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F316" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G316" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H316" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I316" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J316" s="4" t="s">
+        <v>1462</v>
+      </c>
+      <c r="K316" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="L316" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="317" spans="1:12" ht="72" customHeight="1">
+      <c r="A317" s="4" t="s">
+        <v>1464</v>
+      </c>
+      <c r="B317" s="4" t="s">
+        <v>1446</v>
+      </c>
+      <c r="C317" s="4" t="s">
+        <v>1465</v>
+      </c>
+      <c r="D317" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F317" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G317" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="H317" s="4" t="s">
+        <v>1448</v>
+      </c>
+      <c r="I317" s="4" t="s">
+        <v>1449</v>
+      </c>
+      <c r="J317" s="4" t="s">
+        <v>1466</v>
+      </c>
+      <c r="K317" s="4" t="s">
+        <v>1463</v>
+      </c>
+      <c r="L317" s="6" t="s">
+        <v>116</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F312">
+  <conditionalFormatting sqref="E2:F317">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -38340,11 +38581,16 @@
     <hyperlink ref="L310" r:id="rId309"/>
     <hyperlink ref="L311" r:id="rId310"/>
     <hyperlink ref="L312" r:id="rId311"/>
+    <hyperlink ref="L313" r:id="rId312"/>
+    <hyperlink ref="L314" r:id="rId313"/>
+    <hyperlink ref="L315" r:id="rId314"/>
+    <hyperlink ref="L316" r:id="rId315"/>
+    <hyperlink ref="L317" r:id="rId316"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId312"/>
+    <tablePart r:id="rId317"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38361,3128 +38607,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>1461</v>
+        <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>1466</v>
+        <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1469</v>
+        <v>1471</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2498</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2200</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2499</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2168</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2495</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2496</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2198</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2497</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2166</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2493</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2545</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2225</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2542</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2543</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2018</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2544</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2545</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2223</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2546</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2540</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2547</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2541</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2549</v>
+        <v>2551</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2588</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2141</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2142</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2140</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2168</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2586</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2139</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2587</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2140</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2138</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2166</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2584</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2585</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2145</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2143</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2141</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2146</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2144</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2149</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2147</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2585</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2583</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2150</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10179" uniqueCount="2598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10269" uniqueCount="2600">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 07:55 BST</t>
+    <t>Snapshot: 07 September 2026, 08:09 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4431,6 +4431,12 @@
   </si>
   <si>
     <t>Active, available and completed views</t>
+  </si>
+  <si>
+    <t>Full shared Challenges UI: controlled URL state/counts/search, complete qualifying result/target/window/proof rows, chronological completed view, rules with focus return and full creation/review/draft recovery. challenges-browser-final.log PASS59.7s both surfaces x6sizes;12 actual public creations preserve exact dates/scoring/visibility and create zero invites. Mobile/desktop captures inspected. Types/lint pass. Backend9 tests pass dates/closed joins/imported evidence excludes modelled/future/excluded shots. Next development-only indicator pointer interception disabled in test; application errors still asserted absent.</t>
+  </si>
+  <si>
+    <t>Full positive ranked-result browser, search/reset/BackForward edge cases, paid private/friend creation and invitation fixture, save-error retry idempotence, immutable closed ranking snapshot, error/loading boundary and AT/zoom/theme/native keyboard/shared navigation acceptance remain open. No full acceptance.</t>
   </si>
   <si>
     <t>A completed challenge cannot remain presented as currently active after status updates.</t>
@@ -7987,8 +7993,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L317" totalsRowShown="0">
-  <autoFilter ref="A1:L317"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L323" totalsRowShown="0">
+  <autoFilter ref="A1:L323"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8382,11 +8388,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>309</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8421,11 +8427,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>176</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -20587,16 +20593,25 @@
         <v>42</v>
       </c>
       <c r="E318" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F318" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I318" s="4" t="s">
+        <v>1471</v>
       </c>
       <c r="J318" s="4" t="s">
-        <v>1470</v>
+        <v>1472</v>
       </c>
       <c r="K318" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L318" s="6" t="s">
         <v>141</v>
@@ -20604,28 +20619,37 @@
     </row>
     <row r="319" spans="1:12" ht="72" customHeight="1">
       <c r="A319" s="4" t="s">
-        <v>1472</v>
+        <v>1474</v>
       </c>
       <c r="B319" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C319" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G319" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I319" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J319" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K319" s="4" t="s">
         <v>1473</v>
-      </c>
-      <c r="D319" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E319" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F319" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J319" s="4" t="s">
-        <v>1474</v>
-      </c>
-      <c r="K319" s="4" t="s">
-        <v>1471</v>
       </c>
       <c r="L319" s="6" t="s">
         <v>165</v>
@@ -20633,28 +20657,37 @@
     </row>
     <row r="320" spans="1:12" ht="72" customHeight="1">
       <c r="A320" s="4" t="s">
-        <v>1475</v>
+        <v>1477</v>
       </c>
       <c r="B320" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C320" s="4" t="s">
-        <v>1476</v>
+        <v>1478</v>
       </c>
       <c r="D320" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E320" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F320" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I320" s="4" t="s">
+        <v>1471</v>
       </c>
       <c r="J320" s="4" t="s">
-        <v>1477</v>
+        <v>1479</v>
       </c>
       <c r="K320" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L320" s="6" t="s">
         <v>165</v>
@@ -20662,28 +20695,37 @@
     </row>
     <row r="321" spans="1:12" ht="72" customHeight="1">
       <c r="A321" s="4" t="s">
-        <v>1478</v>
+        <v>1480</v>
       </c>
       <c r="B321" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C321" s="4" t="s">
-        <v>1479</v>
+        <v>1481</v>
       </c>
       <c r="D321" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E321" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F321" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G321" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I321" s="4" t="s">
+        <v>1471</v>
       </c>
       <c r="J321" s="4" t="s">
-        <v>1480</v>
+        <v>1482</v>
       </c>
       <c r="K321" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L321" s="6" t="s">
         <v>165</v>
@@ -20691,28 +20733,37 @@
     </row>
     <row r="322" spans="1:12" ht="72" customHeight="1">
       <c r="A322" s="4" t="s">
-        <v>1481</v>
+        <v>1483</v>
       </c>
       <c r="B322" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C322" s="4" t="s">
-        <v>1482</v>
+        <v>1484</v>
       </c>
       <c r="D322" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E322" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F322" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G322" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H322" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I322" s="4" t="s">
+        <v>1471</v>
       </c>
       <c r="J322" s="4" t="s">
-        <v>1483</v>
+        <v>1485</v>
       </c>
       <c r="K322" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L322" s="6" t="s">
         <v>518</v>
@@ -20720,28 +20771,37 @@
     </row>
     <row r="323" spans="1:12" ht="72" customHeight="1">
       <c r="A323" s="4" t="s">
-        <v>1484</v>
+        <v>1486</v>
       </c>
       <c r="B323" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C323" s="4" t="s">
-        <v>1485</v>
+        <v>1487</v>
       </c>
       <c r="D323" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E323" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F323" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G323" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>1471</v>
       </c>
       <c r="J323" s="4" t="s">
-        <v>1486</v>
+        <v>1488</v>
       </c>
       <c r="K323" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="L323" s="6" t="s">
         <v>81</v>
@@ -20749,13 +20809,13 @@
     </row>
     <row r="324" spans="1:12" ht="72" customHeight="1">
       <c r="A324" s="4" t="s">
-        <v>1487</v>
+        <v>1489</v>
       </c>
       <c r="B324" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C324" s="4" t="s">
-        <v>1489</v>
+        <v>1491</v>
       </c>
       <c r="D324" s="4" t="s">
         <v>42</v>
@@ -20767,10 +20827,10 @@
         <v>9</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1490</v>
+        <v>1492</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>1491</v>
+        <v>1493</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>39</v>
@@ -20778,13 +20838,13 @@
     </row>
     <row r="325" spans="1:12" ht="72" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="B325" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>42</v>
@@ -20796,10 +20856,10 @@
         <v>9</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="K325" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>88</v>
@@ -20807,13 +20867,13 @@
     </row>
     <row r="326" spans="1:12" ht="72" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="B326" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>42</v>
@@ -20825,10 +20885,10 @@
         <v>9</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="K326" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="L326" s="6" t="s">
         <v>159</v>
@@ -20836,13 +20896,13 @@
     </row>
     <row r="327" spans="1:12" ht="72" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="B327" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>42</v>
@@ -20854,10 +20914,10 @@
         <v>9</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="K327" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>103</v>
@@ -20865,13 +20925,13 @@
     </row>
     <row r="328" spans="1:12" ht="72" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="B328" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>42</v>
@@ -20883,10 +20943,10 @@
         <v>9</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="K328" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>518</v>
@@ -20894,13 +20954,13 @@
     </row>
     <row r="329" spans="1:12" ht="72" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="B329" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>42</v>
@@ -20912,10 +20972,10 @@
         <v>9</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="L329" s="6" t="s">
         <v>88</v>
@@ -20923,13 +20983,13 @@
     </row>
     <row r="330" spans="1:12" ht="72" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="B330" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>42</v>
@@ -20941,10 +21001,10 @@
         <v>9</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>625</v>
@@ -20952,13 +21012,13 @@
     </row>
     <row r="331" spans="1:12" ht="72" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>42</v>
@@ -20970,10 +21030,10 @@
         <v>9</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -20981,13 +21041,13 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>42</v>
@@ -20999,10 +21059,10 @@
         <v>9</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -21010,13 +21070,13 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
@@ -21028,10 +21088,10 @@
         <v>9</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -21039,13 +21099,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -21057,10 +21117,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -21068,13 +21128,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -21086,10 +21146,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21097,13 +21157,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -21115,10 +21175,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21126,13 +21186,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21144,10 +21204,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21155,13 +21215,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21173,10 +21233,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21184,13 +21244,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21202,10 +21262,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21213,13 +21273,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21231,10 +21291,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21242,13 +21302,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21260,10 +21320,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21271,13 +21331,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21289,10 +21349,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21300,13 +21360,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21318,10 +21378,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21329,13 +21389,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21347,10 +21407,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21358,13 +21418,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21376,10 +21436,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21387,13 +21447,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21405,10 +21465,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21416,13 +21476,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21434,10 +21494,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21445,13 +21505,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21463,10 +21523,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21474,13 +21534,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21492,10 +21552,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21503,13 +21563,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21521,10 +21581,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21532,13 +21592,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21550,24 +21610,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21579,10 +21639,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21590,13 +21650,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21608,10 +21668,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21619,13 +21679,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21637,10 +21697,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21648,13 +21708,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21666,10 +21726,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21677,13 +21737,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21695,10 +21755,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21706,13 +21766,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21724,10 +21784,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21735,13 +21795,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21753,10 +21813,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21764,13 +21824,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21782,10 +21842,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21793,13 +21853,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21811,10 +21871,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21822,13 +21882,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21840,10 +21900,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21851,13 +21911,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21869,10 +21929,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -21880,13 +21940,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -21898,10 +21958,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -21909,13 +21969,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -21927,10 +21987,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -21938,13 +21998,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -21956,10 +22016,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -21967,13 +22027,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -21985,10 +22045,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -21996,13 +22056,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22014,10 +22074,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22025,13 +22085,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22043,10 +22103,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22054,13 +22114,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22072,10 +22132,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22083,13 +22143,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22101,10 +22161,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22112,13 +22172,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22130,10 +22190,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22141,13 +22201,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22159,10 +22219,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22170,13 +22230,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22188,10 +22248,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22199,13 +22259,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22217,10 +22277,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22228,13 +22288,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22246,10 +22306,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22257,13 +22317,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22275,10 +22335,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22286,13 +22346,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22304,10 +22364,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22315,13 +22375,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22333,10 +22393,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22344,13 +22404,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22362,10 +22422,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22373,13 +22433,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22391,10 +22451,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22402,13 +22462,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22420,10 +22480,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22431,13 +22491,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22449,24 +22509,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22478,10 +22538,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22489,13 +22549,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22507,10 +22567,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22518,13 +22578,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22536,10 +22596,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22547,13 +22607,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22565,10 +22625,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22576,13 +22636,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22594,10 +22654,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22605,13 +22665,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22623,10 +22683,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22634,13 +22694,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22652,10 +22712,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22663,13 +22723,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22681,24 +22741,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22710,10 +22770,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22721,13 +22781,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22739,24 +22799,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22768,10 +22828,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22779,13 +22839,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22797,10 +22857,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22808,13 +22868,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22826,24 +22886,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22855,10 +22915,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22866,13 +22926,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -22884,10 +22944,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -22895,13 +22955,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -22913,10 +22973,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -22924,13 +22984,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -22942,10 +23002,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -22953,13 +23013,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -22971,10 +23031,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -22982,13 +23042,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23000,10 +23060,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23011,13 +23071,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23029,10 +23089,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23040,13 +23100,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23058,24 +23118,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23087,10 +23147,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23098,13 +23158,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23116,10 +23176,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23127,13 +23187,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23145,10 +23205,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23156,13 +23216,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23174,10 +23234,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23185,13 +23245,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23203,10 +23263,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23214,13 +23274,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23232,10 +23292,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23243,13 +23303,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23261,10 +23321,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23272,13 +23332,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23290,24 +23350,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23319,10 +23379,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23330,13 +23390,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23348,10 +23408,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23359,13 +23419,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23377,10 +23437,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23388,13 +23448,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23406,10 +23466,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23417,13 +23477,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23435,10 +23495,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23446,13 +23506,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23464,10 +23524,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23475,13 +23535,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23493,10 +23553,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23504,13 +23564,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23522,10 +23582,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23533,13 +23593,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23551,10 +23611,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23562,13 +23622,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23580,10 +23640,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23591,13 +23651,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23609,10 +23669,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23620,13 +23680,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23638,10 +23698,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23649,13 +23709,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23667,10 +23727,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23678,13 +23738,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23696,10 +23756,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23707,13 +23767,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23725,10 +23785,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23736,13 +23796,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23754,10 +23814,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23765,13 +23825,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23783,10 +23843,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23794,13 +23854,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23812,10 +23872,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23823,13 +23883,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23841,10 +23901,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23852,13 +23912,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23870,10 +23930,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -23881,13 +23941,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -23899,10 +23959,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -23910,13 +23970,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -23928,10 +23988,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -23939,13 +23999,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -23957,10 +24017,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -23968,13 +24028,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -23986,10 +24046,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -23997,13 +24057,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24015,10 +24075,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24026,13 +24086,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24044,10 +24104,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24055,13 +24115,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24073,10 +24133,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24084,13 +24144,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24102,10 +24162,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24113,13 +24173,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24131,10 +24191,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24142,13 +24202,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24160,10 +24220,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24171,13 +24231,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24189,10 +24249,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24200,13 +24260,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24218,10 +24278,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24229,13 +24289,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24247,10 +24307,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24258,13 +24318,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24276,10 +24336,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24287,13 +24347,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24305,10 +24365,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24316,13 +24376,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24334,10 +24394,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24345,13 +24405,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24363,10 +24423,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24374,13 +24434,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24392,10 +24452,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24403,13 +24463,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24421,10 +24481,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24432,13 +24492,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24450,10 +24510,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24461,13 +24521,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24479,10 +24539,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24490,13 +24550,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24508,10 +24568,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24519,13 +24579,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24537,10 +24597,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24548,13 +24608,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24566,10 +24626,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24577,13 +24637,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24595,24 +24655,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24624,10 +24684,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24635,13 +24695,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24653,10 +24713,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24664,13 +24724,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24682,10 +24742,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24693,13 +24753,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24711,10 +24771,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24722,13 +24782,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24740,10 +24800,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24751,13 +24811,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24769,10 +24829,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24780,13 +24840,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24798,10 +24858,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24809,13 +24869,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24827,10 +24887,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24838,13 +24898,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24856,10 +24916,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24867,13 +24927,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -24885,10 +24945,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -24896,13 +24956,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -24914,10 +24974,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -24925,13 +24985,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -24943,10 +25003,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -24954,13 +25014,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -24972,10 +25032,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -24983,13 +25043,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25001,10 +25061,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25012,13 +25072,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25030,10 +25090,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25041,13 +25101,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25059,10 +25119,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25070,13 +25130,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25088,10 +25148,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25099,13 +25159,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25117,10 +25177,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25128,13 +25188,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25146,10 +25206,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25157,13 +25217,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25175,10 +25235,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25186,13 +25246,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25204,10 +25264,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25215,13 +25275,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25233,10 +25293,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25244,13 +25304,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25262,10 +25322,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25273,13 +25333,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25291,10 +25351,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25302,13 +25362,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25320,10 +25380,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25331,13 +25391,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25349,10 +25409,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25360,13 +25420,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25378,10 +25438,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25389,13 +25449,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25407,10 +25467,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25418,13 +25478,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25436,10 +25496,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25447,13 +25507,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25465,10 +25525,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25476,13 +25536,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25494,10 +25554,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25505,13 +25565,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25523,10 +25583,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25534,13 +25594,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25552,10 +25612,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25563,13 +25623,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25581,10 +25641,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25592,13 +25652,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25610,10 +25670,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25621,13 +25681,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25639,10 +25699,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25650,13 +25710,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25668,10 +25728,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26202,7 +26262,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L317"/>
+  <dimension ref="A1:L323"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -38251,8 +38311,236 @@
         <v>116</v>
       </c>
     </row>
+    <row r="318" spans="1:12" ht="72" customHeight="1">
+      <c r="A318" s="4" t="s">
+        <v>1467</v>
+      </c>
+      <c r="B318" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C318" s="4" t="s">
+        <v>1469</v>
+      </c>
+      <c r="D318" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E318" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F318" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G318" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H318" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I318" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J318" s="4" t="s">
+        <v>1472</v>
+      </c>
+      <c r="K318" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L318" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="319" spans="1:12" ht="72" customHeight="1">
+      <c r="A319" s="4" t="s">
+        <v>1474</v>
+      </c>
+      <c r="B319" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C319" s="4" t="s">
+        <v>1475</v>
+      </c>
+      <c r="D319" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E319" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F319" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G319" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H319" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I319" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J319" s="4" t="s">
+        <v>1476</v>
+      </c>
+      <c r="K319" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L319" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="320" spans="1:12" ht="72" customHeight="1">
+      <c r="A320" s="4" t="s">
+        <v>1477</v>
+      </c>
+      <c r="B320" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C320" s="4" t="s">
+        <v>1478</v>
+      </c>
+      <c r="D320" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E320" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F320" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G320" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H320" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I320" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J320" s="4" t="s">
+        <v>1479</v>
+      </c>
+      <c r="K320" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L320" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="321" spans="1:12" ht="72" customHeight="1">
+      <c r="A321" s="4" t="s">
+        <v>1480</v>
+      </c>
+      <c r="B321" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C321" s="4" t="s">
+        <v>1481</v>
+      </c>
+      <c r="D321" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E321" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F321" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G321" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H321" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I321" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J321" s="4" t="s">
+        <v>1482</v>
+      </c>
+      <c r="K321" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L321" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="322" spans="1:12" ht="72" customHeight="1">
+      <c r="A322" s="4" t="s">
+        <v>1483</v>
+      </c>
+      <c r="B322" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C322" s="4" t="s">
+        <v>1484</v>
+      </c>
+      <c r="D322" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E322" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F322" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G322" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H322" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I322" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J322" s="4" t="s">
+        <v>1485</v>
+      </c>
+      <c r="K322" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L322" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="323" spans="1:12" ht="72" customHeight="1">
+      <c r="A323" s="4" t="s">
+        <v>1486</v>
+      </c>
+      <c r="B323" s="4" t="s">
+        <v>1468</v>
+      </c>
+      <c r="C323" s="4" t="s">
+        <v>1487</v>
+      </c>
+      <c r="D323" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E323" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F323" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G323" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="H323" s="4" t="s">
+        <v>1470</v>
+      </c>
+      <c r="I323" s="4" t="s">
+        <v>1471</v>
+      </c>
+      <c r="J323" s="4" t="s">
+        <v>1488</v>
+      </c>
+      <c r="K323" s="4" t="s">
+        <v>1473</v>
+      </c>
+      <c r="L323" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F317">
+  <conditionalFormatting sqref="E2:F323">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -38586,11 +38874,17 @@
     <hyperlink ref="L315" r:id="rId314"/>
     <hyperlink ref="L316" r:id="rId315"/>
     <hyperlink ref="L317" r:id="rId316"/>
+    <hyperlink ref="L318" r:id="rId317"/>
+    <hyperlink ref="L319" r:id="rId318"/>
+    <hyperlink ref="L320" r:id="rId319"/>
+    <hyperlink ref="L321" r:id="rId320"/>
+    <hyperlink ref="L322" r:id="rId321"/>
+    <hyperlink ref="L323" r:id="rId322"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId317"/>
+    <tablePart r:id="rId323"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38607,3128 +38901,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>1471</v>
+        <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>1488</v>
+        <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2202</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2501</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2497</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2498</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2200</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2499</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2168</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2495</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2501</v>
+        <v>2503</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2547</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2022</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2227</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2550</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2544</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2545</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2020</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2546</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2547</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2225</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2548</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2542</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2549</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2543</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2550</v>
+        <v>2552</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2551</v>
+        <v>2553</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2590</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2143</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2142</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2170</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2588</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2141</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2589</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2142</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2140</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2168</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2586</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2587</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2147</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2145</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2143</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2148</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2146</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2151</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2149</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2587</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2154</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2585</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2152</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10269" uniqueCount="2600">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10374" uniqueCount="2602">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 08:09 BST</t>
+    <t>Snapshot: 07 September 2026, 08:29 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4497,6 +4497,12 @@
   </si>
   <si>
     <t>Challenge identity and section navigation</t>
+  </si>
+  <si>
+    <t>Full detail shared on both surfaces: five retained URL sections, full ranked table/mobile proof details and personal row, source-session attempt access, scoped membership confirmation, searchable reviewed invitation, chronological comments with confirmed save/retained draft. challenge-detail-browser-role.log PASS2.2m all12 combinations:250yd qualifying source, draft survives sections, one saved comment, Cancel inert, exact single invitation, join/leave outcomes and source shots unchanged. Types/lint pass;390 screenshot inspected. Targeted action/permission/date/invitation tests pass. Earlier label locator failure snapshot retained draft; accessible textbox role verifies actual input.</t>
+  </si>
+  <si>
+    <t>Individual rejected-attempt ledger unavailable in current DTO (explicitly labelled qualifying aggregate); immutable final ranking snapshot not stored. Tie/low-wins/browser positive multi-player sorting, all saved-view/export controls, blocked/revoked permission semantics, actual network failures and idempotent comment retry, unsupported moderation, AT/zoom/theme/keyboard/safe-area matrix remain outstanding. No full acceptance.</t>
   </si>
   <si>
     <t>No section is omitted from the companion experience.</t>
@@ -7993,8 +7999,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L323" totalsRowShown="0">
-  <autoFilter ref="A1:L323"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L330" totalsRowShown="0">
+  <autoFilter ref="A1:L330"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8388,11 +8394,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8427,11 +8433,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>170</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -20821,16 +20827,25 @@
         <v>42</v>
       </c>
       <c r="E324" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F324" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G324" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H324" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I324" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J324" s="4" t="s">
-        <v>1492</v>
+        <v>1494</v>
       </c>
       <c r="K324" s="4" t="s">
-        <v>1493</v>
+        <v>1495</v>
       </c>
       <c r="L324" s="6" t="s">
         <v>39</v>
@@ -20838,28 +20853,37 @@
     </row>
     <row r="325" spans="1:12" ht="72" customHeight="1">
       <c r="A325" s="4" t="s">
-        <v>1494</v>
+        <v>1496</v>
       </c>
       <c r="B325" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C325" s="4" t="s">
-        <v>1495</v>
+        <v>1497</v>
       </c>
       <c r="D325" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E325" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F325" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G325" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I325" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J325" s="4" t="s">
-        <v>1496</v>
+        <v>1498</v>
       </c>
       <c r="K325" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="L325" s="6" t="s">
         <v>88</v>
@@ -20867,28 +20891,37 @@
     </row>
     <row r="326" spans="1:12" ht="72" customHeight="1">
       <c r="A326" s="4" t="s">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="B326" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C326" s="4" t="s">
-        <v>1499</v>
+        <v>1501</v>
       </c>
       <c r="D326" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E326" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F326" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G326" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H326" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I326" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J326" s="4" t="s">
-        <v>1500</v>
+        <v>1502</v>
       </c>
       <c r="K326" s="4" t="s">
-        <v>1501</v>
+        <v>1503</v>
       </c>
       <c r="L326" s="6" t="s">
         <v>159</v>
@@ -20896,28 +20929,37 @@
     </row>
     <row r="327" spans="1:12" ht="72" customHeight="1">
       <c r="A327" s="4" t="s">
-        <v>1502</v>
+        <v>1504</v>
       </c>
       <c r="B327" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C327" s="4" t="s">
-        <v>1503</v>
+        <v>1505</v>
       </c>
       <c r="D327" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E327" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F327" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G327" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I327" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J327" s="4" t="s">
-        <v>1504</v>
+        <v>1506</v>
       </c>
       <c r="K327" s="4" t="s">
-        <v>1505</v>
+        <v>1507</v>
       </c>
       <c r="L327" s="6" t="s">
         <v>103</v>
@@ -20925,28 +20967,37 @@
     </row>
     <row r="328" spans="1:12" ht="72" customHeight="1">
       <c r="A328" s="4" t="s">
-        <v>1506</v>
+        <v>1508</v>
       </c>
       <c r="B328" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C328" s="4" t="s">
-        <v>1507</v>
+        <v>1509</v>
       </c>
       <c r="D328" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E328" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F328" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G328" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I328" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J328" s="4" t="s">
-        <v>1508</v>
+        <v>1510</v>
       </c>
       <c r="K328" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="L328" s="6" t="s">
         <v>518</v>
@@ -20954,28 +21005,37 @@
     </row>
     <row r="329" spans="1:12" ht="72" customHeight="1">
       <c r="A329" s="4" t="s">
-        <v>1509</v>
+        <v>1511</v>
       </c>
       <c r="B329" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C329" s="4" t="s">
-        <v>1510</v>
+        <v>1512</v>
       </c>
       <c r="D329" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E329" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F329" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G329" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I329" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J329" s="4" t="s">
-        <v>1511</v>
+        <v>1513</v>
       </c>
       <c r="K329" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="L329" s="6" t="s">
         <v>88</v>
@@ -20983,28 +21043,37 @@
     </row>
     <row r="330" spans="1:12" ht="72" customHeight="1">
       <c r="A330" s="4" t="s">
-        <v>1512</v>
+        <v>1514</v>
       </c>
       <c r="B330" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C330" s="4" t="s">
-        <v>1513</v>
+        <v>1515</v>
       </c>
       <c r="D330" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E330" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F330" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G330" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H330" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I330" s="4" t="s">
+        <v>1493</v>
       </c>
       <c r="J330" s="4" t="s">
-        <v>1514</v>
+        <v>1516</v>
       </c>
       <c r="K330" s="4" t="s">
-        <v>1515</v>
+        <v>1517</v>
       </c>
       <c r="L330" s="6" t="s">
         <v>625</v>
@@ -21012,13 +21081,13 @@
     </row>
     <row r="331" spans="1:12" ht="72" customHeight="1">
       <c r="A331" s="4" t="s">
-        <v>1516</v>
+        <v>1518</v>
       </c>
       <c r="B331" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C331" s="4" t="s">
-        <v>1518</v>
+        <v>1520</v>
       </c>
       <c r="D331" s="4" t="s">
         <v>42</v>
@@ -21030,10 +21099,10 @@
         <v>9</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1519</v>
+        <v>1521</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -21041,13 +21110,13 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="B332" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C332" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="D332" s="4" t="s">
         <v>42</v>
@@ -21059,10 +21128,10 @@
         <v>9</v>
       </c>
       <c r="J332" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="K332" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -21070,13 +21139,13 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1524</v>
+        <v>1526</v>
       </c>
       <c r="B333" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1525</v>
+        <v>1527</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
@@ -21088,10 +21157,10 @@
         <v>9</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -21099,13 +21168,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -21117,10 +21186,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -21128,13 +21197,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -21146,10 +21215,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21157,13 +21226,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -21175,10 +21244,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21186,13 +21255,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21204,10 +21273,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21215,13 +21284,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21233,10 +21302,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21244,13 +21313,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21262,10 +21331,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21273,13 +21342,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21291,10 +21360,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21302,13 +21371,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21320,10 +21389,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21331,13 +21400,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21349,10 +21418,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21360,13 +21429,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21378,10 +21447,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21389,13 +21458,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21407,10 +21476,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21418,13 +21487,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21436,10 +21505,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21447,13 +21516,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21465,10 +21534,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21476,13 +21545,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21494,10 +21563,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21505,13 +21574,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21523,10 +21592,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21534,13 +21603,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21552,10 +21621,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21563,13 +21632,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21581,10 +21650,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21592,13 +21661,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21610,24 +21679,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21639,10 +21708,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21650,13 +21719,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21668,10 +21737,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21679,13 +21748,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21697,10 +21766,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21708,13 +21777,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21726,10 +21795,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21737,13 +21806,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21755,10 +21824,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21766,13 +21835,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21784,10 +21853,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21795,13 +21864,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21813,10 +21882,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21824,13 +21893,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21842,10 +21911,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21853,13 +21922,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21871,10 +21940,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21882,13 +21951,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21900,10 +21969,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21911,13 +21980,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21929,10 +21998,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -21940,13 +22009,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -21958,10 +22027,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -21969,13 +22038,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -21987,10 +22056,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -21998,13 +22067,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22016,10 +22085,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22027,13 +22096,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22045,10 +22114,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22056,13 +22125,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22074,10 +22143,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22085,13 +22154,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22103,10 +22172,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22114,13 +22183,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22132,10 +22201,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22143,13 +22212,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22161,10 +22230,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22172,13 +22241,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22190,10 +22259,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22201,13 +22270,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22219,10 +22288,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22230,13 +22299,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22248,10 +22317,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22259,13 +22328,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22277,10 +22346,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22288,13 +22357,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22306,10 +22375,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22317,13 +22386,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22335,10 +22404,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22346,13 +22415,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22364,10 +22433,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22375,13 +22444,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22393,10 +22462,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22404,13 +22473,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22422,10 +22491,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22433,13 +22502,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22451,10 +22520,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22462,13 +22531,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22480,10 +22549,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22491,13 +22560,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22509,24 +22578,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22538,10 +22607,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22549,13 +22618,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22567,10 +22636,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22578,13 +22647,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22596,10 +22665,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22607,13 +22676,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22625,10 +22694,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22636,13 +22705,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22654,10 +22723,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22665,13 +22734,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22683,10 +22752,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22694,13 +22763,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22712,10 +22781,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22723,13 +22792,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22741,24 +22810,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22770,10 +22839,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22781,13 +22850,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22799,24 +22868,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22828,10 +22897,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22839,13 +22908,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22857,10 +22926,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22868,13 +22937,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22886,24 +22955,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22915,10 +22984,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22926,13 +22995,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -22944,10 +23013,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -22955,13 +23024,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -22973,10 +23042,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -22984,13 +23053,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23002,10 +23071,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23013,13 +23082,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23031,10 +23100,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23042,13 +23111,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23060,10 +23129,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23071,13 +23140,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23089,10 +23158,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23100,13 +23169,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23118,24 +23187,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23147,10 +23216,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23158,13 +23227,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23176,10 +23245,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23187,13 +23256,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23205,10 +23274,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23216,13 +23285,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23234,10 +23303,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23245,13 +23314,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23263,10 +23332,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23274,13 +23343,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23292,10 +23361,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23303,13 +23372,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23321,10 +23390,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23332,13 +23401,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23350,24 +23419,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23379,10 +23448,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23390,13 +23459,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23408,10 +23477,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23419,13 +23488,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23437,10 +23506,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23448,13 +23517,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23466,10 +23535,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23477,13 +23546,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23495,10 +23564,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23506,13 +23575,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23524,10 +23593,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23535,13 +23604,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23553,10 +23622,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23564,13 +23633,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23582,10 +23651,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23593,13 +23662,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23611,10 +23680,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23622,13 +23691,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23640,10 +23709,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23651,13 +23720,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23669,10 +23738,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23680,13 +23749,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23698,10 +23767,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23709,13 +23778,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23727,10 +23796,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23738,13 +23807,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23756,10 +23825,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23767,13 +23836,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23785,10 +23854,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23796,13 +23865,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23814,10 +23883,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23825,13 +23894,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23843,10 +23912,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23854,13 +23923,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23872,10 +23941,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23883,13 +23952,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23901,10 +23970,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23912,13 +23981,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23930,10 +23999,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -23941,13 +24010,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -23959,10 +24028,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -23970,13 +24039,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -23988,10 +24057,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -23999,13 +24068,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24017,10 +24086,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24028,13 +24097,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24046,10 +24115,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24057,13 +24126,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24075,10 +24144,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24086,13 +24155,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24104,10 +24173,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24115,13 +24184,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24133,10 +24202,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24144,13 +24213,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24162,10 +24231,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24173,13 +24242,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24191,10 +24260,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24202,13 +24271,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24220,10 +24289,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24231,13 +24300,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24249,10 +24318,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24260,13 +24329,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24278,10 +24347,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24289,13 +24358,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24307,10 +24376,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24318,13 +24387,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24336,10 +24405,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24347,13 +24416,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24365,10 +24434,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24376,13 +24445,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24394,10 +24463,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24405,13 +24474,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24423,10 +24492,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24434,13 +24503,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24452,10 +24521,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24463,13 +24532,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24481,10 +24550,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24492,13 +24561,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24510,10 +24579,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24521,13 +24590,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24539,10 +24608,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24550,13 +24619,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24568,10 +24637,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24579,13 +24648,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24597,10 +24666,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24608,13 +24677,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24626,10 +24695,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24637,13 +24706,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24655,24 +24724,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24684,10 +24753,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24695,13 +24764,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24713,10 +24782,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24724,13 +24793,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24742,10 +24811,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24753,13 +24822,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24771,10 +24840,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24782,13 +24851,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24800,10 +24869,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24811,13 +24880,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24829,10 +24898,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24840,13 +24909,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24858,10 +24927,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24869,13 +24938,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24887,10 +24956,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24898,13 +24967,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24916,10 +24985,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24927,13 +24996,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -24945,10 +25014,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -24956,13 +25025,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -24974,10 +25043,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -24985,13 +25054,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25003,10 +25072,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25014,13 +25083,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25032,10 +25101,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25043,13 +25112,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25061,10 +25130,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25072,13 +25141,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25090,10 +25159,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25101,13 +25170,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25119,10 +25188,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25130,13 +25199,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25148,10 +25217,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25159,13 +25228,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25177,10 +25246,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25188,13 +25257,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25206,10 +25275,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25217,13 +25286,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25235,10 +25304,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25246,13 +25315,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25264,10 +25333,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25275,13 +25344,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25293,10 +25362,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25304,13 +25373,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25322,10 +25391,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25333,13 +25402,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25351,10 +25420,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25362,13 +25431,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25380,10 +25449,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25391,13 +25460,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25409,10 +25478,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25420,13 +25489,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25438,10 +25507,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25449,13 +25518,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25467,10 +25536,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25478,13 +25547,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25496,10 +25565,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25507,13 +25576,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25525,10 +25594,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25536,13 +25605,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25554,10 +25623,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25565,13 +25634,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25583,10 +25652,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25594,13 +25663,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25612,10 +25681,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25623,13 +25692,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25641,10 +25710,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25652,13 +25721,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25670,10 +25739,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25681,13 +25750,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25699,10 +25768,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25710,13 +25779,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25728,10 +25797,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26262,7 +26331,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L323"/>
+  <dimension ref="A1:L330"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -38539,8 +38608,274 @@
         <v>81</v>
       </c>
     </row>
+    <row r="324" spans="1:12" ht="72" customHeight="1">
+      <c r="A324" s="4" t="s">
+        <v>1489</v>
+      </c>
+      <c r="B324" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C324" s="4" t="s">
+        <v>1491</v>
+      </c>
+      <c r="D324" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E324" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F324" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G324" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H324" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I324" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J324" s="4" t="s">
+        <v>1494</v>
+      </c>
+      <c r="K324" s="4" t="s">
+        <v>1495</v>
+      </c>
+      <c r="L324" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="325" spans="1:12" ht="72" customHeight="1">
+      <c r="A325" s="4" t="s">
+        <v>1496</v>
+      </c>
+      <c r="B325" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C325" s="4" t="s">
+        <v>1497</v>
+      </c>
+      <c r="D325" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E325" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F325" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G325" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H325" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I325" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J325" s="4" t="s">
+        <v>1498</v>
+      </c>
+      <c r="K325" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L325" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="326" spans="1:12" ht="72" customHeight="1">
+      <c r="A326" s="4" t="s">
+        <v>1500</v>
+      </c>
+      <c r="B326" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C326" s="4" t="s">
+        <v>1501</v>
+      </c>
+      <c r="D326" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E326" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F326" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G326" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H326" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I326" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J326" s="4" t="s">
+        <v>1502</v>
+      </c>
+      <c r="K326" s="4" t="s">
+        <v>1503</v>
+      </c>
+      <c r="L326" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="327" spans="1:12" ht="72" customHeight="1">
+      <c r="A327" s="4" t="s">
+        <v>1504</v>
+      </c>
+      <c r="B327" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C327" s="4" t="s">
+        <v>1505</v>
+      </c>
+      <c r="D327" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E327" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F327" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G327" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H327" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I327" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J327" s="4" t="s">
+        <v>1506</v>
+      </c>
+      <c r="K327" s="4" t="s">
+        <v>1507</v>
+      </c>
+      <c r="L327" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="328" spans="1:12" ht="72" customHeight="1">
+      <c r="A328" s="4" t="s">
+        <v>1508</v>
+      </c>
+      <c r="B328" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C328" s="4" t="s">
+        <v>1509</v>
+      </c>
+      <c r="D328" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E328" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F328" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G328" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H328" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I328" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J328" s="4" t="s">
+        <v>1510</v>
+      </c>
+      <c r="K328" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L328" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="329" spans="1:12" ht="72" customHeight="1">
+      <c r="A329" s="4" t="s">
+        <v>1511</v>
+      </c>
+      <c r="B329" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C329" s="4" t="s">
+        <v>1512</v>
+      </c>
+      <c r="D329" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E329" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F329" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G329" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H329" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I329" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J329" s="4" t="s">
+        <v>1513</v>
+      </c>
+      <c r="K329" s="4" t="s">
+        <v>1499</v>
+      </c>
+      <c r="L329" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="330" spans="1:12" ht="72" customHeight="1">
+      <c r="A330" s="4" t="s">
+        <v>1514</v>
+      </c>
+      <c r="B330" s="4" t="s">
+        <v>1490</v>
+      </c>
+      <c r="C330" s="4" t="s">
+        <v>1515</v>
+      </c>
+      <c r="D330" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E330" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F330" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G330" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="H330" s="4" t="s">
+        <v>1492</v>
+      </c>
+      <c r="I330" s="4" t="s">
+        <v>1493</v>
+      </c>
+      <c r="J330" s="4" t="s">
+        <v>1516</v>
+      </c>
+      <c r="K330" s="4" t="s">
+        <v>1517</v>
+      </c>
+      <c r="L330" s="6" t="s">
+        <v>625</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F323">
+  <conditionalFormatting sqref="E2:F330">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -38880,11 +39215,18 @@
     <hyperlink ref="L321" r:id="rId320"/>
     <hyperlink ref="L322" r:id="rId321"/>
     <hyperlink ref="L323" r:id="rId322"/>
+    <hyperlink ref="L324" r:id="rId323"/>
+    <hyperlink ref="L325" r:id="rId324"/>
+    <hyperlink ref="L326" r:id="rId325"/>
+    <hyperlink ref="L327" r:id="rId326"/>
+    <hyperlink ref="L328" r:id="rId327"/>
+    <hyperlink ref="L329" r:id="rId328"/>
+    <hyperlink ref="L330" r:id="rId329"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId323"/>
+    <tablePart r:id="rId330"/>
   </tableParts>
 </worksheet>
 </file>
@@ -38901,3128 +39243,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>1497</v>
+        <v>1499</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>1517</v>
+        <v>1519</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1520</v>
+        <v>1522</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2502</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2503</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2172</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2499</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2500</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2202</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2501</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2170</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2497</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2502</v>
+        <v>2504</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2503</v>
+        <v>2505</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2549</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2024</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2550</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2229</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2546</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2547</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2022</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2548</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2549</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2227</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2550</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2544</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2551</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2545</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2552</v>
+        <v>2554</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2553</v>
+        <v>2555</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2592</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2145</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2593</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2146</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2144</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2172</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2590</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2143</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2591</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2144</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2142</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2170</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2588</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2589</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2592</v>
+        <v>2594</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2593</v>
+        <v>2595</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2147</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2145</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2150</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2148</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2153</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2151</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2589</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2156</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2587</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2154</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10374" uniqueCount="2602">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10419" uniqueCount="2604">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 08:29 BST</t>
+    <t>Snapshot: 07 September 2026, 08:40 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4584,6 +4584,12 @@
   </si>
   <si>
     <t>Event status tabs and course scope</t>
+  </si>
+  <si>
+    <t>Shared full-width tournament index: counted controlled URL statuses, course/search/order filters, desktop full table and full mobile event/proof context. tournaments-browser-alias.log PASS1.3m both surfaces x6sizes: alias retains exactcourseId, selectedcounts1/0, cancelled notactiveentry, upcoming reload, search empty/recovery/nameorder, mobilefullfields, component and document bounds. Types/lint pass;390 screenshot inspected. Fixed companion alias desktop gate and intrinsic selector overflow. Earlier strict test locators corrected without hiding app states.</t>
+  </si>
+  <si>
+    <t>Large histories beyond latest80 source limit, entered/result positive fixture, unknowncourse and clear/backforward edge cases, all errors/loading/AT/zoom/theme/nativekeyboard/safearea remain outstanding. Backend tournament transaction/date/entry guard changes are present and tested but reserved for coordinated P61 commit. No full acceptance.</t>
   </si>
   <si>
     <t>The course-tournaments alias opens the correctly filtered event list.</t>
@@ -7999,8 +8005,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L330" totalsRowShown="0">
-  <autoFilter ref="A1:L330"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L333" totalsRowShown="0">
+  <autoFilter ref="A1:L333"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8394,11 +8400,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8433,11 +8439,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -21093,16 +21099,25 @@
         <v>42</v>
       </c>
       <c r="E331" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F331" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G331" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I331" s="4" t="s">
+        <v>1522</v>
       </c>
       <c r="J331" s="4" t="s">
-        <v>1521</v>
+        <v>1523</v>
       </c>
       <c r="K331" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="L331" s="6" t="s">
         <v>141</v>
@@ -21110,28 +21125,37 @@
     </row>
     <row r="332" spans="1:12" ht="72" customHeight="1">
       <c r="A332" s="4" t="s">
-        <v>1523</v>
+        <v>1525</v>
       </c>
       <c r="B332" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C332" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G332" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H332" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I332" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J332" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="K332" s="4" t="s">
         <v>1524</v>
-      </c>
-      <c r="D332" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="E332" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F332" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J332" s="4" t="s">
-        <v>1525</v>
-      </c>
-      <c r="K332" s="4" t="s">
-        <v>1522</v>
       </c>
       <c r="L332" s="6" t="s">
         <v>88</v>
@@ -21139,28 +21163,37 @@
     </row>
     <row r="333" spans="1:12" ht="72" customHeight="1">
       <c r="A333" s="4" t="s">
-        <v>1526</v>
+        <v>1528</v>
       </c>
       <c r="B333" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C333" s="4" t="s">
-        <v>1527</v>
+        <v>1529</v>
       </c>
       <c r="D333" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E333" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F333" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G333" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I333" s="4" t="s">
+        <v>1522</v>
       </c>
       <c r="J333" s="4" t="s">
-        <v>1528</v>
+        <v>1530</v>
       </c>
       <c r="K333" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="L333" s="6" t="s">
         <v>159</v>
@@ -21168,13 +21201,13 @@
     </row>
     <row r="334" spans="1:12" ht="72" customHeight="1">
       <c r="A334" s="4" t="s">
-        <v>1529</v>
+        <v>1531</v>
       </c>
       <c r="B334" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C334" s="4" t="s">
-        <v>1531</v>
+        <v>1533</v>
       </c>
       <c r="D334" s="4" t="s">
         <v>42</v>
@@ -21186,10 +21219,10 @@
         <v>9</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1532</v>
+        <v>1534</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -21197,13 +21230,13 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1534</v>
+        <v>1536</v>
       </c>
       <c r="B335" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1535</v>
+        <v>1537</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
@@ -21215,10 +21248,10 @@
         <v>9</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1536</v>
+        <v>1538</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1537</v>
+        <v>1539</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21226,13 +21259,13 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1538</v>
+        <v>1540</v>
       </c>
       <c r="B336" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1539</v>
+        <v>1541</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
@@ -21244,10 +21277,10 @@
         <v>9</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1540</v>
+        <v>1542</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1541</v>
+        <v>1543</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21255,13 +21288,13 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1542</v>
+        <v>1544</v>
       </c>
       <c r="B337" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1543</v>
+        <v>1545</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
@@ -21273,10 +21306,10 @@
         <v>9</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1544</v>
+        <v>1546</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21284,13 +21317,13 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="B338" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1546</v>
+        <v>1548</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
@@ -21302,10 +21335,10 @@
         <v>9</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1547</v>
+        <v>1549</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21313,13 +21346,13 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1548</v>
+        <v>1550</v>
       </c>
       <c r="B339" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1549</v>
+        <v>1551</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
@@ -21331,10 +21364,10 @@
         <v>9</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1550</v>
+        <v>1552</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1551</v>
+        <v>1553</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21342,13 +21375,13 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1552</v>
+        <v>1554</v>
       </c>
       <c r="B340" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1553</v>
+        <v>1555</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
@@ -21360,10 +21393,10 @@
         <v>9</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1554</v>
+        <v>1556</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1555</v>
+        <v>1557</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21371,13 +21404,13 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1556</v>
+        <v>1558</v>
       </c>
       <c r="B341" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1557</v>
+        <v>1559</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
@@ -21389,10 +21422,10 @@
         <v>9</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1558</v>
+        <v>1560</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1559</v>
+        <v>1561</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21400,13 +21433,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1560</v>
+        <v>1562</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1562</v>
+        <v>1564</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21418,10 +21451,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1563</v>
+        <v>1565</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1564</v>
+        <v>1566</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21429,13 +21462,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1565</v>
+        <v>1567</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1566</v>
+        <v>1568</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21447,10 +21480,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1567</v>
+        <v>1569</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1568</v>
+        <v>1570</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21458,13 +21491,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1569</v>
+        <v>1571</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1570</v>
+        <v>1572</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21476,10 +21509,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1571</v>
+        <v>1573</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21487,13 +21520,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1573</v>
+        <v>1575</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1574</v>
+        <v>1576</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21505,10 +21538,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
-        <v>1575</v>
+        <v>1577</v>
       </c>
       <c r="K345" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21516,13 +21549,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1576</v>
+        <v>1578</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1577</v>
+        <v>1579</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21534,10 +21567,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1578</v>
+        <v>1580</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21545,13 +21578,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1579</v>
+        <v>1581</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1581</v>
+        <v>1583</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21563,10 +21596,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1582</v>
+        <v>1584</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21574,13 +21607,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1584</v>
+        <v>1586</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1585</v>
+        <v>1587</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21592,10 +21625,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1586</v>
+        <v>1588</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1587</v>
+        <v>1589</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21603,13 +21636,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1588</v>
+        <v>1590</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1589</v>
+        <v>1591</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21621,10 +21654,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1590</v>
+        <v>1592</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21632,13 +21665,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1591</v>
+        <v>1593</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1592</v>
+        <v>1594</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21650,10 +21683,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1593</v>
+        <v>1595</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1594</v>
+        <v>1596</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21661,13 +21694,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1595</v>
+        <v>1597</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1596</v>
+        <v>1598</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21679,24 +21712,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1597</v>
+        <v>1599</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1583</v>
+        <v>1585</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1598</v>
+        <v>1600</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1599</v>
+        <v>1601</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1600</v>
+        <v>1602</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21708,10 +21741,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1601</v>
+        <v>1603</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21719,13 +21752,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1603</v>
+        <v>1605</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1605</v>
+        <v>1607</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21737,10 +21770,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1606</v>
+        <v>1608</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1607</v>
+        <v>1609</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21748,13 +21781,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1608</v>
+        <v>1610</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1609</v>
+        <v>1611</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21766,10 +21799,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1610</v>
+        <v>1612</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1611</v>
+        <v>1613</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21777,13 +21810,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1612</v>
+        <v>1614</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1613</v>
+        <v>1615</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21795,10 +21828,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1614</v>
+        <v>1616</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21806,13 +21839,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1616</v>
+        <v>1618</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1617</v>
+        <v>1619</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21824,10 +21857,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1618</v>
+        <v>1620</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1619</v>
+        <v>1621</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21835,13 +21868,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1620</v>
+        <v>1622</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1622</v>
+        <v>1624</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21853,10 +21886,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1623</v>
+        <v>1625</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1624</v>
+        <v>1626</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21864,13 +21897,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1625</v>
+        <v>1627</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1626</v>
+        <v>1628</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21882,10 +21915,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1627</v>
+        <v>1629</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21893,13 +21926,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1629</v>
+        <v>1631</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1630</v>
+        <v>1632</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21911,10 +21944,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
-        <v>1631</v>
+        <v>1633</v>
       </c>
       <c r="K359" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21922,13 +21955,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1632</v>
+        <v>1634</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1633</v>
+        <v>1635</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21940,10 +21973,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1634</v>
+        <v>1636</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1635</v>
+        <v>1637</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21951,13 +21984,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1636</v>
+        <v>1638</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1638</v>
+        <v>1640</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -21969,10 +22002,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1639</v>
+        <v>1641</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1640</v>
+        <v>1642</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -21980,13 +22013,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1641</v>
+        <v>1643</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1642</v>
+        <v>1644</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -21998,10 +22031,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1643</v>
+        <v>1645</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -22009,13 +22042,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1645</v>
+        <v>1647</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1646</v>
+        <v>1648</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -22027,10 +22060,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
-        <v>1647</v>
+        <v>1649</v>
       </c>
       <c r="K363" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -22038,13 +22071,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1648</v>
+        <v>1650</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1649</v>
+        <v>1651</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -22056,10 +22089,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1650</v>
+        <v>1652</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -22067,13 +22100,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1651</v>
+        <v>1653</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1652</v>
+        <v>1654</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22085,10 +22118,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1653</v>
+        <v>1655</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1654</v>
+        <v>1656</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22096,13 +22129,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1655</v>
+        <v>1657</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1656</v>
+        <v>1658</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22114,10 +22147,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1657</v>
+        <v>1659</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1658</v>
+        <v>1660</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22125,13 +22158,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1659</v>
+        <v>1661</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1661</v>
+        <v>1663</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22143,10 +22176,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1662</v>
+        <v>1664</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1663</v>
+        <v>1665</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22154,13 +22187,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1664</v>
+        <v>1666</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1665</v>
+        <v>1667</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22172,10 +22205,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1666</v>
+        <v>1668</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1667</v>
+        <v>1669</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22183,13 +22216,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1668</v>
+        <v>1670</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1669</v>
+        <v>1671</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22201,10 +22234,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1670</v>
+        <v>1672</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1671</v>
+        <v>1673</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22212,13 +22245,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1672</v>
+        <v>1674</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1673</v>
+        <v>1675</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22230,10 +22263,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1674</v>
+        <v>1676</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22241,13 +22274,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1676</v>
+        <v>1678</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1678</v>
+        <v>1680</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22259,10 +22292,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1679</v>
+        <v>1681</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22270,13 +22303,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1681</v>
+        <v>1683</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1682</v>
+        <v>1684</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22288,10 +22321,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1683</v>
+        <v>1685</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1684</v>
+        <v>1686</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22299,13 +22332,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1685</v>
+        <v>1687</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1686</v>
+        <v>1688</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22317,10 +22350,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1687</v>
+        <v>1689</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22328,13 +22361,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1688</v>
+        <v>1690</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1689</v>
+        <v>1691</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22346,10 +22379,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1690</v>
+        <v>1692</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22357,13 +22390,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1691</v>
+        <v>1693</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1693</v>
+        <v>1695</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22375,10 +22408,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1694</v>
+        <v>1696</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22386,13 +22419,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1696</v>
+        <v>1698</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1697</v>
+        <v>1699</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22404,10 +22437,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1698</v>
+        <v>1700</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1699</v>
+        <v>1701</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22415,13 +22448,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1700</v>
+        <v>1702</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1701</v>
+        <v>1703</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22433,10 +22466,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1702</v>
+        <v>1704</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22444,13 +22477,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1703</v>
+        <v>1705</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1704</v>
+        <v>1706</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22462,10 +22495,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1705</v>
+        <v>1707</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22473,13 +22506,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1706</v>
+        <v>1708</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1707</v>
+        <v>1709</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22491,10 +22524,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1708</v>
+        <v>1710</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22502,13 +22535,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1709</v>
+        <v>1711</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1710</v>
+        <v>1712</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22520,10 +22553,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1711</v>
+        <v>1713</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1712</v>
+        <v>1714</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22531,13 +22564,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1713</v>
+        <v>1715</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1714</v>
+        <v>1716</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22549,10 +22582,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1715</v>
+        <v>1717</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1716</v>
+        <v>1718</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22560,13 +22593,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1718</v>
+        <v>1720</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22578,24 +22611,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1719</v>
+        <v>1721</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1721</v>
+        <v>1723</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1722</v>
+        <v>1724</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22607,10 +22640,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1723</v>
+        <v>1725</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1724</v>
+        <v>1726</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22618,13 +22651,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1725</v>
+        <v>1727</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22636,10 +22669,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1728</v>
+        <v>1730</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1729</v>
+        <v>1731</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22647,13 +22680,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1730</v>
+        <v>1732</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1731</v>
+        <v>1733</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22665,10 +22698,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1732</v>
+        <v>1734</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22676,13 +22709,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1734</v>
+        <v>1736</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1735</v>
+        <v>1737</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22694,10 +22727,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
-        <v>1736</v>
+        <v>1738</v>
       </c>
       <c r="K386" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22705,13 +22738,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1737</v>
+        <v>1739</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1738</v>
+        <v>1740</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22723,10 +22756,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1739</v>
+        <v>1741</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1740</v>
+        <v>1742</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22734,13 +22767,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1741</v>
+        <v>1743</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1743</v>
+        <v>1745</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22752,10 +22785,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1744</v>
+        <v>1746</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22763,13 +22796,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1746</v>
+        <v>1748</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1747</v>
+        <v>1749</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22781,10 +22814,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
-        <v>1748</v>
+        <v>1750</v>
       </c>
       <c r="K389" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22792,13 +22825,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1749</v>
+        <v>1751</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1750</v>
+        <v>1752</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22810,24 +22843,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1751</v>
+        <v>1753</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1752</v>
+        <v>1754</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1753</v>
+        <v>1755</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22839,10 +22872,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1754</v>
+        <v>1756</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1755</v>
+        <v>1757</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22850,13 +22883,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1756</v>
+        <v>1758</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1757</v>
+        <v>1759</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22868,24 +22901,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1758</v>
+        <v>1760</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1759</v>
+        <v>1761</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1760</v>
+        <v>1762</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22897,10 +22930,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1761</v>
+        <v>1763</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22908,13 +22941,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1762</v>
+        <v>1764</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1763</v>
+        <v>1765</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22926,10 +22959,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1764</v>
+        <v>1766</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1765</v>
+        <v>1767</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22937,13 +22970,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1766</v>
+        <v>1768</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1767</v>
+        <v>1769</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22955,24 +22988,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1768</v>
+        <v>1770</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1769</v>
+        <v>1771</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1770</v>
+        <v>1772</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -22984,10 +23017,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1771</v>
+        <v>1773</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1772</v>
+        <v>1774</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -22995,13 +23028,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1773</v>
+        <v>1775</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1774</v>
+        <v>1776</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -23013,10 +23046,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1775</v>
+        <v>1777</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1776</v>
+        <v>1778</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -23024,13 +23057,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1777</v>
+        <v>1779</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1778</v>
+        <v>1780</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -23042,10 +23075,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1779</v>
+        <v>1781</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -23053,13 +23086,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1780</v>
+        <v>1782</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1781</v>
+        <v>1783</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23071,10 +23104,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1782</v>
+        <v>1784</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1783</v>
+        <v>1785</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23082,13 +23115,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1784</v>
+        <v>1786</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1785</v>
+        <v>1787</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23100,10 +23133,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1786</v>
+        <v>1788</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23111,13 +23144,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1788</v>
+        <v>1790</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1789</v>
+        <v>1791</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23129,10 +23162,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
-        <v>1790</v>
+        <v>1792</v>
       </c>
       <c r="K401" s="4" t="s">
-        <v>1787</v>
+        <v>1789</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23140,13 +23173,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1791</v>
+        <v>1793</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1793</v>
+        <v>1795</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23158,10 +23191,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1794</v>
+        <v>1796</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1795</v>
+        <v>1797</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23169,13 +23202,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1796</v>
+        <v>1798</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1797</v>
+        <v>1799</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23187,24 +23220,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1798</v>
+        <v>1800</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1799</v>
+        <v>1801</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1720</v>
+        <v>1722</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1800</v>
+        <v>1802</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1801</v>
+        <v>1803</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23216,10 +23249,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1802</v>
+        <v>1804</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1803</v>
+        <v>1805</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23227,13 +23260,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1804</v>
+        <v>1806</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1806</v>
+        <v>1808</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23245,10 +23278,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1807</v>
+        <v>1809</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1808</v>
+        <v>1810</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23256,13 +23289,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1809</v>
+        <v>1811</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1810</v>
+        <v>1812</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23274,10 +23307,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1811</v>
+        <v>1813</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1812</v>
+        <v>1814</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23285,13 +23318,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1813</v>
+        <v>1815</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1815</v>
+        <v>1817</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23303,10 +23336,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1816</v>
+        <v>1818</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23314,13 +23347,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1818</v>
+        <v>1820</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1819</v>
+        <v>1821</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23332,10 +23365,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
-        <v>1820</v>
+        <v>1822</v>
       </c>
       <c r="K408" s="4" t="s">
-        <v>1817</v>
+        <v>1819</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23343,13 +23376,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1821</v>
+        <v>1823</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1822</v>
+        <v>1824</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23361,10 +23394,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1823</v>
+        <v>1825</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1824</v>
+        <v>1826</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23372,13 +23405,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1825</v>
+        <v>1827</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1827</v>
+        <v>1829</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23390,10 +23423,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1828</v>
+        <v>1830</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23401,13 +23434,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1830</v>
+        <v>1832</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1831</v>
+        <v>1833</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23419,24 +23452,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1832</v>
+        <v>1834</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1833</v>
+        <v>1835</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1835</v>
+        <v>1837</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1836</v>
+        <v>1838</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23448,10 +23481,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1837</v>
+        <v>1839</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23459,13 +23492,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1838</v>
+        <v>1840</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1839</v>
+        <v>1841</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23477,10 +23510,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1840</v>
+        <v>1842</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1841</v>
+        <v>1843</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23488,13 +23521,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1842</v>
+        <v>1844</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1843</v>
+        <v>1845</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23506,10 +23539,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1844</v>
+        <v>1846</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23517,13 +23550,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1845</v>
+        <v>1847</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1846</v>
+        <v>1848</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23535,10 +23568,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1847</v>
+        <v>1849</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23546,13 +23579,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1848</v>
+        <v>1850</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1850</v>
+        <v>1852</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23564,10 +23597,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1851</v>
+        <v>1853</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1852</v>
+        <v>1854</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23575,13 +23608,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1853</v>
+        <v>1855</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1854</v>
+        <v>1856</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23593,10 +23626,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1855</v>
+        <v>1857</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23604,13 +23637,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1857</v>
+        <v>1859</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1858</v>
+        <v>1860</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23622,10 +23655,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
-        <v>1859</v>
+        <v>1861</v>
       </c>
       <c r="K418" s="4" t="s">
-        <v>1856</v>
+        <v>1858</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23633,13 +23666,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1860</v>
+        <v>1862</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1861</v>
+        <v>1863</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23651,10 +23684,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1862</v>
+        <v>1864</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1863</v>
+        <v>1865</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23662,13 +23695,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1864</v>
+        <v>1866</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1865</v>
+        <v>1867</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23680,10 +23713,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1866</v>
+        <v>1868</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1867</v>
+        <v>1869</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23691,13 +23724,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1868</v>
+        <v>1870</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1870</v>
+        <v>1872</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23709,10 +23742,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1871</v>
+        <v>1873</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1872</v>
+        <v>1874</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23720,13 +23753,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1873</v>
+        <v>1875</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1874</v>
+        <v>1876</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23738,10 +23771,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1875</v>
+        <v>1877</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1876</v>
+        <v>1878</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23749,13 +23782,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1877</v>
+        <v>1879</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1878</v>
+        <v>1880</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23767,10 +23800,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1879</v>
+        <v>1881</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1880</v>
+        <v>1882</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23778,13 +23811,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1881</v>
+        <v>1883</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1882</v>
+        <v>1884</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23796,10 +23829,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1883</v>
+        <v>1885</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1884</v>
+        <v>1886</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23807,13 +23840,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1885</v>
+        <v>1887</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1887</v>
+        <v>1889</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23825,10 +23858,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1888</v>
+        <v>1890</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1889</v>
+        <v>1891</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23836,13 +23869,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1890</v>
+        <v>1892</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1891</v>
+        <v>1893</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23854,10 +23887,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23865,13 +23898,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1894</v>
+        <v>1896</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1895</v>
+        <v>1897</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23883,10 +23916,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
-        <v>1896</v>
+        <v>1898</v>
       </c>
       <c r="K427" s="4" t="s">
-        <v>1893</v>
+        <v>1895</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23894,13 +23927,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1897</v>
+        <v>1899</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1898</v>
+        <v>1900</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23912,10 +23945,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1899</v>
+        <v>1901</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1900</v>
+        <v>1902</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23923,13 +23956,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1901</v>
+        <v>1903</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1902</v>
+        <v>1904</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23941,10 +23974,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1903</v>
+        <v>1905</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1904</v>
+        <v>1906</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23952,13 +23985,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1905</v>
+        <v>1907</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1907</v>
+        <v>1909</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -23970,10 +24003,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1908</v>
+        <v>1910</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1909</v>
+        <v>1911</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -23981,13 +24014,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1910</v>
+        <v>1912</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1911</v>
+        <v>1913</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -23999,10 +24032,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1912</v>
+        <v>1914</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1913</v>
+        <v>1915</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -24010,13 +24043,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1914</v>
+        <v>1916</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1915</v>
+        <v>1917</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -24028,10 +24061,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1916</v>
+        <v>1918</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1917</v>
+        <v>1919</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -24039,13 +24072,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1918</v>
+        <v>1920</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1919</v>
+        <v>1921</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -24057,10 +24090,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1920</v>
+        <v>1922</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1921</v>
+        <v>1923</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -24068,13 +24101,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1922</v>
+        <v>1924</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1924</v>
+        <v>1926</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24086,10 +24119,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1925</v>
+        <v>1927</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1926</v>
+        <v>1928</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24097,13 +24130,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1927</v>
+        <v>1929</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1928</v>
+        <v>1930</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24115,10 +24148,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1929</v>
+        <v>1931</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24126,13 +24159,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1931</v>
+        <v>1933</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1932</v>
+        <v>1934</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24144,10 +24177,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1933</v>
+        <v>1935</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1934</v>
+        <v>1936</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24155,13 +24188,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1935</v>
+        <v>1937</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1936</v>
+        <v>1938</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24173,10 +24206,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1930</v>
+        <v>1932</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24184,13 +24217,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1938</v>
+        <v>1940</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1940</v>
+        <v>1942</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24202,10 +24235,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1941</v>
+        <v>1943</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24213,13 +24246,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1943</v>
+        <v>1945</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1944</v>
+        <v>1946</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24231,10 +24264,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
-        <v>1945</v>
+        <v>1947</v>
       </c>
       <c r="K439" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24242,13 +24275,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1946</v>
+        <v>1948</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1947</v>
+        <v>1949</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24260,10 +24293,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1948</v>
+        <v>1950</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1949</v>
+        <v>1951</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24271,13 +24304,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1950</v>
+        <v>1952</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1951</v>
+        <v>1953</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24289,10 +24322,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1952</v>
+        <v>1954</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1953</v>
+        <v>1955</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24300,13 +24333,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1954</v>
+        <v>1956</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1956</v>
+        <v>1958</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24318,10 +24351,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1957</v>
+        <v>1959</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24329,13 +24362,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1959</v>
+        <v>1961</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1960</v>
+        <v>1962</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24347,10 +24380,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1961</v>
+        <v>1963</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1962</v>
+        <v>1964</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24358,13 +24391,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1963</v>
+        <v>1965</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1964</v>
+        <v>1966</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24376,10 +24409,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1965</v>
+        <v>1967</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1966</v>
+        <v>1968</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24387,13 +24420,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1967</v>
+        <v>1969</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1968</v>
+        <v>1970</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24405,10 +24438,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1969</v>
+        <v>1971</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1970</v>
+        <v>1972</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24416,13 +24449,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1971</v>
+        <v>1973</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1972</v>
+        <v>1974</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24434,10 +24467,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1973</v>
+        <v>1975</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24445,13 +24478,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1974</v>
+        <v>1976</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1976</v>
+        <v>1978</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24463,10 +24496,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1977</v>
+        <v>1979</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1978</v>
+        <v>1980</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24474,13 +24507,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1979</v>
+        <v>1981</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1980</v>
+        <v>1982</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24492,10 +24525,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1981</v>
+        <v>1983</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1982</v>
+        <v>1984</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24503,13 +24536,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1983</v>
+        <v>1985</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1984</v>
+        <v>1986</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24521,10 +24554,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1985</v>
+        <v>1987</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1986</v>
+        <v>1988</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24532,13 +24565,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1987</v>
+        <v>1989</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1988</v>
+        <v>1990</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24550,10 +24583,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1989</v>
+        <v>1991</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24561,13 +24594,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1991</v>
+        <v>1993</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1992</v>
+        <v>1994</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24579,10 +24612,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1993</v>
+        <v>1995</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24590,13 +24623,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1995</v>
+        <v>1997</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1996</v>
+        <v>1998</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24608,10 +24641,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24619,13 +24652,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>1998</v>
+        <v>2000</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>1999</v>
+        <v>2001</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24637,10 +24670,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>2000</v>
+        <v>2002</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24648,13 +24681,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>2001</v>
+        <v>2003</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2002</v>
+        <v>2004</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24666,10 +24699,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2003</v>
+        <v>2005</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1990</v>
+        <v>1992</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24677,13 +24710,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2004</v>
+        <v>2006</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2005</v>
+        <v>2007</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24695,10 +24728,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2006</v>
+        <v>2008</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2007</v>
+        <v>2009</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24706,13 +24739,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2008</v>
+        <v>2010</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2009</v>
+        <v>2011</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24724,24 +24757,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2010</v>
+        <v>2012</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2011</v>
+        <v>2013</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1834</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2012</v>
+        <v>2014</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2013</v>
+        <v>2015</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24753,10 +24786,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2014</v>
+        <v>2016</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2015</v>
+        <v>2017</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24764,13 +24797,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2017</v>
+        <v>2019</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24782,10 +24815,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2018</v>
+        <v>2020</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1994</v>
+        <v>1996</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24793,13 +24826,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2019</v>
+        <v>2021</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24811,10 +24844,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24822,13 +24855,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2025</v>
+        <v>2027</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24840,10 +24873,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2026</v>
+        <v>2028</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2027</v>
+        <v>2029</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24851,13 +24884,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2028</v>
+        <v>2030</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2029</v>
+        <v>2031</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24869,10 +24902,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2030</v>
+        <v>2032</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2031</v>
+        <v>2033</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24880,13 +24913,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2032</v>
+        <v>2034</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2033</v>
+        <v>2035</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24898,10 +24931,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2034</v>
+        <v>2036</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2035</v>
+        <v>2037</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24909,13 +24942,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2036</v>
+        <v>2038</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2024</v>
+        <v>2026</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2037</v>
+        <v>2039</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24927,10 +24960,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2038</v>
+        <v>2040</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2039</v>
+        <v>2041</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24938,13 +24971,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2040</v>
+        <v>2042</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2042</v>
+        <v>2044</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24956,10 +24989,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2043</v>
+        <v>2045</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -24967,13 +25000,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2045</v>
+        <v>2047</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2046</v>
+        <v>2048</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -24985,10 +25018,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
-        <v>2047</v>
+        <v>2049</v>
       </c>
       <c r="K465" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -24996,13 +25029,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2048</v>
+        <v>2050</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2049</v>
+        <v>2051</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -25014,10 +25047,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2050</v>
+        <v>2052</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2044</v>
+        <v>2046</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -25025,13 +25058,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2051</v>
+        <v>2053</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2053</v>
+        <v>2055</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -25043,10 +25076,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2054</v>
+        <v>2056</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -25054,13 +25087,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2056</v>
+        <v>2058</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2057</v>
+        <v>2059</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25072,10 +25105,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
-        <v>2058</v>
+        <v>2060</v>
       </c>
       <c r="K468" s="4" t="s">
-        <v>2055</v>
+        <v>2057</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25083,13 +25116,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2059</v>
+        <v>2061</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2060</v>
+        <v>2062</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25101,10 +25134,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2061</v>
+        <v>2063</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2062</v>
+        <v>2064</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25112,13 +25145,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2063</v>
+        <v>2065</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2065</v>
+        <v>2067</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25130,10 +25163,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2066</v>
+        <v>2068</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2067</v>
+        <v>2069</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25141,13 +25174,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2068</v>
+        <v>2070</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2069</v>
+        <v>2071</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25159,10 +25192,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2070</v>
+        <v>2072</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2071</v>
+        <v>2073</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25170,13 +25203,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2072</v>
+        <v>2074</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2073</v>
+        <v>2075</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25188,10 +25221,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2074</v>
+        <v>2076</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2075</v>
+        <v>2077</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25199,13 +25232,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2076</v>
+        <v>2078</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2077</v>
+        <v>2079</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25217,10 +25250,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2078</v>
+        <v>2080</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2079</v>
+        <v>2081</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25228,13 +25261,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2080</v>
+        <v>2082</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2081</v>
+        <v>2083</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25246,10 +25279,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2082</v>
+        <v>2084</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2083</v>
+        <v>2085</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25257,13 +25290,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2084</v>
+        <v>2086</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2086</v>
+        <v>2088</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25275,10 +25308,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2087</v>
+        <v>2089</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25286,13 +25319,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2089</v>
+        <v>2091</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2090</v>
+        <v>2092</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25304,10 +25337,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
-        <v>2091</v>
+        <v>2093</v>
       </c>
       <c r="K476" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25315,13 +25348,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2092</v>
+        <v>2094</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2093</v>
+        <v>2095</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25333,10 +25366,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2094</v>
+        <v>2096</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2088</v>
+        <v>2090</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25344,13 +25377,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2095</v>
+        <v>2097</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2097</v>
+        <v>2099</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25362,10 +25395,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2098</v>
+        <v>2100</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2099</v>
+        <v>2101</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25373,13 +25406,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2100</v>
+        <v>2102</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2101</v>
+        <v>2103</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25391,10 +25424,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2102</v>
+        <v>2104</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2103</v>
+        <v>2105</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25402,13 +25435,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2104</v>
+        <v>2106</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2105</v>
+        <v>2107</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25420,10 +25453,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2106</v>
+        <v>2108</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2107</v>
+        <v>2109</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25431,13 +25464,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2108</v>
+        <v>2110</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2110</v>
+        <v>2112</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25449,10 +25482,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2111</v>
+        <v>2113</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2112</v>
+        <v>2114</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25460,13 +25493,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2113</v>
+        <v>2115</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2114</v>
+        <v>2116</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25478,10 +25511,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2115</v>
+        <v>2117</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25489,13 +25522,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2117</v>
+        <v>2119</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2118</v>
+        <v>2120</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25507,10 +25540,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2119</v>
+        <v>2121</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2120</v>
+        <v>2122</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25518,13 +25551,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2121</v>
+        <v>2123</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2123</v>
+        <v>2125</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25536,10 +25569,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2124</v>
+        <v>2126</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2125</v>
+        <v>2127</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25547,13 +25580,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2126</v>
+        <v>2128</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2127</v>
+        <v>2129</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25565,10 +25598,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2128</v>
+        <v>2130</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25576,13 +25609,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2130</v>
+        <v>2132</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2132</v>
+        <v>2134</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25594,10 +25627,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2133</v>
+        <v>2135</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25605,13 +25638,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2135</v>
+        <v>2137</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2136</v>
+        <v>2138</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25623,10 +25656,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2137</v>
+        <v>2139</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2138</v>
+        <v>2140</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25634,13 +25667,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25652,10 +25685,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25663,13 +25696,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
-        <v>2144</v>
+        <v>2146</v>
       </c>
       <c r="B489" s="4" t="s">
-        <v>2145</v>
+        <v>2147</v>
       </c>
       <c r="C489" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25681,10 +25714,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2146</v>
+        <v>2148</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25692,13 +25725,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2147</v>
+        <v>2149</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25710,10 +25743,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2149</v>
+        <v>2151</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25721,13 +25754,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2150</v>
+        <v>2152</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25739,10 +25772,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2152</v>
+        <v>2154</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25750,13 +25783,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2153</v>
+        <v>2155</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25768,10 +25801,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2155</v>
+        <v>2157</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25779,13 +25812,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2156</v>
+        <v>2158</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2141</v>
+        <v>2143</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25797,10 +25830,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2142</v>
+        <v>2144</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2158</v>
+        <v>2160</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26331,7 +26364,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L330"/>
+  <dimension ref="A1:L333"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -38874,8 +38907,122 @@
         <v>625</v>
       </c>
     </row>
+    <row r="331" spans="1:12" ht="72" customHeight="1">
+      <c r="A331" s="4" t="s">
+        <v>1518</v>
+      </c>
+      <c r="B331" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C331" s="4" t="s">
+        <v>1520</v>
+      </c>
+      <c r="D331" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E331" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F331" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G331" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H331" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I331" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J331" s="4" t="s">
+        <v>1523</v>
+      </c>
+      <c r="K331" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L331" s="6" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="332" spans="1:12" ht="72" customHeight="1">
+      <c r="A332" s="4" t="s">
+        <v>1525</v>
+      </c>
+      <c r="B332" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C332" s="4" t="s">
+        <v>1526</v>
+      </c>
+      <c r="D332" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E332" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F332" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G332" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H332" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I332" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J332" s="4" t="s">
+        <v>1527</v>
+      </c>
+      <c r="K332" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L332" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="333" spans="1:12" ht="72" customHeight="1">
+      <c r="A333" s="4" t="s">
+        <v>1528</v>
+      </c>
+      <c r="B333" s="4" t="s">
+        <v>1519</v>
+      </c>
+      <c r="C333" s="4" t="s">
+        <v>1529</v>
+      </c>
+      <c r="D333" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E333" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F333" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G333" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="H333" s="4" t="s">
+        <v>1521</v>
+      </c>
+      <c r="I333" s="4" t="s">
+        <v>1522</v>
+      </c>
+      <c r="J333" s="4" t="s">
+        <v>1530</v>
+      </c>
+      <c r="K333" s="4" t="s">
+        <v>1524</v>
+      </c>
+      <c r="L333" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F330">
+  <conditionalFormatting sqref="E2:F333">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -39222,11 +39369,14 @@
     <hyperlink ref="L328" r:id="rId327"/>
     <hyperlink ref="L329" r:id="rId328"/>
     <hyperlink ref="L330" r:id="rId329"/>
+    <hyperlink ref="L331" r:id="rId330"/>
+    <hyperlink ref="L332" r:id="rId331"/>
+    <hyperlink ref="L333" r:id="rId332"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId330"/>
+    <tablePart r:id="rId333"/>
   </tableParts>
 </worksheet>
 </file>
@@ -39243,3128 +39393,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2159</v>
+        <v>2161</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2160</v>
+        <v>2162</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2161</v>
+        <v>2163</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2162</v>
+        <v>2164</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2163</v>
+        <v>2165</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2164</v>
+        <v>2166</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2165</v>
+        <v>2167</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2166</v>
+        <v>2168</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2167</v>
+        <v>2169</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2168</v>
+        <v>2170</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2169</v>
+        <v>2171</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2171</v>
+        <v>2173</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2175</v>
+        <v>2177</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2176</v>
+        <v>2178</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2179</v>
+        <v>2181</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2180</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2181</v>
+        <v>2183</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2182</v>
+        <v>2184</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2184</v>
+        <v>2186</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2186</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2187</v>
+        <v>2189</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2188</v>
+        <v>2190</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2189</v>
+        <v>2191</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2191</v>
+        <v>2193</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2192</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2193</v>
+        <v>2195</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2194</v>
+        <v>2196</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2195</v>
+        <v>2197</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2196</v>
+        <v>2198</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2197</v>
+        <v>2199</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2198</v>
+        <v>2200</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2199</v>
+        <v>2201</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2200</v>
+        <v>2202</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2201</v>
+        <v>2203</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2202</v>
+        <v>2204</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2203</v>
+        <v>2205</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2205</v>
+        <v>2207</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2206</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2207</v>
+        <v>2209</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2208</v>
+        <v>2210</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2209</v>
+        <v>2211</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2210</v>
+        <v>2212</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2211</v>
+        <v>2213</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2212</v>
+        <v>2214</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2213</v>
+        <v>2215</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2214</v>
+        <v>2216</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2216</v>
+        <v>2218</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2217</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2218</v>
+        <v>2220</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2219</v>
+        <v>2221</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2220</v>
+        <v>2222</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2221</v>
+        <v>2223</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2222</v>
+        <v>2224</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2223</v>
+        <v>2225</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2224</v>
+        <v>2226</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2225</v>
+        <v>2227</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2226</v>
+        <v>2228</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2227</v>
+        <v>2229</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2228</v>
+        <v>2230</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2230</v>
+        <v>2232</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2231</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2233</v>
+        <v>2235</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2234</v>
+        <v>2236</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2235</v>
+        <v>2237</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2236</v>
+        <v>2238</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2237</v>
+        <v>2239</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2238</v>
+        <v>2240</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2239</v>
+        <v>2241</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2240</v>
+        <v>2242</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2241</v>
+        <v>2243</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2242</v>
+        <v>2244</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2244</v>
+        <v>2246</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2245</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2246</v>
+        <v>2248</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2247</v>
+        <v>2249</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2248</v>
+        <v>2250</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2249</v>
+        <v>2251</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2250</v>
+        <v>2252</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2251</v>
+        <v>2253</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2252</v>
+        <v>2254</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2253</v>
+        <v>2255</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2255</v>
+        <v>2257</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2256</v>
+        <v>2258</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2257</v>
+        <v>2259</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2258</v>
+        <v>2260</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2259</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2260</v>
+        <v>2262</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2261</v>
+        <v>2263</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2262</v>
+        <v>2264</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2263</v>
+        <v>2265</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2264</v>
+        <v>2266</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2265</v>
+        <v>2267</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2266</v>
+        <v>2268</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2267</v>
+        <v>2269</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2268</v>
+        <v>2270</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2269</v>
+        <v>2271</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2270</v>
+        <v>2272</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2271</v>
+        <v>2273</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2272</v>
+        <v>2274</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2273</v>
+        <v>2275</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2274</v>
+        <v>2276</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2275</v>
+        <v>2277</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2276</v>
+        <v>2278</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2278</v>
+        <v>2280</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2279</v>
+        <v>2281</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2280</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2281</v>
+        <v>2283</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2282</v>
+        <v>2284</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2283</v>
+        <v>2285</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2284</v>
+        <v>2286</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2285</v>
+        <v>2287</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2286</v>
+        <v>2288</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2287</v>
+        <v>2289</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2288</v>
+        <v>2290</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2289</v>
+        <v>2291</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2290</v>
+        <v>2292</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2291</v>
+        <v>2293</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2292</v>
+        <v>2294</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2293</v>
+        <v>2295</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2294</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2295</v>
+        <v>2297</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2296</v>
+        <v>2298</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2297</v>
+        <v>2299</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2298</v>
+        <v>2300</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2299</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2300</v>
+        <v>2302</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2301</v>
+        <v>2303</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2302</v>
+        <v>2304</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2303</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2304</v>
+        <v>2306</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2305</v>
+        <v>2307</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2306</v>
+        <v>2308</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2307</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2308</v>
+        <v>2310</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2309</v>
+        <v>2311</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2310</v>
+        <v>2312</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2311</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2312</v>
+        <v>2314</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2314</v>
+        <v>2316</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2315</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2316</v>
+        <v>2318</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2317</v>
+        <v>2319</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2318</v>
+        <v>2320</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2319</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2320</v>
+        <v>2322</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2321</v>
+        <v>2323</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2322</v>
+        <v>2324</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2323</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2324</v>
+        <v>2326</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2325</v>
+        <v>2327</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2326</v>
+        <v>2328</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2327</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2328</v>
+        <v>2330</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2329</v>
+        <v>2331</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2330</v>
+        <v>2332</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2170</v>
+        <v>2172</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2331</v>
+        <v>2333</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2332</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2333</v>
+        <v>2335</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2334</v>
+        <v>2336</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2335</v>
+        <v>2337</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2336</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2337</v>
+        <v>2339</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2338</v>
+        <v>2340</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2339</v>
+        <v>2341</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2340</v>
+        <v>2342</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2341</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2342</v>
+        <v>2344</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2343</v>
+        <v>2345</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2344</v>
+        <v>2346</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2345</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2346</v>
+        <v>2348</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2347</v>
+        <v>2349</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2348</v>
+        <v>2350</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2350</v>
+        <v>2352</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2353</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2354</v>
+        <v>2356</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>2355</v>
+        <v>2357</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>2356</v>
+        <v>2358</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>2357</v>
+        <v>2359</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>2358</v>
+        <v>2360</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2359</v>
+        <v>2361</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2360</v>
+        <v>2362</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2361</v>
+        <v>2363</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2362</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2363</v>
+        <v>2365</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2364</v>
+        <v>2366</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2365</v>
+        <v>2367</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2366</v>
+        <v>2368</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2351</v>
+        <v>2353</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2352</v>
+        <v>2354</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2367</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2368</v>
+        <v>2370</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2369</v>
+        <v>2371</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2370</v>
+        <v>2372</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2371</v>
+        <v>2373</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2372</v>
+        <v>2374</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2373</v>
+        <v>2375</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2374</v>
+        <v>2376</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2375</v>
+        <v>2377</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2376</v>
+        <v>2378</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2377</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2378</v>
+        <v>2380</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2379</v>
+        <v>2381</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2380</v>
+        <v>2382</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2381</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2382</v>
+        <v>2384</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2383</v>
+        <v>2385</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2384</v>
+        <v>2386</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2385</v>
+        <v>2387</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2386</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2387</v>
+        <v>2389</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2388</v>
+        <v>2390</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2389</v>
+        <v>2391</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2390</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2391</v>
+        <v>2393</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2392</v>
+        <v>2394</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2393</v>
+        <v>2395</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2394</v>
+        <v>2396</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2395</v>
+        <v>2397</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2396</v>
+        <v>2398</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2397</v>
+        <v>2399</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2398</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2400</v>
+        <v>2402</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2401</v>
+        <v>2403</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2402</v>
+        <v>2404</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2403</v>
+        <v>2405</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2404</v>
+        <v>2406</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2405</v>
+        <v>2407</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2406</v>
+        <v>2408</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2407</v>
+        <v>2409</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2408</v>
+        <v>2410</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2409</v>
+        <v>2411</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2410</v>
+        <v>2412</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2411</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2412</v>
+        <v>2414</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2413</v>
+        <v>2415</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2414</v>
+        <v>2416</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2415</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2416</v>
+        <v>2418</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2417</v>
+        <v>2419</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2418</v>
+        <v>2420</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2419</v>
+        <v>2421</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2420</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2421</v>
+        <v>2423</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2422</v>
+        <v>2424</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2423</v>
+        <v>2425</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2424</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2425</v>
+        <v>2427</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2426</v>
+        <v>2428</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2427</v>
+        <v>2429</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2428</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2429</v>
+        <v>2431</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2430</v>
+        <v>2432</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2431</v>
+        <v>2433</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2432</v>
+        <v>2434</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2433</v>
+        <v>2435</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2434</v>
+        <v>2436</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2435</v>
+        <v>2437</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2436</v>
+        <v>2438</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2437</v>
+        <v>2439</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2438</v>
+        <v>2440</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>1499</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2183</v>
+        <v>2185</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2439</v>
+        <v>2441</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2440</v>
+        <v>2442</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2441</v>
+        <v>2443</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2442</v>
+        <v>2444</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>1522</v>
+        <v>1524</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2443</v>
+        <v>2445</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2444</v>
+        <v>2446</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2445</v>
+        <v>2447</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>1530</v>
+        <v>1532</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2446</v>
+        <v>2448</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1533</v>
+        <v>1535</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2243</v>
+        <v>2245</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2447</v>
+        <v>2449</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2448</v>
+        <v>2450</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1561</v>
+        <v>1563</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2450</v>
+        <v>2452</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1572</v>
+        <v>1574</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2451</v>
+        <v>2453</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2452</v>
+        <v>2454</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2453</v>
+        <v>2455</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1580</v>
+        <v>1582</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2454</v>
+        <v>2456</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1602</v>
+        <v>1604</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2455</v>
+        <v>2457</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2254</v>
+        <v>2256</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2456</v>
+        <v>2458</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2457</v>
+        <v>2459</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1604</v>
+        <v>1606</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2458</v>
+        <v>2460</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1615</v>
+        <v>1617</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2459</v>
+        <v>2461</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2460</v>
+        <v>2462</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2461</v>
+        <v>2463</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1621</v>
+        <v>1623</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2462</v>
+        <v>2464</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1628</v>
+        <v>1630</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2463</v>
+        <v>2465</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2464</v>
+        <v>2466</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2465</v>
+        <v>2467</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1637</v>
+        <v>1639</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2466</v>
+        <v>2468</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1644</v>
+        <v>1646</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2467</v>
+        <v>2469</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2468</v>
+        <v>2470</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2469</v>
+        <v>2471</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1660</v>
+        <v>1662</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2470</v>
+        <v>2472</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1675</v>
+        <v>1677</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2471</v>
+        <v>2473</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2472</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2473</v>
+        <v>2475</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1677</v>
+        <v>1679</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2474</v>
+        <v>2476</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1680</v>
+        <v>1682</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2475</v>
+        <v>2477</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2476</v>
+        <v>2478</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2477</v>
+        <v>2479</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1692</v>
+        <v>1694</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2478</v>
+        <v>2480</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1695</v>
+        <v>1697</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2178</v>
+        <v>2180</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2479</v>
+        <v>2481</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2480</v>
+        <v>2482</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2481</v>
+        <v>2483</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1726</v>
+        <v>1728</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2482</v>
+        <v>2484</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1733</v>
+        <v>1735</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2483</v>
+        <v>2485</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2484</v>
+        <v>2486</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2485</v>
+        <v>2487</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1742</v>
+        <v>1744</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2486</v>
+        <v>2488</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1745</v>
+        <v>1747</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2487</v>
+        <v>2489</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2488</v>
+        <v>2490</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2489</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2490</v>
+        <v>2492</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1792</v>
+        <v>1794</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2491</v>
+        <v>2493</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2492</v>
+        <v>2494</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2493</v>
+        <v>2495</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2494</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2495</v>
+        <v>2497</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1805</v>
+        <v>1807</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2496</v>
+        <v>2498</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2497</v>
+        <v>2499</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2498</v>
+        <v>2500</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2500</v>
+        <v>2502</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1814</v>
+        <v>1816</v>
       </c>
       <c r="C75" s="4" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>2504</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2206</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2505</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2501</v>
       </c>
-      <c r="D75" s="4" t="s">
-        <v>2502</v>
-      </c>
-      <c r="E75" s="4" t="s">
-        <v>2204</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2503</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2172</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2499</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2504</v>
+        <v>2506</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1826</v>
+        <v>1828</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2505</v>
+        <v>2507</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1829</v>
+        <v>1831</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2215</v>
+        <v>2217</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2506</v>
+        <v>2508</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2507</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2508</v>
+        <v>2510</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1849</v>
+        <v>1851</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2509</v>
+        <v>2511</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2510</v>
+        <v>2512</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2511</v>
+        <v>2513</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2512</v>
+        <v>2514</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2513</v>
+        <v>2515</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1869</v>
+        <v>1871</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2514</v>
+        <v>2516</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2515</v>
+        <v>2517</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2516</v>
+        <v>2518</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2517</v>
+        <v>2519</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2518</v>
+        <v>2520</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1886</v>
+        <v>1888</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2519</v>
+        <v>2521</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2520</v>
+        <v>2522</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2521</v>
+        <v>2523</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2522</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2523</v>
+        <v>2525</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1906</v>
+        <v>1908</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2524</v>
+        <v>2526</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2525</v>
+        <v>2527</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2526</v>
+        <v>2528</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2527</v>
+        <v>2529</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2528</v>
+        <v>2530</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1923</v>
+        <v>1925</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2529</v>
+        <v>2531</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2530</v>
+        <v>2532</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2531</v>
+        <v>2533</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2532</v>
+        <v>2534</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2533</v>
+        <v>2535</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1939</v>
+        <v>1941</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2534</v>
+        <v>2536</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2229</v>
+        <v>2231</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2535</v>
+        <v>2537</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2536</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2537</v>
+        <v>2539</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1955</v>
+        <v>1957</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2538</v>
+        <v>2540</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1958</v>
+        <v>1960</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2539</v>
+        <v>2541</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2185</v>
+        <v>2187</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2540</v>
+        <v>2542</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2541</v>
+        <v>2543</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1975</v>
+        <v>1977</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2542</v>
+        <v>2544</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2543</v>
+        <v>2545</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2544</v>
+        <v>2546</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2545</v>
+        <v>2547</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2548</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2551</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2026</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2552</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2553</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2231</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>2548</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2549</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>2024</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>2550</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2551</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2229</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2552</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2546</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2553</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2547</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2554</v>
+        <v>2556</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2041</v>
+        <v>2043</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2555</v>
+        <v>2557</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2556</v>
+        <v>2558</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2557</v>
+        <v>2559</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2558</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2559</v>
+        <v>2561</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2052</v>
+        <v>2054</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2560</v>
+        <v>2562</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2561</v>
+        <v>2563</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2562</v>
+        <v>2564</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2563</v>
+        <v>2565</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2564</v>
+        <v>2566</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2064</v>
+        <v>2066</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2565</v>
+        <v>2567</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2566</v>
+        <v>2568</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2190</v>
+        <v>2192</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2567</v>
+        <v>2569</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2173</v>
+        <v>2175</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2568</v>
+        <v>2570</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2569</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2570</v>
+        <v>2572</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2085</v>
+        <v>2087</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2571</v>
+        <v>2573</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2572</v>
+        <v>2574</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2573</v>
+        <v>2575</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2574</v>
+        <v>2576</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2096</v>
+        <v>2098</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2575</v>
+        <v>2577</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2576</v>
+        <v>2578</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2577</v>
+        <v>2579</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2578</v>
+        <v>2580</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2109</v>
+        <v>2111</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2579</v>
+        <v>2581</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2116</v>
+        <v>2118</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2204</v>
+        <v>2206</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2580</v>
+        <v>2582</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2546</v>
+        <v>2548</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2547</v>
+        <v>2549</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2581</v>
+        <v>2583</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2122</v>
+        <v>2124</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2582</v>
+        <v>2584</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2129</v>
+        <v>2131</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2583</v>
+        <v>2585</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2584</v>
+        <v>2586</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2131</v>
+        <v>2133</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2585</v>
+        <v>2587</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2134</v>
+        <v>2136</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2349</v>
+        <v>2351</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2586</v>
+        <v>2588</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2499</v>
+        <v>2501</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2174</v>
+        <v>2176</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2587</v>
+        <v>2589</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2140</v>
+        <v>2142</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2588</v>
+        <v>2590</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2143</v>
+        <v>2145</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2589</v>
+        <v>2591</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2139</v>
+        <v>2141</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2594</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2148</v>
+      </c>
+      <c r="E95" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>2146</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2174</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2592</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2145</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="I95" s="4" t="s">
         <v>2593</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>2146</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2144</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2172</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2590</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>2591</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
-        <v>2594</v>
+        <v>2596</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>2148</v>
+        <v>2150</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>2595</v>
+        <v>2597</v>
       </c>
       <c r="D96" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F96" s="4" t="s">
         <v>2149</v>
       </c>
-      <c r="E96" s="4" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2147</v>
-      </c>
       <c r="G96" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2596</v>
+        <v>2598</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2151</v>
+        <v>2153</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2597</v>
+        <v>2599</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E97" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F97" s="4" t="s">
         <v>2152</v>
       </c>
-      <c r="E97" s="4" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F97" s="4" t="s">
-        <v>2150</v>
-      </c>
       <c r="G97" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2598</v>
+        <v>2600</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2154</v>
+        <v>2156</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2599</v>
+        <v>2601</v>
       </c>
       <c r="D98" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>2155</v>
       </c>
-      <c r="E98" s="4" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>2153</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2600</v>
+        <v>2602</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2157</v>
+        <v>2159</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2601</v>
+        <v>2603</v>
       </c>
       <c r="D99" s="4" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E99" s="4" t="s">
+        <v>2591</v>
+      </c>
+      <c r="F99" s="4" t="s">
         <v>2158</v>
       </c>
-      <c r="E99" s="4" t="s">
-        <v>2589</v>
-      </c>
-      <c r="F99" s="4" t="s">
-        <v>2156</v>
-      </c>
       <c r="G99" s="4" t="s">
-        <v>2172</v>
+        <v>2174</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2590</v>
+        <v>2592</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2591</v>
+        <v>2593</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10419" uniqueCount="2604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="2607">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 08:40 BST</t>
+    <t>Snapshot: 07 September 2026, 09:00 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4623,6 +4623,15 @@
   </si>
   <si>
     <t>Event identity and primary action</t>
+  </si>
+  <si>
+    <t>Full shared compact detail; URL sections/aliases, complete standings/history, completed-only progress, reviewable entry/submission/withdrawal. Actual matrix PASS2.2m all12; multiround reset PASS47.6s 1440/390 both surfaces. TypeScript/scoped lint pass. tournament-detail-browser-stack and tournament-detail-multiround under output/playwright/ui-upgrade.</t>
+  </si>
+  <si>
+    <t>Same complete task; vertical progress, full standing cards, retained draft across sections, cancellation inert, exactly one pending manual save, withdrawal preserves history. Actual matrix includes390x844,360x800,1023x800,1024x800 both surfaces. Desktop1440/mobile390 screenshots inspected. API round-bound token test4PASS; uploader browser positive round binding outstanding.</t>
+  </si>
+  <si>
+    <t>Full acceptance outstanding: signed OCR/round-bound uploader browser, saved-round positive proof/ties/full toolbar, completed/draft/closed permission/error/loading cases, focus return/AT/zoom/themes/shared fixed bars. First run loading/compilation timeout; next all12 actions passed but one Invalid token browser error; stack repeat passed, original error unreproduced not diagnosed. Saved matching list limited12. Submission retry service tests pass; post-transaction standings/feed failure recovery remains broader acceptance.</t>
   </si>
   <si>
     <t>Not entered, entered, submitted and completed states have distinct correct actions.</t>
@@ -8005,8 +8014,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L333" totalsRowShown="0">
-  <autoFilter ref="A1:L333"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L341" totalsRowShown="0">
+  <autoFilter ref="A1:L341"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8400,11 +8409,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>325</v>
+        <v>333</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8439,11 +8448,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>160</v>
+        <v>152</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -21213,16 +21222,25 @@
         <v>42</v>
       </c>
       <c r="E334" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F334" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G334" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H334" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I334" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J334" s="4" t="s">
-        <v>1534</v>
+        <v>1537</v>
       </c>
       <c r="K334" s="4" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="L334" s="6" t="s">
         <v>39</v>
@@ -21230,28 +21248,37 @@
     </row>
     <row r="335" spans="1:12" ht="72" customHeight="1">
       <c r="A335" s="4" t="s">
-        <v>1536</v>
+        <v>1539</v>
       </c>
       <c r="B335" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C335" s="4" t="s">
-        <v>1537</v>
+        <v>1540</v>
       </c>
       <c r="D335" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E335" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F335" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G335" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H335" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I335" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J335" s="4" t="s">
-        <v>1538</v>
+        <v>1541</v>
       </c>
       <c r="K335" s="4" t="s">
-        <v>1539</v>
+        <v>1542</v>
       </c>
       <c r="L335" s="6" t="s">
         <v>311</v>
@@ -21259,28 +21286,37 @@
     </row>
     <row r="336" spans="1:12" ht="72" customHeight="1">
       <c r="A336" s="4" t="s">
-        <v>1540</v>
+        <v>1543</v>
       </c>
       <c r="B336" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C336" s="4" t="s">
-        <v>1541</v>
+        <v>1544</v>
       </c>
       <c r="D336" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E336" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F336" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G336" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H336" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I336" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J336" s="4" t="s">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="K336" s="4" t="s">
-        <v>1543</v>
+        <v>1546</v>
       </c>
       <c r="L336" s="6" t="s">
         <v>518</v>
@@ -21288,28 +21324,37 @@
     </row>
     <row r="337" spans="1:12" ht="72" customHeight="1">
       <c r="A337" s="4" t="s">
-        <v>1544</v>
+        <v>1547</v>
       </c>
       <c r="B337" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C337" s="4" t="s">
-        <v>1545</v>
+        <v>1548</v>
       </c>
       <c r="D337" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E337" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F337" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G337" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H337" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I337" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J337" s="4" t="s">
-        <v>1546</v>
+        <v>1549</v>
       </c>
       <c r="K337" s="4" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="L337" s="6" t="s">
         <v>81</v>
@@ -21317,28 +21362,37 @@
     </row>
     <row r="338" spans="1:12" ht="72" customHeight="1">
       <c r="A338" s="4" t="s">
-        <v>1547</v>
+        <v>1550</v>
       </c>
       <c r="B338" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C338" s="4" t="s">
-        <v>1548</v>
+        <v>1551</v>
       </c>
       <c r="D338" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E338" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F338" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G338" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J338" s="4" t="s">
-        <v>1549</v>
+        <v>1552</v>
       </c>
       <c r="K338" s="4" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="L338" s="6" t="s">
         <v>518</v>
@@ -21346,28 +21400,37 @@
     </row>
     <row r="339" spans="1:12" ht="72" customHeight="1">
       <c r="A339" s="4" t="s">
-        <v>1550</v>
+        <v>1553</v>
       </c>
       <c r="B339" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C339" s="4" t="s">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="D339" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E339" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F339" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G339" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I339" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J339" s="4" t="s">
-        <v>1552</v>
+        <v>1555</v>
       </c>
       <c r="K339" s="4" t="s">
-        <v>1553</v>
+        <v>1556</v>
       </c>
       <c r="L339" s="6" t="s">
         <v>1045</v>
@@ -21375,28 +21438,37 @@
     </row>
     <row r="340" spans="1:12" ht="72" customHeight="1">
       <c r="A340" s="4" t="s">
-        <v>1554</v>
+        <v>1557</v>
       </c>
       <c r="B340" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C340" s="4" t="s">
-        <v>1555</v>
+        <v>1558</v>
       </c>
       <c r="D340" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E340" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F340" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G340" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H340" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I340" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J340" s="4" t="s">
-        <v>1556</v>
+        <v>1559</v>
       </c>
       <c r="K340" s="4" t="s">
-        <v>1557</v>
+        <v>1560</v>
       </c>
       <c r="L340" s="6" t="s">
         <v>88</v>
@@ -21404,28 +21476,37 @@
     </row>
     <row r="341" spans="1:12" ht="72" customHeight="1">
       <c r="A341" s="4" t="s">
-        <v>1558</v>
+        <v>1561</v>
       </c>
       <c r="B341" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C341" s="4" t="s">
-        <v>1559</v>
+        <v>1562</v>
       </c>
       <c r="D341" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E341" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F341" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G341" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I341" s="4" t="s">
+        <v>1536</v>
       </c>
       <c r="J341" s="4" t="s">
-        <v>1560</v>
+        <v>1563</v>
       </c>
       <c r="K341" s="4" t="s">
-        <v>1561</v>
+        <v>1564</v>
       </c>
       <c r="L341" s="6" t="s">
         <v>103</v>
@@ -21433,13 +21514,13 @@
     </row>
     <row r="342" spans="1:12" ht="72" customHeight="1">
       <c r="A342" s="4" t="s">
-        <v>1562</v>
+        <v>1565</v>
       </c>
       <c r="B342" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C342" s="4" t="s">
-        <v>1564</v>
+        <v>1567</v>
       </c>
       <c r="D342" s="4" t="s">
         <v>42</v>
@@ -21451,10 +21532,10 @@
         <v>9</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1565</v>
+        <v>1568</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1566</v>
+        <v>1569</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21462,13 +21543,13 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1567</v>
+        <v>1570</v>
       </c>
       <c r="B343" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
@@ -21480,10 +21561,10 @@
         <v>9</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21491,13 +21572,13 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="B344" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
@@ -21509,10 +21590,10 @@
         <v>9</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21520,13 +21601,13 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="B345" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
@@ -21538,10 +21619,10 @@
         <v>9</v>
       </c>
       <c r="J345" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="K345" s="4" t="s">
         <v>1577</v>
-      </c>
-      <c r="K345" s="4" t="s">
-        <v>1574</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21549,13 +21630,13 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="B346" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
@@ -21567,10 +21648,10 @@
         <v>9</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1580</v>
+        <v>1583</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21578,13 +21659,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21596,10 +21677,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21607,13 +21688,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21625,10 +21706,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21636,13 +21717,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21654,10 +21735,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21665,13 +21746,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21683,10 +21764,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21694,13 +21775,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21712,24 +21793,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21741,10 +21822,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21752,13 +21833,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21770,10 +21851,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21781,13 +21862,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21799,10 +21880,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21810,13 +21891,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21828,10 +21909,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21839,13 +21920,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21857,10 +21938,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21868,13 +21949,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21886,10 +21967,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21897,13 +21978,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21915,10 +21996,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -21926,13 +22007,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -21944,10 +22025,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
+        <v>1636</v>
+      </c>
+      <c r="K359" s="4" t="s">
         <v>1633</v>
-      </c>
-      <c r="K359" s="4" t="s">
-        <v>1630</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -21955,13 +22036,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -21973,10 +22054,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -21984,13 +22065,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -22002,10 +22083,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -22013,13 +22094,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -22031,10 +22112,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -22042,13 +22123,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -22060,10 +22141,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
+        <v>1652</v>
+      </c>
+      <c r="K363" s="4" t="s">
         <v>1649</v>
-      </c>
-      <c r="K363" s="4" t="s">
-        <v>1646</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -22071,13 +22152,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -22089,10 +22170,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -22100,13 +22181,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22118,10 +22199,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22129,13 +22210,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22147,10 +22228,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22158,13 +22239,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22176,10 +22257,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22187,13 +22268,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22205,10 +22286,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22216,13 +22297,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22234,10 +22315,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22245,13 +22326,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22263,10 +22344,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22274,13 +22355,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22292,10 +22373,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22303,13 +22384,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22321,10 +22402,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22332,13 +22413,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22350,10 +22431,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22361,13 +22442,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22379,10 +22460,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22390,13 +22471,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22408,10 +22489,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22419,13 +22500,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22437,10 +22518,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22448,13 +22529,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22466,10 +22547,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22477,13 +22558,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22495,10 +22576,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22506,13 +22587,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22524,10 +22605,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22535,13 +22616,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22553,10 +22634,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22564,13 +22645,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22582,10 +22663,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22593,13 +22674,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22611,24 +22692,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22640,10 +22721,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22651,13 +22732,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22669,10 +22750,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22680,13 +22761,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22698,10 +22779,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22709,13 +22790,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22727,10 +22808,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
+        <v>1741</v>
+      </c>
+      <c r="K386" s="4" t="s">
         <v>1738</v>
-      </c>
-      <c r="K386" s="4" t="s">
-        <v>1735</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22738,13 +22819,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22756,10 +22837,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22767,13 +22848,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22785,10 +22866,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22796,13 +22877,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22814,10 +22895,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
+        <v>1753</v>
+      </c>
+      <c r="K389" s="4" t="s">
         <v>1750</v>
-      </c>
-      <c r="K389" s="4" t="s">
-        <v>1747</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22825,13 +22906,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22843,24 +22924,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22872,10 +22953,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22883,13 +22964,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22901,24 +22982,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -22930,10 +23011,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -22941,13 +23022,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -22959,10 +23040,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -22970,13 +23051,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -22988,24 +23069,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -23017,10 +23098,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -23028,13 +23109,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -23046,10 +23127,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -23057,13 +23138,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -23075,10 +23156,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -23086,13 +23167,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23104,10 +23185,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23115,13 +23196,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23133,10 +23214,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23144,13 +23225,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23162,10 +23243,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
+        <v>1795</v>
+      </c>
+      <c r="K401" s="4" t="s">
         <v>1792</v>
-      </c>
-      <c r="K401" s="4" t="s">
-        <v>1789</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23173,13 +23254,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23191,10 +23272,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23202,13 +23283,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23220,24 +23301,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23249,10 +23330,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23260,13 +23341,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23278,10 +23359,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23289,13 +23370,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23307,10 +23388,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23318,13 +23399,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23336,10 +23417,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23347,13 +23428,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23365,10 +23446,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
+        <v>1825</v>
+      </c>
+      <c r="K408" s="4" t="s">
         <v>1822</v>
-      </c>
-      <c r="K408" s="4" t="s">
-        <v>1819</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23376,13 +23457,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23394,10 +23475,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23405,13 +23486,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23423,10 +23504,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23434,13 +23515,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23452,24 +23533,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23481,10 +23562,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23492,13 +23573,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23510,10 +23591,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23521,13 +23602,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23539,10 +23620,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23550,13 +23631,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23568,10 +23649,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23579,13 +23660,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23597,10 +23678,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23608,13 +23689,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23626,10 +23707,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23637,13 +23718,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23655,10 +23736,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
+        <v>1864</v>
+      </c>
+      <c r="K418" s="4" t="s">
         <v>1861</v>
-      </c>
-      <c r="K418" s="4" t="s">
-        <v>1858</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23666,13 +23747,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23684,10 +23765,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1864</v>
+        <v>1867</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23695,13 +23776,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1867</v>
+        <v>1870</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23713,10 +23794,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23724,13 +23805,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23742,10 +23823,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23753,13 +23834,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23771,10 +23852,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23782,13 +23863,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23800,10 +23881,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23811,13 +23892,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23829,10 +23910,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23840,13 +23921,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23858,10 +23939,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23869,13 +23950,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23887,10 +23968,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23898,13 +23979,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23916,10 +23997,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
+        <v>1901</v>
+      </c>
+      <c r="K427" s="4" t="s">
         <v>1898</v>
-      </c>
-      <c r="K427" s="4" t="s">
-        <v>1895</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -23927,13 +24008,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -23945,10 +24026,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -23956,13 +24037,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -23974,10 +24055,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -23985,13 +24066,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -24003,10 +24084,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -24014,13 +24095,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -24032,10 +24113,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -24043,13 +24124,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -24061,10 +24142,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -24072,13 +24153,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -24090,10 +24171,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -24101,13 +24182,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24119,10 +24200,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24130,13 +24211,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24148,10 +24229,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24159,13 +24240,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24177,10 +24258,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24188,13 +24269,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24206,10 +24287,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24217,13 +24298,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24235,10 +24316,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24246,13 +24327,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24264,10 +24345,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
+        <v>1950</v>
+      </c>
+      <c r="K439" s="4" t="s">
         <v>1947</v>
-      </c>
-      <c r="K439" s="4" t="s">
-        <v>1944</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24275,13 +24356,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24293,10 +24374,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24304,13 +24385,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24322,10 +24403,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24333,13 +24414,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24351,10 +24432,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24362,13 +24443,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24380,10 +24461,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24391,13 +24472,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24409,10 +24490,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24420,13 +24501,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24438,10 +24519,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24449,13 +24530,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24467,10 +24548,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24478,13 +24559,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24496,10 +24577,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24507,13 +24588,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24525,10 +24606,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24536,13 +24617,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24554,10 +24635,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24565,13 +24646,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24583,10 +24664,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24594,13 +24675,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24612,10 +24693,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24623,13 +24704,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24641,10 +24722,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24652,13 +24733,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24670,10 +24751,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24681,13 +24762,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24699,10 +24780,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24710,13 +24791,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24728,10 +24809,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24739,13 +24820,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24757,24 +24838,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24786,10 +24867,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24797,13 +24878,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24815,10 +24896,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24826,13 +24907,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24844,10 +24925,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24855,13 +24936,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24873,10 +24954,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24884,13 +24965,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24902,10 +24983,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24913,13 +24994,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -24931,10 +25012,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -24942,13 +25023,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -24960,10 +25041,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -24971,13 +25052,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -24989,10 +25070,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -25000,13 +25081,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -25018,10 +25099,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
+        <v>2052</v>
+      </c>
+      <c r="K465" s="4" t="s">
         <v>2049</v>
-      </c>
-      <c r="K465" s="4" t="s">
-        <v>2046</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -25029,13 +25110,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -25047,10 +25128,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -25058,13 +25139,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -25076,10 +25157,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -25087,13 +25168,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25105,10 +25186,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
+        <v>2063</v>
+      </c>
+      <c r="K468" s="4" t="s">
         <v>2060</v>
-      </c>
-      <c r="K468" s="4" t="s">
-        <v>2057</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25116,13 +25197,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25134,10 +25215,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25145,13 +25226,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25163,10 +25244,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25174,13 +25255,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25192,10 +25273,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25203,13 +25284,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25221,10 +25302,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25232,13 +25313,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25250,10 +25331,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25261,13 +25342,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25279,10 +25360,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25290,13 +25371,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25308,10 +25389,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25319,13 +25400,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25337,10 +25418,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
+        <v>2096</v>
+      </c>
+      <c r="K476" s="4" t="s">
         <v>2093</v>
-      </c>
-      <c r="K476" s="4" t="s">
-        <v>2090</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25348,13 +25429,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25366,10 +25447,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25377,13 +25458,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25395,10 +25476,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25406,13 +25487,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25424,10 +25505,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25435,13 +25516,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25453,10 +25534,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25464,13 +25545,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25482,10 +25563,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25493,13 +25574,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25511,10 +25592,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25522,13 +25603,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25540,10 +25621,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25551,13 +25632,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25569,10 +25650,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25580,13 +25661,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25598,10 +25679,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25609,13 +25690,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25627,10 +25708,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25638,13 +25719,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25656,10 +25737,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25667,13 +25748,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25685,10 +25766,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25696,13 +25777,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>2146</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>2147</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>2143</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25714,10 +25795,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25725,13 +25806,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25743,10 +25824,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25754,13 +25835,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25772,10 +25853,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25783,13 +25864,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25801,10 +25882,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25812,13 +25893,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25830,10 +25911,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26364,7 +26445,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L333"/>
+  <dimension ref="A1:L341"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -39021,8 +39102,312 @@
         <v>159</v>
       </c>
     </row>
+    <row r="334" spans="1:12" ht="72" customHeight="1">
+      <c r="A334" s="4" t="s">
+        <v>1531</v>
+      </c>
+      <c r="B334" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C334" s="4" t="s">
+        <v>1533</v>
+      </c>
+      <c r="D334" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E334" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F334" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G334" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H334" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I334" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J334" s="4" t="s">
+        <v>1537</v>
+      </c>
+      <c r="K334" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L334" s="6" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="335" spans="1:12" ht="72" customHeight="1">
+      <c r="A335" s="4" t="s">
+        <v>1539</v>
+      </c>
+      <c r="B335" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C335" s="4" t="s">
+        <v>1540</v>
+      </c>
+      <c r="D335" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E335" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F335" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G335" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H335" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I335" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J335" s="4" t="s">
+        <v>1541</v>
+      </c>
+      <c r="K335" s="4" t="s">
+        <v>1542</v>
+      </c>
+      <c r="L335" s="6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="336" spans="1:12" ht="72" customHeight="1">
+      <c r="A336" s="4" t="s">
+        <v>1543</v>
+      </c>
+      <c r="B336" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C336" s="4" t="s">
+        <v>1544</v>
+      </c>
+      <c r="D336" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E336" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F336" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G336" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H336" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I336" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J336" s="4" t="s">
+        <v>1545</v>
+      </c>
+      <c r="K336" s="4" t="s">
+        <v>1546</v>
+      </c>
+      <c r="L336" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="337" spans="1:12" ht="72" customHeight="1">
+      <c r="A337" s="4" t="s">
+        <v>1547</v>
+      </c>
+      <c r="B337" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C337" s="4" t="s">
+        <v>1548</v>
+      </c>
+      <c r="D337" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E337" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F337" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G337" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H337" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I337" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J337" s="4" t="s">
+        <v>1549</v>
+      </c>
+      <c r="K337" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L337" s="6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="338" spans="1:12" ht="72" customHeight="1">
+      <c r="A338" s="4" t="s">
+        <v>1550</v>
+      </c>
+      <c r="B338" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C338" s="4" t="s">
+        <v>1551</v>
+      </c>
+      <c r="D338" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E338" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F338" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G338" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H338" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I338" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J338" s="4" t="s">
+        <v>1552</v>
+      </c>
+      <c r="K338" s="4" t="s">
+        <v>1538</v>
+      </c>
+      <c r="L338" s="6" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="339" spans="1:12" ht="72" customHeight="1">
+      <c r="A339" s="4" t="s">
+        <v>1553</v>
+      </c>
+      <c r="B339" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C339" s="4" t="s">
+        <v>1554</v>
+      </c>
+      <c r="D339" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E339" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F339" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G339" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H339" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I339" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J339" s="4" t="s">
+        <v>1555</v>
+      </c>
+      <c r="K339" s="4" t="s">
+        <v>1556</v>
+      </c>
+      <c r="L339" s="6" t="s">
+        <v>1045</v>
+      </c>
+    </row>
+    <row r="340" spans="1:12" ht="72" customHeight="1">
+      <c r="A340" s="4" t="s">
+        <v>1557</v>
+      </c>
+      <c r="B340" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C340" s="4" t="s">
+        <v>1558</v>
+      </c>
+      <c r="D340" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E340" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F340" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G340" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H340" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I340" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J340" s="4" t="s">
+        <v>1559</v>
+      </c>
+      <c r="K340" s="4" t="s">
+        <v>1560</v>
+      </c>
+      <c r="L340" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="341" spans="1:12" ht="72" customHeight="1">
+      <c r="A341" s="4" t="s">
+        <v>1561</v>
+      </c>
+      <c r="B341" s="4" t="s">
+        <v>1532</v>
+      </c>
+      <c r="C341" s="4" t="s">
+        <v>1562</v>
+      </c>
+      <c r="D341" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E341" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F341" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G341" s="4" t="s">
+        <v>1534</v>
+      </c>
+      <c r="H341" s="4" t="s">
+        <v>1535</v>
+      </c>
+      <c r="I341" s="4" t="s">
+        <v>1536</v>
+      </c>
+      <c r="J341" s="4" t="s">
+        <v>1563</v>
+      </c>
+      <c r="K341" s="4" t="s">
+        <v>1564</v>
+      </c>
+      <c r="L341" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F333">
+  <conditionalFormatting sqref="E2:F341">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -39372,11 +39757,19 @@
     <hyperlink ref="L331" r:id="rId330"/>
     <hyperlink ref="L332" r:id="rId331"/>
     <hyperlink ref="L333" r:id="rId332"/>
+    <hyperlink ref="L334" r:id="rId333"/>
+    <hyperlink ref="L335" r:id="rId334"/>
+    <hyperlink ref="L336" r:id="rId335"/>
+    <hyperlink ref="L337" r:id="rId336"/>
+    <hyperlink ref="L338" r:id="rId337"/>
+    <hyperlink ref="L339" r:id="rId338"/>
+    <hyperlink ref="L340" r:id="rId339"/>
+    <hyperlink ref="L341" r:id="rId340"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId333"/>
+    <tablePart r:id="rId341"/>
   </tableParts>
 </worksheet>
 </file>
@@ -39393,3128 +39786,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>2360</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>2361</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>2362</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>2356</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>2357</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>2358</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>2206</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>2359</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>2353</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>2354</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>1499</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>1524</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>1535</v>
+        <v>1538</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>1563</v>
+        <v>1566</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>2507</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2209</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2508</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2504</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>2206</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2505</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2501</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2554</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2555</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2556</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2234</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>2551</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>2026</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="H85" s="4" t="s">
+        <v>2558</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2552</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2553</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2231</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2554</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2548</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2555</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2549</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2557</v>
+        <v>2560</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2558</v>
+        <v>2561</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2150</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2598</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2151</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>2594</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2147</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="F95" s="4" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2595</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>2148</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2591</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2146</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2592</v>
-      </c>
       <c r="I95" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
+        <v>2599</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2594</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>2177</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>2595</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>2596</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>2597</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>2151</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>2591</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2149</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>2174</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>2592</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>2593</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2600</v>
+        <v>2603</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10539" uniqueCount="2607">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10614" uniqueCount="2610">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 09:00 BST</t>
+    <t>Snapshot: 07 September 2026, 09:14 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4725,6 +4725,15 @@
   </si>
   <si>
     <t>Result, scope and period controls</t>
+  </si>
+  <si>
+    <t>Full shared five-board UI; exact scope/period/source/evidence/sort/search URLs; original ranks retained through search; query guards exclude unverified/inactive/private outsider boards; distinct board leaders, no invented global rank. TypeScript/scoped lintpass. Actual12matrix PASS1.1m leaderboards-browser-final; initial sort wiring smoke4cases PASS25.7s leaderboards-sort-final.</t>
+  </si>
+  <si>
+    <t>All five boards reachable, advanced filter drawer Apply/Reset, full player/challenge/course/tournament details in panel; original desktop table fields retained and no fabricated movement.390/360+1023/1024 both surfaces exercised, plus1440/1280. 390 screenshot inspected. Matrices under output/playwright/ui-upgrade.</t>
+  </si>
+  <si>
+    <t>Full acceptance pending: positive multi-player/tie/provider/champion/partial-event browser fixtures; query guards not yet directly browser-tested with malicious scope fixtures; full saved views/column-density/export parity on mobile cards, large profile pagination (public first100candidates; course/tournament12boards), focus/AT/zoom/themes/loading/errors. Initial native hydration selection reverted; guarded fields. Earlier ready matrix overlapped concurrent service edit; stable final repeated successfully.</t>
   </si>
   <si>
     <t>Copied URLs reproduce the same authorised standings.</t>
@@ -8014,8 +8023,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L341" totalsRowShown="0">
-  <autoFilter ref="A1:L341"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L346" totalsRowShown="0">
+  <autoFilter ref="A1:L346"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8409,11 +8418,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>333</v>
+        <v>338</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8448,11 +8457,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -21526,16 +21535,25 @@
         <v>42</v>
       </c>
       <c r="E342" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F342" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G342" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H342" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I342" s="4" t="s">
+        <v>1570</v>
       </c>
       <c r="J342" s="4" t="s">
-        <v>1568</v>
+        <v>1571</v>
       </c>
       <c r="K342" s="4" t="s">
-        <v>1569</v>
+        <v>1572</v>
       </c>
       <c r="L342" s="6" t="s">
         <v>147</v>
@@ -21543,28 +21561,37 @@
     </row>
     <row r="343" spans="1:12" ht="72" customHeight="1">
       <c r="A343" s="4" t="s">
-        <v>1570</v>
+        <v>1573</v>
       </c>
       <c r="B343" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C343" s="4" t="s">
-        <v>1571</v>
+        <v>1574</v>
       </c>
       <c r="D343" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E343" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F343" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G343" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H343" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>1570</v>
       </c>
       <c r="J343" s="4" t="s">
-        <v>1572</v>
+        <v>1575</v>
       </c>
       <c r="K343" s="4" t="s">
-        <v>1573</v>
+        <v>1576</v>
       </c>
       <c r="L343" s="6" t="s">
         <v>88</v>
@@ -21572,28 +21599,37 @@
     </row>
     <row r="344" spans="1:12" ht="72" customHeight="1">
       <c r="A344" s="4" t="s">
-        <v>1574</v>
+        <v>1577</v>
       </c>
       <c r="B344" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C344" s="4" t="s">
-        <v>1575</v>
+        <v>1578</v>
       </c>
       <c r="D344" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E344" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F344" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G344" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>1570</v>
       </c>
       <c r="J344" s="4" t="s">
-        <v>1576</v>
+        <v>1579</v>
       </c>
       <c r="K344" s="4" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="L344" s="6" t="s">
         <v>88</v>
@@ -21601,28 +21637,37 @@
     </row>
     <row r="345" spans="1:12" ht="72" customHeight="1">
       <c r="A345" s="4" t="s">
-        <v>1578</v>
+        <v>1581</v>
       </c>
       <c r="B345" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C345" s="4" t="s">
-        <v>1579</v>
+        <v>1582</v>
       </c>
       <c r="D345" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E345" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F345" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G345" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H345" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I345" s="4" t="s">
+        <v>1570</v>
       </c>
       <c r="J345" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="K345" s="4" t="s">
         <v>1580</v>
-      </c>
-      <c r="K345" s="4" t="s">
-        <v>1577</v>
       </c>
       <c r="L345" s="6" t="s">
         <v>88</v>
@@ -21630,28 +21675,37 @@
     </row>
     <row r="346" spans="1:12" ht="72" customHeight="1">
       <c r="A346" s="4" t="s">
-        <v>1581</v>
+        <v>1584</v>
       </c>
       <c r="B346" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C346" s="4" t="s">
-        <v>1582</v>
+        <v>1585</v>
       </c>
       <c r="D346" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E346" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F346" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G346" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H346" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I346" s="4" t="s">
+        <v>1570</v>
       </c>
       <c r="J346" s="4" t="s">
-        <v>1583</v>
+        <v>1586</v>
       </c>
       <c r="K346" s="4" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="L346" s="6" t="s">
         <v>88</v>
@@ -21659,13 +21713,13 @@
     </row>
     <row r="347" spans="1:12" ht="72" customHeight="1">
       <c r="A347" s="4" t="s">
-        <v>1584</v>
+        <v>1587</v>
       </c>
       <c r="B347" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C347" s="4" t="s">
-        <v>1586</v>
+        <v>1589</v>
       </c>
       <c r="D347" s="4" t="s">
         <v>42</v>
@@ -21677,10 +21731,10 @@
         <v>9</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1587</v>
+        <v>1590</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21688,13 +21742,13 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1589</v>
+        <v>1592</v>
       </c>
       <c r="B348" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
@@ -21706,10 +21760,10 @@
         <v>9</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21717,13 +21771,13 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="B349" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
@@ -21735,10 +21789,10 @@
         <v>9</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21746,13 +21800,13 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="B350" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
@@ -21764,10 +21818,10 @@
         <v>9</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21775,13 +21829,13 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="B351" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
@@ -21793,24 +21847,24 @@
         <v>9</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1588</v>
+        <v>1591</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="B352" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
@@ -21822,10 +21876,10 @@
         <v>9</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21833,13 +21887,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21851,10 +21905,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21862,13 +21916,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21880,10 +21934,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21891,13 +21945,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21909,10 +21963,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21920,13 +21974,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21938,10 +21992,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -21949,13 +22003,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -21967,10 +22021,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -21978,13 +22032,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -21996,10 +22050,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -22007,13 +22061,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -22025,10 +22079,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
+        <v>1639</v>
+      </c>
+      <c r="K359" s="4" t="s">
         <v>1636</v>
-      </c>
-      <c r="K359" s="4" t="s">
-        <v>1633</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -22036,13 +22090,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -22054,10 +22108,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -22065,13 +22119,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -22083,10 +22137,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -22094,13 +22148,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -22112,10 +22166,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -22123,13 +22177,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -22141,10 +22195,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
+        <v>1655</v>
+      </c>
+      <c r="K363" s="4" t="s">
         <v>1652</v>
-      </c>
-      <c r="K363" s="4" t="s">
-        <v>1649</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -22152,13 +22206,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -22170,10 +22224,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -22181,13 +22235,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22199,10 +22253,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22210,13 +22264,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22228,10 +22282,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22239,13 +22293,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22257,10 +22311,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22268,13 +22322,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22286,10 +22340,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22297,13 +22351,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22315,10 +22369,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22326,13 +22380,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22344,10 +22398,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22355,13 +22409,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22373,10 +22427,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22384,13 +22438,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22402,10 +22456,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22413,13 +22467,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22431,10 +22485,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22442,13 +22496,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22460,10 +22514,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22471,13 +22525,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22489,10 +22543,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22500,13 +22554,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22518,10 +22572,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22529,13 +22583,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22547,10 +22601,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22558,13 +22612,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22576,10 +22630,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22587,13 +22641,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22605,10 +22659,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22616,13 +22670,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22634,10 +22688,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22645,13 +22699,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22663,10 +22717,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22674,13 +22728,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22692,24 +22746,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22721,10 +22775,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22732,13 +22786,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22750,10 +22804,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22761,13 +22815,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22779,10 +22833,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22790,13 +22844,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22808,10 +22862,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
+        <v>1744</v>
+      </c>
+      <c r="K386" s="4" t="s">
         <v>1741</v>
-      </c>
-      <c r="K386" s="4" t="s">
-        <v>1738</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22819,13 +22873,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22837,10 +22891,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22848,13 +22902,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22866,10 +22920,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22877,13 +22931,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22895,10 +22949,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
+        <v>1756</v>
+      </c>
+      <c r="K389" s="4" t="s">
         <v>1753</v>
-      </c>
-      <c r="K389" s="4" t="s">
-        <v>1750</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22906,13 +22960,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22924,24 +22978,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -22953,10 +23007,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -22964,13 +23018,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -22982,24 +23036,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -23011,10 +23065,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -23022,13 +23076,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -23040,10 +23094,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -23051,13 +23105,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -23069,24 +23123,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -23098,10 +23152,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -23109,13 +23163,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -23127,10 +23181,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -23138,13 +23192,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -23156,10 +23210,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -23167,13 +23221,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23185,10 +23239,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23196,13 +23250,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23214,10 +23268,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23225,13 +23279,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23243,10 +23297,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
+        <v>1798</v>
+      </c>
+      <c r="K401" s="4" t="s">
         <v>1795</v>
-      </c>
-      <c r="K401" s="4" t="s">
-        <v>1792</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23254,13 +23308,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23272,10 +23326,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23283,13 +23337,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23301,24 +23355,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23330,10 +23384,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23341,13 +23395,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23359,10 +23413,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23370,13 +23424,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23388,10 +23442,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23399,13 +23453,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23417,10 +23471,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23428,13 +23482,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23446,10 +23500,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
+        <v>1828</v>
+      </c>
+      <c r="K408" s="4" t="s">
         <v>1825</v>
-      </c>
-      <c r="K408" s="4" t="s">
-        <v>1822</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23457,13 +23511,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23475,10 +23529,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23486,13 +23540,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23504,10 +23558,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23515,13 +23569,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23533,24 +23587,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23562,10 +23616,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23573,13 +23627,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23591,10 +23645,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23602,13 +23656,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23620,10 +23674,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23631,13 +23685,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23649,10 +23703,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23660,13 +23714,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23678,10 +23732,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23689,13 +23743,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23707,10 +23761,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23718,13 +23772,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23736,10 +23790,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
+        <v>1867</v>
+      </c>
+      <c r="K418" s="4" t="s">
         <v>1864</v>
-      </c>
-      <c r="K418" s="4" t="s">
-        <v>1861</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23747,13 +23801,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23765,10 +23819,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1867</v>
+        <v>1870</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23776,13 +23830,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23794,10 +23848,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23805,13 +23859,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23823,10 +23877,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23834,13 +23888,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23852,10 +23906,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23863,13 +23917,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23881,10 +23935,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23892,13 +23946,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23910,10 +23964,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23921,13 +23975,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23939,10 +23993,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -23950,13 +24004,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -23968,10 +24022,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -23979,13 +24033,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -23997,10 +24051,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
+        <v>1904</v>
+      </c>
+      <c r="K427" s="4" t="s">
         <v>1901</v>
-      </c>
-      <c r="K427" s="4" t="s">
-        <v>1898</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -24008,13 +24062,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -24026,10 +24080,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -24037,13 +24091,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -24055,10 +24109,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -24066,13 +24120,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -24084,10 +24138,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -24095,13 +24149,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -24113,10 +24167,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -24124,13 +24178,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -24142,10 +24196,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -24153,13 +24207,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -24171,10 +24225,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -24182,13 +24236,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24200,10 +24254,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24211,13 +24265,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24229,10 +24283,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24240,13 +24294,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24258,10 +24312,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24269,13 +24323,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24287,10 +24341,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24298,13 +24352,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24316,10 +24370,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24327,13 +24381,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24345,10 +24399,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
+        <v>1953</v>
+      </c>
+      <c r="K439" s="4" t="s">
         <v>1950</v>
-      </c>
-      <c r="K439" s="4" t="s">
-        <v>1947</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24356,13 +24410,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24374,10 +24428,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24385,13 +24439,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24403,10 +24457,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24414,13 +24468,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24432,10 +24486,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24443,13 +24497,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24461,10 +24515,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24472,13 +24526,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24490,10 +24544,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24501,13 +24555,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24519,10 +24573,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24530,13 +24584,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24548,10 +24602,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24559,13 +24613,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24577,10 +24631,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24588,13 +24642,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24606,10 +24660,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24617,13 +24671,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24635,10 +24689,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24646,13 +24700,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24664,10 +24718,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24675,13 +24729,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24693,10 +24747,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24704,13 +24758,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24722,10 +24776,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24733,13 +24787,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24751,10 +24805,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24762,13 +24816,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24780,10 +24834,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24791,13 +24845,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24809,10 +24863,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24820,13 +24874,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24838,24 +24892,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24867,10 +24921,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24878,13 +24932,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24896,10 +24950,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24907,13 +24961,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24925,10 +24979,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24936,13 +24990,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -24954,10 +25008,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -24965,13 +25019,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -24983,10 +25037,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -24994,13 +25048,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -25012,10 +25066,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -25023,13 +25077,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -25041,10 +25095,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -25052,13 +25106,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -25070,10 +25124,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -25081,13 +25135,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -25099,10 +25153,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
+        <v>2055</v>
+      </c>
+      <c r="K465" s="4" t="s">
         <v>2052</v>
-      </c>
-      <c r="K465" s="4" t="s">
-        <v>2049</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -25110,13 +25164,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -25128,10 +25182,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -25139,13 +25193,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -25157,10 +25211,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -25168,13 +25222,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25186,10 +25240,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
+        <v>2066</v>
+      </c>
+      <c r="K468" s="4" t="s">
         <v>2063</v>
-      </c>
-      <c r="K468" s="4" t="s">
-        <v>2060</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25197,13 +25251,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25215,10 +25269,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25226,13 +25280,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25244,10 +25298,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25255,13 +25309,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25273,10 +25327,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25284,13 +25338,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25302,10 +25356,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25313,13 +25367,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25331,10 +25385,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25342,13 +25396,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25360,10 +25414,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25371,13 +25425,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25389,10 +25443,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25400,13 +25454,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25418,10 +25472,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
+        <v>2099</v>
+      </c>
+      <c r="K476" s="4" t="s">
         <v>2096</v>
-      </c>
-      <c r="K476" s="4" t="s">
-        <v>2093</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25429,13 +25483,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25447,10 +25501,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2099</v>
+        <v>2102</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25458,13 +25512,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25476,10 +25530,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25487,13 +25541,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25505,10 +25559,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25516,13 +25570,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25534,10 +25588,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25545,13 +25599,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25563,10 +25617,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25574,13 +25628,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25592,10 +25646,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25603,13 +25657,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25621,10 +25675,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25632,13 +25686,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25650,10 +25704,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25661,13 +25715,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25679,10 +25733,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25690,13 +25744,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25708,10 +25762,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25719,13 +25773,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25737,10 +25791,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25748,13 +25802,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25766,10 +25820,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25777,13 +25831,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>2149</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>2146</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25795,10 +25849,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25806,13 +25860,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2152</v>
+        <v>2155</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2153</v>
+        <v>2156</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25824,10 +25878,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25835,13 +25889,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25853,10 +25907,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25864,13 +25918,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25882,10 +25936,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25893,13 +25947,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25911,10 +25965,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26445,7 +26499,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L341"/>
+  <dimension ref="A1:L346"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -39406,8 +39460,198 @@
         <v>103</v>
       </c>
     </row>
+    <row r="342" spans="1:12" ht="72" customHeight="1">
+      <c r="A342" s="4" t="s">
+        <v>1565</v>
+      </c>
+      <c r="B342" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C342" s="4" t="s">
+        <v>1567</v>
+      </c>
+      <c r="D342" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E342" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F342" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G342" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H342" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I342" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J342" s="4" t="s">
+        <v>1571</v>
+      </c>
+      <c r="K342" s="4" t="s">
+        <v>1572</v>
+      </c>
+      <c r="L342" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="343" spans="1:12" ht="72" customHeight="1">
+      <c r="A343" s="4" t="s">
+        <v>1573</v>
+      </c>
+      <c r="B343" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C343" s="4" t="s">
+        <v>1574</v>
+      </c>
+      <c r="D343" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E343" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F343" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G343" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H343" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I343" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J343" s="4" t="s">
+        <v>1575</v>
+      </c>
+      <c r="K343" s="4" t="s">
+        <v>1576</v>
+      </c>
+      <c r="L343" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="344" spans="1:12" ht="72" customHeight="1">
+      <c r="A344" s="4" t="s">
+        <v>1577</v>
+      </c>
+      <c r="B344" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C344" s="4" t="s">
+        <v>1578</v>
+      </c>
+      <c r="D344" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E344" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F344" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G344" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H344" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I344" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J344" s="4" t="s">
+        <v>1579</v>
+      </c>
+      <c r="K344" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L344" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="345" spans="1:12" ht="72" customHeight="1">
+      <c r="A345" s="4" t="s">
+        <v>1581</v>
+      </c>
+      <c r="B345" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C345" s="4" t="s">
+        <v>1582</v>
+      </c>
+      <c r="D345" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E345" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F345" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G345" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H345" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I345" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J345" s="4" t="s">
+        <v>1583</v>
+      </c>
+      <c r="K345" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L345" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="346" spans="1:12" ht="72" customHeight="1">
+      <c r="A346" s="4" t="s">
+        <v>1584</v>
+      </c>
+      <c r="B346" s="4" t="s">
+        <v>1566</v>
+      </c>
+      <c r="C346" s="4" t="s">
+        <v>1585</v>
+      </c>
+      <c r="D346" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E346" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F346" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G346" s="4" t="s">
+        <v>1568</v>
+      </c>
+      <c r="H346" s="4" t="s">
+        <v>1569</v>
+      </c>
+      <c r="I346" s="4" t="s">
+        <v>1570</v>
+      </c>
+      <c r="J346" s="4" t="s">
+        <v>1586</v>
+      </c>
+      <c r="K346" s="4" t="s">
+        <v>1580</v>
+      </c>
+      <c r="L346" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F341">
+  <conditionalFormatting sqref="E2:F346">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -39765,11 +40009,16 @@
     <hyperlink ref="L339" r:id="rId338"/>
     <hyperlink ref="L340" r:id="rId339"/>
     <hyperlink ref="L341" r:id="rId340"/>
+    <hyperlink ref="L342" r:id="rId341"/>
+    <hyperlink ref="L343" r:id="rId342"/>
+    <hyperlink ref="L344" r:id="rId343"/>
+    <hyperlink ref="L345" r:id="rId344"/>
+    <hyperlink ref="L346" r:id="rId345"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId341"/>
+    <tablePart r:id="rId346"/>
   </tableParts>
 </worksheet>
 </file>
@@ -39786,3128 +40035,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>2363</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>2364</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>2365</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>2359</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>2360</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>2361</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>2209</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>2362</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>2356</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>2357</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>2363</v>
+        <v>2366</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2364</v>
+        <v>2367</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2365</v>
+        <v>2368</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>1499</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>1524</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>1538</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>1577</v>
+        <v>1580</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>1585</v>
+        <v>1588</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>2510</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2212</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2511</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2507</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>2209</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2508</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2504</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2510</v>
+        <v>2513</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2511</v>
+        <v>2514</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2557</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2032</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2559</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2237</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>2554</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>2029</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="H85" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2555</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2556</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2234</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2557</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2551</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2558</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2552</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2559</v>
+        <v>2562</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2560</v>
+        <v>2563</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2561</v>
+        <v>2564</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2153</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2154</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>2597</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2150</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="F95" s="4" t="s">
+        <v>2152</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2598</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>2151</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2594</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2149</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2595</v>
-      </c>
       <c r="I95" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
+        <v>2602</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2597</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>2180</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>2598</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>2599</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>2600</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>2154</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>2594</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2152</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>2177</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>2595</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>2596</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2601</v>
+        <v>2604</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2602</v>
+        <v>2605</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2603</v>
+        <v>2606</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10614" uniqueCount="2610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10704" uniqueCount="2613">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 09:14 BST</t>
+    <t>Snapshot: 07 September 2026, 09:28 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4791,6 +4791,15 @@
   </si>
   <si>
     <t>Level, XP and next unlock summary</t>
+  </si>
+  <si>
+    <t>Shared full achievements workspace; adaptive exact XP/unlock metrics, full catalogue, native badge detail action with date/source, ledger and real date events, owner-only share field preview/download recovery. Isolated1200/1201unlock60000XP fixture all12 PASS52.9s achievements-fixture-final; actual route1440/390bothsurfaces PASS45.7s achievements-route. Types/lintpass; provenance8+shareendpoint3tests pass.</t>
+  </si>
+  <si>
+    <t>Full ledger cards with all evidence, staged filter drawer, same full catalogue instead of first12only, readable native date picker plus day events, full share confirmation/cancel/failure/retry.390/360/1023/1024 exercised on both surfaces. Synthetic390 and actual1440 screenshots inspected. Breakpoint metric clipping found and fixed with auto-fit.</t>
+  </si>
+  <si>
+    <t>Full acceptance pending: real positive unlock/source/XP-ledger reconciliation, repeatable awards, modelled-vs-measured achievement eligibility unchanged, real SVG long-text layout/download system completion, URLfocus/source/deleted/sharepermission regression, saved views/column-density mobile parity, AT/zoom/themes/nativekeyboard/syncfailure. Isolated uses mocked actions/share endpoint and fallback fonts; actualroute fixture empty user. Final Clear all includes completed and download-start/ledger copy refinements after browser runs; types/lintpass. Native date picker is complete date/list alternative; desktop calendar retained.</t>
   </si>
   <si>
     <t>Large counts such as four-digit numerators render without clipping at every required width.</t>
@@ -8023,8 +8032,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L346" totalsRowShown="0">
-  <autoFilter ref="A1:L346"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L352" totalsRowShown="0">
+  <autoFilter ref="A1:L352"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8418,11 +8427,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>338</v>
+        <v>344</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8457,11 +8466,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>147</v>
+        <v>141</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -21725,16 +21734,25 @@
         <v>42</v>
       </c>
       <c r="E347" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F347" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G347" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H347" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I347" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J347" s="4" t="s">
-        <v>1590</v>
+        <v>1593</v>
       </c>
       <c r="K347" s="4" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="L347" s="6" t="s">
         <v>159</v>
@@ -21742,28 +21760,37 @@
     </row>
     <row r="348" spans="1:12" ht="72" customHeight="1">
       <c r="A348" s="4" t="s">
-        <v>1592</v>
+        <v>1595</v>
       </c>
       <c r="B348" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C348" s="4" t="s">
-        <v>1593</v>
+        <v>1596</v>
       </c>
       <c r="D348" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E348" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F348" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G348" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H348" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I348" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J348" s="4" t="s">
-        <v>1594</v>
+        <v>1597</v>
       </c>
       <c r="K348" s="4" t="s">
-        <v>1595</v>
+        <v>1598</v>
       </c>
       <c r="L348" s="6" t="s">
         <v>165</v>
@@ -21771,28 +21798,37 @@
     </row>
     <row r="349" spans="1:12" ht="72" customHeight="1">
       <c r="A349" s="4" t="s">
-        <v>1596</v>
+        <v>1599</v>
       </c>
       <c r="B349" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C349" s="4" t="s">
-        <v>1597</v>
+        <v>1600</v>
       </c>
       <c r="D349" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E349" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F349" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G349" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H349" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J349" s="4" t="s">
-        <v>1598</v>
+        <v>1601</v>
       </c>
       <c r="K349" s="4" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="L349" s="6" t="s">
         <v>147</v>
@@ -21800,28 +21836,37 @@
     </row>
     <row r="350" spans="1:12" ht="72" customHeight="1">
       <c r="A350" s="4" t="s">
-        <v>1599</v>
+        <v>1602</v>
       </c>
       <c r="B350" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C350" s="4" t="s">
-        <v>1600</v>
+        <v>1603</v>
       </c>
       <c r="D350" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E350" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F350" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G350" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H350" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I350" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J350" s="4" t="s">
-        <v>1601</v>
+        <v>1604</v>
       </c>
       <c r="K350" s="4" t="s">
-        <v>1602</v>
+        <v>1605</v>
       </c>
       <c r="L350" s="6" t="s">
         <v>88</v>
@@ -21829,57 +21874,75 @@
     </row>
     <row r="351" spans="1:12" ht="72" customHeight="1">
       <c r="A351" s="4" t="s">
-        <v>1603</v>
+        <v>1606</v>
       </c>
       <c r="B351" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C351" s="4" t="s">
-        <v>1604</v>
+        <v>1607</v>
       </c>
       <c r="D351" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E351" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F351" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G351" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H351" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I351" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J351" s="4" t="s">
-        <v>1605</v>
+        <v>1608</v>
       </c>
       <c r="K351" s="4" t="s">
-        <v>1591</v>
+        <v>1594</v>
       </c>
       <c r="L351" s="6" t="s">
-        <v>1606</v>
+        <v>1609</v>
       </c>
     </row>
     <row r="352" spans="1:12" ht="72" customHeight="1">
       <c r="A352" s="4" t="s">
-        <v>1607</v>
+        <v>1610</v>
       </c>
       <c r="B352" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C352" s="4" t="s">
-        <v>1608</v>
+        <v>1611</v>
       </c>
       <c r="D352" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E352" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F352" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G352" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>1592</v>
       </c>
       <c r="J352" s="4" t="s">
-        <v>1609</v>
+        <v>1612</v>
       </c>
       <c r="K352" s="4" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="L352" s="6" t="s">
         <v>103</v>
@@ -21887,13 +21950,13 @@
     </row>
     <row r="353" spans="1:12" ht="72" customHeight="1">
       <c r="A353" s="4" t="s">
-        <v>1611</v>
+        <v>1614</v>
       </c>
       <c r="B353" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C353" s="4" t="s">
-        <v>1613</v>
+        <v>1616</v>
       </c>
       <c r="D353" s="4" t="s">
         <v>42</v>
@@ -21905,10 +21968,10 @@
         <v>9</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1614</v>
+        <v>1617</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1615</v>
+        <v>1618</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21916,13 +21979,13 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1616</v>
+        <v>1619</v>
       </c>
       <c r="B354" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
@@ -21934,10 +21997,10 @@
         <v>9</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -21945,13 +22008,13 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="B355" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
@@ -21963,10 +22026,10 @@
         <v>9</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -21974,13 +22037,13 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="B356" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
@@ -21992,10 +22055,10 @@
         <v>9</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -22003,13 +22066,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -22021,10 +22084,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -22032,13 +22095,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -22050,10 +22113,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -22061,13 +22124,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -22079,10 +22142,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
+        <v>1642</v>
+      </c>
+      <c r="K359" s="4" t="s">
         <v>1639</v>
-      </c>
-      <c r="K359" s="4" t="s">
-        <v>1636</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -22090,13 +22153,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -22108,10 +22171,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1642</v>
+        <v>1645</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -22119,13 +22182,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -22137,10 +22200,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -22148,13 +22211,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -22166,10 +22229,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -22177,13 +22240,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -22195,10 +22258,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
+        <v>1658</v>
+      </c>
+      <c r="K363" s="4" t="s">
         <v>1655</v>
-      </c>
-      <c r="K363" s="4" t="s">
-        <v>1652</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -22206,13 +22269,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -22224,10 +22287,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1658</v>
+        <v>1661</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -22235,13 +22298,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22253,10 +22316,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22264,13 +22327,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22282,10 +22345,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22293,13 +22356,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22311,10 +22374,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22322,13 +22385,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22340,10 +22403,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22351,13 +22414,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22369,10 +22432,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22380,13 +22443,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22398,10 +22461,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22409,13 +22472,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22427,10 +22490,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22438,13 +22501,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22456,10 +22519,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22467,13 +22530,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22485,10 +22548,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22496,13 +22559,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22514,10 +22577,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22525,13 +22588,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22543,10 +22606,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22554,13 +22617,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22572,10 +22635,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22583,13 +22646,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22601,10 +22664,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22612,13 +22675,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22630,10 +22693,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22641,13 +22704,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22659,10 +22722,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22670,13 +22733,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22688,10 +22751,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22699,13 +22762,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22717,10 +22780,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22728,13 +22791,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22746,24 +22809,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22775,10 +22838,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22786,13 +22849,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22804,10 +22867,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22815,13 +22878,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22833,10 +22896,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22844,13 +22907,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22862,10 +22925,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
+        <v>1747</v>
+      </c>
+      <c r="K386" s="4" t="s">
         <v>1744</v>
-      </c>
-      <c r="K386" s="4" t="s">
-        <v>1741</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22873,13 +22936,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22891,10 +22954,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1747</v>
+        <v>1750</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22902,13 +22965,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22920,10 +22983,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22931,13 +22994,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -22949,10 +23012,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
+        <v>1759</v>
+      </c>
+      <c r="K389" s="4" t="s">
         <v>1756</v>
-      </c>
-      <c r="K389" s="4" t="s">
-        <v>1753</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -22960,13 +23023,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -22978,24 +23041,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1759</v>
+        <v>1762</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -23007,10 +23070,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -23018,13 +23081,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -23036,24 +23099,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -23065,10 +23128,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -23076,13 +23139,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -23094,10 +23157,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -23105,13 +23168,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -23123,24 +23186,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -23152,10 +23215,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -23163,13 +23226,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -23181,10 +23244,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -23192,13 +23255,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -23210,10 +23273,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -23221,13 +23284,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23239,10 +23302,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23250,13 +23313,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23268,10 +23331,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23279,13 +23342,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23297,10 +23360,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
+        <v>1801</v>
+      </c>
+      <c r="K401" s="4" t="s">
         <v>1798</v>
-      </c>
-      <c r="K401" s="4" t="s">
-        <v>1795</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23308,13 +23371,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1801</v>
+        <v>1804</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23326,10 +23389,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23337,13 +23400,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23355,24 +23418,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23384,10 +23447,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23395,13 +23458,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23413,10 +23476,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23424,13 +23487,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23442,10 +23505,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23453,13 +23516,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23471,10 +23534,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23482,13 +23545,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23500,10 +23563,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
+        <v>1831</v>
+      </c>
+      <c r="K408" s="4" t="s">
         <v>1828</v>
-      </c>
-      <c r="K408" s="4" t="s">
-        <v>1825</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23511,13 +23574,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23529,10 +23592,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1831</v>
+        <v>1834</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23540,13 +23603,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23558,10 +23621,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23569,13 +23632,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23587,24 +23650,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23616,10 +23679,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23627,13 +23690,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23645,10 +23708,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23656,13 +23719,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23674,10 +23737,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23685,13 +23748,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23703,10 +23766,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23714,13 +23777,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23732,10 +23795,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23743,13 +23806,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23761,10 +23824,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1864</v>
+        <v>1867</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23772,13 +23835,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23790,10 +23853,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
+        <v>1870</v>
+      </c>
+      <c r="K418" s="4" t="s">
         <v>1867</v>
-      </c>
-      <c r="K418" s="4" t="s">
-        <v>1864</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23801,13 +23864,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23819,10 +23882,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1870</v>
+        <v>1873</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23830,13 +23893,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23848,10 +23911,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23859,13 +23922,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23877,10 +23940,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23888,13 +23951,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23906,10 +23969,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23917,13 +23980,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23935,10 +23998,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -23946,13 +24009,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -23964,10 +24027,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -23975,13 +24038,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -23993,10 +24056,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -24004,13 +24067,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -24022,10 +24085,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -24033,13 +24096,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -24051,10 +24114,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
+        <v>1907</v>
+      </c>
+      <c r="K427" s="4" t="s">
         <v>1904</v>
-      </c>
-      <c r="K427" s="4" t="s">
-        <v>1901</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -24062,13 +24125,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -24080,10 +24143,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1907</v>
+        <v>1910</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -24091,13 +24154,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -24109,10 +24172,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -24120,13 +24183,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -24138,10 +24201,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -24149,13 +24212,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -24167,10 +24230,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -24178,13 +24241,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -24196,10 +24259,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -24207,13 +24270,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -24225,10 +24288,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -24236,13 +24299,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24254,10 +24317,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24265,13 +24328,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24283,10 +24346,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24294,13 +24357,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24312,10 +24375,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24323,13 +24386,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24341,10 +24404,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24352,13 +24415,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24370,10 +24433,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24381,13 +24444,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24399,10 +24462,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
+        <v>1956</v>
+      </c>
+      <c r="K439" s="4" t="s">
         <v>1953</v>
-      </c>
-      <c r="K439" s="4" t="s">
-        <v>1950</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24410,13 +24473,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24428,10 +24491,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1956</v>
+        <v>1959</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24439,13 +24502,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24457,10 +24520,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24468,13 +24531,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24486,10 +24549,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24497,13 +24560,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24515,10 +24578,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24526,13 +24589,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24544,10 +24607,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24555,13 +24618,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24573,10 +24636,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24584,13 +24647,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24602,10 +24665,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24613,13 +24676,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24631,10 +24694,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24642,13 +24705,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24660,10 +24723,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24671,13 +24734,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24689,10 +24752,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24700,13 +24763,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24718,10 +24781,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24729,13 +24792,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24747,10 +24810,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24758,13 +24821,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24776,10 +24839,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24787,13 +24850,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24805,10 +24868,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24816,13 +24879,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24834,10 +24897,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24845,13 +24908,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24863,10 +24926,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24874,13 +24937,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24892,24 +24955,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24921,10 +24984,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24932,13 +24995,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -24950,10 +25013,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -24961,13 +25024,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -24979,10 +25042,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -24990,13 +25053,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -25008,10 +25071,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -25019,13 +25082,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -25037,10 +25100,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -25048,13 +25111,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -25066,10 +25129,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -25077,13 +25140,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -25095,10 +25158,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -25106,13 +25169,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -25124,10 +25187,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -25135,13 +25198,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -25153,10 +25216,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
+        <v>2058</v>
+      </c>
+      <c r="K465" s="4" t="s">
         <v>2055</v>
-      </c>
-      <c r="K465" s="4" t="s">
-        <v>2052</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -25164,13 +25227,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -25182,10 +25245,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2058</v>
+        <v>2061</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -25193,13 +25256,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -25211,10 +25274,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -25222,13 +25285,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25240,10 +25303,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
+        <v>2069</v>
+      </c>
+      <c r="K468" s="4" t="s">
         <v>2066</v>
-      </c>
-      <c r="K468" s="4" t="s">
-        <v>2063</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25251,13 +25314,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25269,10 +25332,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2069</v>
+        <v>2072</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25280,13 +25343,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25298,10 +25361,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25309,13 +25372,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25327,10 +25390,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25338,13 +25401,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25356,10 +25419,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25367,13 +25430,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25385,10 +25448,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25396,13 +25459,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25414,10 +25477,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25425,13 +25488,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="B475" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C475" s="4" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="D475" s="4" t="s">
         <v>42</v>
@@ -25443,10 +25506,10 @@
         <v>9</v>
       </c>
       <c r="J475" s="4" t="s">
-        <v>2095</v>
+        <v>2098</v>
       </c>
       <c r="K475" s="4" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="L475" s="6" t="s">
         <v>39</v>
@@ -25454,13 +25517,13 @@
     </row>
     <row r="476" spans="1:12" ht="72" customHeight="1">
       <c r="A476" s="4" t="s">
-        <v>2097</v>
+        <v>2100</v>
       </c>
       <c r="B476" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C476" s="4" t="s">
-        <v>2098</v>
+        <v>2101</v>
       </c>
       <c r="D476" s="4" t="s">
         <v>42</v>
@@ -25472,10 +25535,10 @@
         <v>9</v>
       </c>
       <c r="J476" s="4" t="s">
+        <v>2102</v>
+      </c>
+      <c r="K476" s="4" t="s">
         <v>2099</v>
-      </c>
-      <c r="K476" s="4" t="s">
-        <v>2096</v>
       </c>
       <c r="L476" s="6" t="s">
         <v>88</v>
@@ -25483,13 +25546,13 @@
     </row>
     <row r="477" spans="1:12" ht="72" customHeight="1">
       <c r="A477" s="4" t="s">
-        <v>2100</v>
+        <v>2103</v>
       </c>
       <c r="B477" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C477" s="4" t="s">
-        <v>2101</v>
+        <v>2104</v>
       </c>
       <c r="D477" s="4" t="s">
         <v>42</v>
@@ -25501,10 +25564,10 @@
         <v>9</v>
       </c>
       <c r="J477" s="4" t="s">
-        <v>2102</v>
+        <v>2105</v>
       </c>
       <c r="K477" s="4" t="s">
-        <v>2096</v>
+        <v>2099</v>
       </c>
       <c r="L477" s="6" t="s">
         <v>110</v>
@@ -25512,13 +25575,13 @@
     </row>
     <row r="478" spans="1:12" ht="72" customHeight="1">
       <c r="A478" s="4" t="s">
-        <v>2103</v>
+        <v>2106</v>
       </c>
       <c r="B478" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C478" s="4" t="s">
-        <v>2105</v>
+        <v>2108</v>
       </c>
       <c r="D478" s="4" t="s">
         <v>42</v>
@@ -25530,10 +25593,10 @@
         <v>9</v>
       </c>
       <c r="J478" s="4" t="s">
-        <v>2106</v>
+        <v>2109</v>
       </c>
       <c r="K478" s="4" t="s">
-        <v>2107</v>
+        <v>2110</v>
       </c>
       <c r="L478" s="6" t="s">
         <v>39</v>
@@ -25541,13 +25604,13 @@
     </row>
     <row r="479" spans="1:12" ht="72" customHeight="1">
       <c r="A479" s="4" t="s">
-        <v>2108</v>
+        <v>2111</v>
       </c>
       <c r="B479" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C479" s="4" t="s">
-        <v>2109</v>
+        <v>2112</v>
       </c>
       <c r="D479" s="4" t="s">
         <v>42</v>
@@ -25559,10 +25622,10 @@
         <v>9</v>
       </c>
       <c r="J479" s="4" t="s">
-        <v>2110</v>
+        <v>2113</v>
       </c>
       <c r="K479" s="4" t="s">
-        <v>2111</v>
+        <v>2114</v>
       </c>
       <c r="L479" s="6" t="s">
         <v>95</v>
@@ -25570,13 +25633,13 @@
     </row>
     <row r="480" spans="1:12" ht="72" customHeight="1">
       <c r="A480" s="4" t="s">
-        <v>2112</v>
+        <v>2115</v>
       </c>
       <c r="B480" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C480" s="4" t="s">
-        <v>2113</v>
+        <v>2116</v>
       </c>
       <c r="D480" s="4" t="s">
         <v>42</v>
@@ -25588,10 +25651,10 @@
         <v>9</v>
       </c>
       <c r="J480" s="4" t="s">
-        <v>2114</v>
+        <v>2117</v>
       </c>
       <c r="K480" s="4" t="s">
-        <v>2115</v>
+        <v>2118</v>
       </c>
       <c r="L480" s="6" t="s">
         <v>110</v>
@@ -25599,13 +25662,13 @@
     </row>
     <row r="481" spans="1:12" ht="72" customHeight="1">
       <c r="A481" s="4" t="s">
-        <v>2116</v>
+        <v>2119</v>
       </c>
       <c r="B481" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="C481" s="4" t="s">
-        <v>2118</v>
+        <v>2121</v>
       </c>
       <c r="D481" s="4" t="s">
         <v>42</v>
@@ -25617,10 +25680,10 @@
         <v>9</v>
       </c>
       <c r="J481" s="4" t="s">
-        <v>2119</v>
+        <v>2122</v>
       </c>
       <c r="K481" s="4" t="s">
-        <v>2120</v>
+        <v>2123</v>
       </c>
       <c r="L481" s="6" t="s">
         <v>518</v>
@@ -25628,13 +25691,13 @@
     </row>
     <row r="482" spans="1:12" ht="72" customHeight="1">
       <c r="A482" s="4" t="s">
-        <v>2121</v>
+        <v>2124</v>
       </c>
       <c r="B482" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="C482" s="4" t="s">
-        <v>2122</v>
+        <v>2125</v>
       </c>
       <c r="D482" s="4" t="s">
         <v>42</v>
@@ -25646,10 +25709,10 @@
         <v>9</v>
       </c>
       <c r="J482" s="4" t="s">
-        <v>2123</v>
+        <v>2126</v>
       </c>
       <c r="K482" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="L482" s="6" t="s">
         <v>307</v>
@@ -25657,13 +25720,13 @@
     </row>
     <row r="483" spans="1:12" ht="72" customHeight="1">
       <c r="A483" s="4" t="s">
-        <v>2125</v>
+        <v>2128</v>
       </c>
       <c r="B483" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="C483" s="4" t="s">
-        <v>2126</v>
+        <v>2129</v>
       </c>
       <c r="D483" s="4" t="s">
         <v>42</v>
@@ -25675,10 +25738,10 @@
         <v>9</v>
       </c>
       <c r="J483" s="4" t="s">
-        <v>2127</v>
+        <v>2130</v>
       </c>
       <c r="K483" s="4" t="s">
-        <v>2128</v>
+        <v>2131</v>
       </c>
       <c r="L483" s="6" t="s">
         <v>110</v>
@@ -25686,13 +25749,13 @@
     </row>
     <row r="484" spans="1:12" ht="72" customHeight="1">
       <c r="A484" s="4" t="s">
-        <v>2129</v>
+        <v>2132</v>
       </c>
       <c r="B484" s="4" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C484" s="4" t="s">
-        <v>2131</v>
+        <v>2134</v>
       </c>
       <c r="D484" s="4" t="s">
         <v>32</v>
@@ -25704,10 +25767,10 @@
         <v>9</v>
       </c>
       <c r="J484" s="4" t="s">
-        <v>2132</v>
+        <v>2135</v>
       </c>
       <c r="K484" s="4" t="s">
-        <v>2133</v>
+        <v>2136</v>
       </c>
       <c r="L484" s="6" t="s">
         <v>165</v>
@@ -25715,13 +25778,13 @@
     </row>
     <row r="485" spans="1:12" ht="72" customHeight="1">
       <c r="A485" s="4" t="s">
-        <v>2134</v>
+        <v>2137</v>
       </c>
       <c r="B485" s="4" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C485" s="4" t="s">
-        <v>2135</v>
+        <v>2138</v>
       </c>
       <c r="D485" s="4" t="s">
         <v>32</v>
@@ -25733,10 +25796,10 @@
         <v>9</v>
       </c>
       <c r="J485" s="4" t="s">
-        <v>2136</v>
+        <v>2139</v>
       </c>
       <c r="K485" s="4" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="L485" s="6" t="s">
         <v>110</v>
@@ -25744,13 +25807,13 @@
     </row>
     <row r="486" spans="1:12" ht="72" customHeight="1">
       <c r="A486" s="4" t="s">
-        <v>2138</v>
+        <v>2141</v>
       </c>
       <c r="B486" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="C486" s="4" t="s">
-        <v>2140</v>
+        <v>2143</v>
       </c>
       <c r="D486" s="4" t="s">
         <v>42</v>
@@ -25762,10 +25825,10 @@
         <v>9</v>
       </c>
       <c r="J486" s="4" t="s">
-        <v>2141</v>
+        <v>2144</v>
       </c>
       <c r="K486" s="4" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="L486" s="6" t="s">
         <v>165</v>
@@ -25773,13 +25836,13 @@
     </row>
     <row r="487" spans="1:12" ht="72" customHeight="1">
       <c r="A487" s="4" t="s">
-        <v>2143</v>
+        <v>2146</v>
       </c>
       <c r="B487" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="C487" s="4" t="s">
-        <v>2144</v>
+        <v>2147</v>
       </c>
       <c r="D487" s="4" t="s">
         <v>42</v>
@@ -25791,10 +25854,10 @@
         <v>9</v>
       </c>
       <c r="J487" s="4" t="s">
-        <v>2145</v>
+        <v>2148</v>
       </c>
       <c r="K487" s="4" t="s">
-        <v>2146</v>
+        <v>2149</v>
       </c>
       <c r="L487" s="6" t="s">
         <v>165</v>
@@ -25802,13 +25865,13 @@
     </row>
     <row r="488" spans="1:12" ht="72" customHeight="1">
       <c r="A488" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="B488" s="4" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="C488" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D488" s="4" t="s">
         <v>42</v>
@@ -25820,10 +25883,10 @@
         <v>9</v>
       </c>
       <c r="J488" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K488" s="4" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="L488" s="6" t="s">
         <v>141</v>
@@ -25831,13 +25894,13 @@
     </row>
     <row r="489" spans="1:12" ht="72" customHeight="1">
       <c r="A489" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="B489" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C489" s="4" t="s">
         <v>2152</v>
-      </c>
-      <c r="B489" s="4" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C489" s="4" t="s">
-        <v>2149</v>
       </c>
       <c r="D489" s="4" t="s">
         <v>42</v>
@@ -25849,10 +25912,10 @@
         <v>9</v>
       </c>
       <c r="J489" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K489" s="4" t="s">
-        <v>2154</v>
+        <v>2157</v>
       </c>
       <c r="L489" s="6" t="s">
         <v>141</v>
@@ -25860,13 +25923,13 @@
     </row>
     <row r="490" spans="1:12" ht="72" customHeight="1">
       <c r="A490" s="4" t="s">
-        <v>2155</v>
+        <v>2158</v>
       </c>
       <c r="B490" s="4" t="s">
-        <v>2156</v>
+        <v>2159</v>
       </c>
       <c r="C490" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D490" s="4" t="s">
         <v>42</v>
@@ -25878,10 +25941,10 @@
         <v>9</v>
       </c>
       <c r="J490" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K490" s="4" t="s">
-        <v>2157</v>
+        <v>2160</v>
       </c>
       <c r="L490" s="6" t="s">
         <v>141</v>
@@ -25889,13 +25952,13 @@
     </row>
     <row r="491" spans="1:12" ht="72" customHeight="1">
       <c r="A491" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="B491" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C491" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D491" s="4" t="s">
         <v>42</v>
@@ -25907,10 +25970,10 @@
         <v>9</v>
       </c>
       <c r="J491" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K491" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="L491" s="6" t="s">
         <v>141</v>
@@ -25918,13 +25981,13 @@
     </row>
     <row r="492" spans="1:12" ht="72" customHeight="1">
       <c r="A492" s="4" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="B492" s="4" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="C492" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D492" s="4" t="s">
         <v>42</v>
@@ -25936,10 +25999,10 @@
         <v>9</v>
       </c>
       <c r="J492" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K492" s="4" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="L492" s="6" t="s">
         <v>141</v>
@@ -25947,13 +26010,13 @@
     </row>
     <row r="493" spans="1:12" ht="72" customHeight="1">
       <c r="A493" s="4" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="B493" s="4" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="C493" s="4" t="s">
-        <v>2149</v>
+        <v>2152</v>
       </c>
       <c r="D493" s="4" t="s">
         <v>42</v>
@@ -25965,10 +26028,10 @@
         <v>9</v>
       </c>
       <c r="J493" s="4" t="s">
-        <v>2150</v>
+        <v>2153</v>
       </c>
       <c r="K493" s="4" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="L493" s="6" t="s">
         <v>141</v>
@@ -26499,7 +26562,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L346"/>
+  <dimension ref="A1:L352"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" style="4" customWidth="1"/>
@@ -39650,8 +39713,236 @@
         <v>88</v>
       </c>
     </row>
+    <row r="347" spans="1:12" ht="72" customHeight="1">
+      <c r="A347" s="4" t="s">
+        <v>1587</v>
+      </c>
+      <c r="B347" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C347" s="4" t="s">
+        <v>1589</v>
+      </c>
+      <c r="D347" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E347" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F347" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G347" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H347" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I347" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J347" s="4" t="s">
+        <v>1593</v>
+      </c>
+      <c r="K347" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L347" s="6" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="348" spans="1:12" ht="72" customHeight="1">
+      <c r="A348" s="4" t="s">
+        <v>1595</v>
+      </c>
+      <c r="B348" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C348" s="4" t="s">
+        <v>1596</v>
+      </c>
+      <c r="D348" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E348" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F348" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G348" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H348" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I348" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J348" s="4" t="s">
+        <v>1597</v>
+      </c>
+      <c r="K348" s="4" t="s">
+        <v>1598</v>
+      </c>
+      <c r="L348" s="6" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="349" spans="1:12" ht="72" customHeight="1">
+      <c r="A349" s="4" t="s">
+        <v>1599</v>
+      </c>
+      <c r="B349" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C349" s="4" t="s">
+        <v>1600</v>
+      </c>
+      <c r="D349" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E349" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F349" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G349" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H349" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I349" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J349" s="4" t="s">
+        <v>1601</v>
+      </c>
+      <c r="K349" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L349" s="6" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="350" spans="1:12" ht="72" customHeight="1">
+      <c r="A350" s="4" t="s">
+        <v>1602</v>
+      </c>
+      <c r="B350" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C350" s="4" t="s">
+        <v>1603</v>
+      </c>
+      <c r="D350" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E350" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F350" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G350" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H350" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I350" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J350" s="4" t="s">
+        <v>1604</v>
+      </c>
+      <c r="K350" s="4" t="s">
+        <v>1605</v>
+      </c>
+      <c r="L350" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="351" spans="1:12" ht="72" customHeight="1">
+      <c r="A351" s="4" t="s">
+        <v>1606</v>
+      </c>
+      <c r="B351" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C351" s="4" t="s">
+        <v>1607</v>
+      </c>
+      <c r="D351" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E351" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F351" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G351" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H351" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I351" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J351" s="4" t="s">
+        <v>1608</v>
+      </c>
+      <c r="K351" s="4" t="s">
+        <v>1594</v>
+      </c>
+      <c r="L351" s="6" t="s">
+        <v>1609</v>
+      </c>
+    </row>
+    <row r="352" spans="1:12" ht="72" customHeight="1">
+      <c r="A352" s="4" t="s">
+        <v>1610</v>
+      </c>
+      <c r="B352" s="4" t="s">
+        <v>1588</v>
+      </c>
+      <c r="C352" s="4" t="s">
+        <v>1611</v>
+      </c>
+      <c r="D352" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="E352" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="F352" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="G352" s="4" t="s">
+        <v>1590</v>
+      </c>
+      <c r="H352" s="4" t="s">
+        <v>1591</v>
+      </c>
+      <c r="I352" s="4" t="s">
+        <v>1592</v>
+      </c>
+      <c r="J352" s="4" t="s">
+        <v>1612</v>
+      </c>
+      <c r="K352" s="4" t="s">
+        <v>1613</v>
+      </c>
+      <c r="L352" s="6" t="s">
+        <v>103</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="E2:F346">
+  <conditionalFormatting sqref="E2:F352">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
       <formula>"Implemented; partial verification"</formula>
     </cfRule>
@@ -40014,11 +40305,17 @@
     <hyperlink ref="L344" r:id="rId343"/>
     <hyperlink ref="L345" r:id="rId344"/>
     <hyperlink ref="L346" r:id="rId345"/>
+    <hyperlink ref="L347" r:id="rId346"/>
+    <hyperlink ref="L348" r:id="rId347"/>
+    <hyperlink ref="L349" r:id="rId348"/>
+    <hyperlink ref="L350" r:id="rId349"/>
+    <hyperlink ref="L351" r:id="rId350"/>
+    <hyperlink ref="L352" r:id="rId351"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup fitToHeight="0" orientation="landscape"/>
   <tableParts count="1">
-    <tablePart r:id="rId346"/>
+    <tablePart r:id="rId352"/>
   </tableParts>
 </worksheet>
 </file>
@@ -40035,3128 +40332,3128 @@
   <sheetData>
     <row r="1" spans="1:10">
       <c r="A1" s="3" t="s">
-        <v>2167</v>
+        <v>2170</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2168</v>
+        <v>2171</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>2169</v>
+        <v>2172</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>2170</v>
+        <v>2173</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>2171</v>
+        <v>2174</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>2172</v>
+        <v>2175</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>2173</v>
+        <v>2176</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>2174</v>
+        <v>2177</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>2175</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="4" t="s">
-        <v>2176</v>
+        <v>2179</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>128</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>2177</v>
+        <v>2180</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>134</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>2179</v>
+        <v>2182</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>2183</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="4" t="s">
-        <v>2184</v>
+        <v>2187</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>190</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>2185</v>
+        <v>2188</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>230</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>2187</v>
+        <v>2190</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>2188</v>
+        <v>2191</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="4" t="s">
-        <v>2189</v>
+        <v>2192</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>236</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>2190</v>
+        <v>2193</v>
       </c>
       <c r="D4" s="4" t="s">
         <v>241</v>
       </c>
       <c r="E4" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>2192</v>
+        <v>2195</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I4" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>2194</v>
+        <v>2197</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="4" t="s">
-        <v>2195</v>
+        <v>2198</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>269</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>2196</v>
+        <v>2199</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>2197</v>
+        <v>2200</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>2199</v>
+        <v>2202</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J5" s="4" t="s">
-        <v>2200</v>
+        <v>2203</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
-        <v>2201</v>
+        <v>2204</v>
       </c>
       <c r="B6" s="4" t="s">
         <v>292</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>2202</v>
+        <v>2205</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>306</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>2203</v>
+        <v>2206</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>2204</v>
+        <v>2207</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
-        <v>2205</v>
+        <v>2208</v>
       </c>
       <c r="B7" s="4" t="s">
         <v>325</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>2206</v>
+        <v>2209</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>342</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>2207</v>
+        <v>2210</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>2208</v>
+        <v>2211</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>347</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>2210</v>
+        <v>2213</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>2211</v>
+        <v>2214</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>2213</v>
+        <v>2216</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>2214</v>
+        <v>2217</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
-        <v>2215</v>
+        <v>2218</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>362</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>2216</v>
+        <v>2219</v>
       </c>
       <c r="D9" s="4" t="s">
         <v>368</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>2217</v>
+        <v>2220</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>2218</v>
+        <v>2221</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>2219</v>
+        <v>2222</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="4" t="s">
-        <v>2220</v>
+        <v>2223</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>422</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>2221</v>
+        <v>2224</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>2222</v>
+        <v>2225</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>2224</v>
+        <v>2227</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>2225</v>
+        <v>2228</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="4" t="s">
-        <v>2226</v>
+        <v>2229</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>445</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>2227</v>
+        <v>2230</v>
       </c>
       <c r="D11" s="4" t="s">
         <v>460</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>2228</v>
+        <v>2231</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>2229</v>
+        <v>2232</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="4" t="s">
-        <v>2230</v>
+        <v>2233</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>477</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>2231</v>
+        <v>2234</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>488</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>2232</v>
+        <v>2235</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>2233</v>
+        <v>2236</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="4" t="s">
-        <v>2234</v>
+        <v>2237</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>490</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>2235</v>
+        <v>2238</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>2236</v>
+        <v>2239</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>2238</v>
+        <v>2241</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>2239</v>
+        <v>2242</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="4" t="s">
-        <v>2240</v>
+        <v>2243</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>508</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>2241</v>
+        <v>2244</v>
       </c>
       <c r="D14" s="4" t="s">
         <v>513</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>2242</v>
+        <v>2245</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>2243</v>
+        <v>2246</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="4" t="s">
-        <v>2244</v>
+        <v>2247</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>541</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>2245</v>
+        <v>2248</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>546</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>2246</v>
+        <v>2249</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>2247</v>
+        <v>2250</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="4" t="s">
-        <v>2248</v>
+        <v>2251</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>557</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>2249</v>
+        <v>2252</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>2250</v>
+        <v>2253</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>2252</v>
+        <v>2255</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>2253</v>
+        <v>2256</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="4" t="s">
-        <v>2254</v>
+        <v>2257</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>591</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>2255</v>
+        <v>2258</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>2256</v>
+        <v>2259</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>2258</v>
+        <v>2261</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="4" t="s">
-        <v>2259</v>
+        <v>2262</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>605</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>2260</v>
+        <v>2263</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>611</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>2261</v>
+        <v>2264</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>2263</v>
+        <v>2266</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="4" t="s">
-        <v>2264</v>
+        <v>2267</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>631</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>2265</v>
+        <v>2268</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>637</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>2266</v>
+        <v>2269</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>2267</v>
+        <v>2270</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="4" t="s">
-        <v>2268</v>
+        <v>2271</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>646</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>2269</v>
+        <v>2272</v>
       </c>
       <c r="D20" s="4" t="s">
         <v>656</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>2270</v>
+        <v>2273</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>2271</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="4" t="s">
-        <v>2272</v>
+        <v>2275</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>662</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>2273</v>
+        <v>2276</v>
       </c>
       <c r="D21" s="4" t="s">
         <v>673</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>2274</v>
+        <v>2277</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>2275</v>
+        <v>2278</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="4" t="s">
-        <v>2276</v>
+        <v>2279</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>682</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>2277</v>
+        <v>2280</v>
       </c>
       <c r="D22" s="4" t="s">
         <v>698</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>2278</v>
+        <v>2281</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>2279</v>
+        <v>2282</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="4" t="s">
-        <v>2280</v>
+        <v>2283</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>700</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>2281</v>
+        <v>2284</v>
       </c>
       <c r="D23" s="4" t="s">
         <v>706</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>2282</v>
+        <v>2285</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>2283</v>
+        <v>2286</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="4" t="s">
-        <v>2284</v>
+        <v>2287</v>
       </c>
       <c r="B24" s="4" t="s">
         <v>721</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>2285</v>
+        <v>2288</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>2286</v>
+        <v>2289</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>2287</v>
+        <v>2290</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>2288</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="4" t="s">
-        <v>2289</v>
+        <v>2292</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>745</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>2290</v>
+        <v>2293</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>2291</v>
+        <v>2294</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>2292</v>
+        <v>2295</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>2293</v>
+        <v>2296</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="4" t="s">
-        <v>2294</v>
+        <v>2297</v>
       </c>
       <c r="B26" s="4" t="s">
         <v>764</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>2295</v>
+        <v>2298</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>2296</v>
+        <v>2299</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>2297</v>
+        <v>2300</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>2298</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="4" t="s">
-        <v>2299</v>
+        <v>2302</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>781</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>2300</v>
+        <v>2303</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>787</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>2301</v>
+        <v>2304</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>2302</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="4" t="s">
-        <v>2303</v>
+        <v>2306</v>
       </c>
       <c r="B28" s="4" t="s">
         <v>798</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>2304</v>
+        <v>2307</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>2305</v>
+        <v>2308</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>2306</v>
+        <v>2309</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>2307</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="4" t="s">
-        <v>2308</v>
+        <v>2311</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>825</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>2309</v>
+        <v>2312</v>
       </c>
       <c r="D29" s="4" t="s">
         <v>831</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>2310</v>
+        <v>2313</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>2311</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="4" t="s">
-        <v>2312</v>
+        <v>2315</v>
       </c>
       <c r="B30" s="4" t="s">
         <v>851</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>2313</v>
+        <v>2316</v>
       </c>
       <c r="D30" s="4" t="s">
         <v>865</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>2314</v>
+        <v>2317</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>2315</v>
+        <v>2318</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="4" t="s">
-        <v>2316</v>
+        <v>2319</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>887</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>2317</v>
+        <v>2320</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>904</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>2318</v>
+        <v>2321</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>2319</v>
+        <v>2322</v>
       </c>
     </row>
     <row r="32" spans="1:10">
       <c r="A32" s="4" t="s">
-        <v>2320</v>
+        <v>2323</v>
       </c>
       <c r="B32" s="4" t="s">
         <v>922</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>2321</v>
+        <v>2324</v>
       </c>
       <c r="D32" s="4" t="s">
         <v>935</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>2322</v>
+        <v>2325</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>2323</v>
+        <v>2326</v>
       </c>
     </row>
     <row r="33" spans="1:10">
       <c r="A33" s="4" t="s">
-        <v>2324</v>
+        <v>2327</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>948</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>2325</v>
+        <v>2328</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>965</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>2326</v>
+        <v>2329</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>2327</v>
+        <v>2330</v>
       </c>
     </row>
     <row r="34" spans="1:10">
       <c r="A34" s="4" t="s">
-        <v>2328</v>
+        <v>2331</v>
       </c>
       <c r="B34" s="4" t="s">
         <v>975</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>2329</v>
+        <v>2332</v>
       </c>
       <c r="D34" s="4" t="s">
         <v>981</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>2330</v>
+        <v>2333</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H34" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>2331</v>
+        <v>2334</v>
       </c>
     </row>
     <row r="35" spans="1:10">
       <c r="A35" s="4" t="s">
-        <v>2332</v>
+        <v>2335</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>1003</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>2333</v>
+        <v>2336</v>
       </c>
       <c r="D35" s="4" t="s">
         <v>1008</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>2334</v>
+        <v>2337</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>2335</v>
+        <v>2338</v>
       </c>
     </row>
     <row r="36" spans="1:10">
       <c r="A36" s="4" t="s">
-        <v>2336</v>
+        <v>2339</v>
       </c>
       <c r="B36" s="4" t="s">
         <v>1024</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>2337</v>
+        <v>2340</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>2338</v>
+        <v>2341</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>2178</v>
+        <v>2181</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>2339</v>
+        <v>2342</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>2340</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="4" t="s">
-        <v>2341</v>
+        <v>2344</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>1076</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>2342</v>
+        <v>2345</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>1081</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>2343</v>
+        <v>2346</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>2344</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="38" spans="1:10">
       <c r="A38" s="4" t="s">
-        <v>2345</v>
+        <v>2348</v>
       </c>
       <c r="B38" s="4" t="s">
         <v>1092</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>2346</v>
+        <v>2349</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>2347</v>
+        <v>2350</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>2348</v>
+        <v>2351</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>2349</v>
+        <v>2352</v>
       </c>
     </row>
     <row r="39" spans="1:10">
       <c r="A39" s="4" t="s">
-        <v>2350</v>
+        <v>2353</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>1108</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>2351</v>
+        <v>2354</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>1121</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>2352</v>
+        <v>2355</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>2353</v>
+        <v>2356</v>
       </c>
     </row>
     <row r="40" spans="1:10">
       <c r="A40" s="4" t="s">
-        <v>2354</v>
+        <v>2357</v>
       </c>
       <c r="B40" s="4" t="s">
         <v>1127</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>2355</v>
+        <v>2358</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>2356</v>
+        <v>2359</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>2358</v>
+        <v>2361</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>2361</v>
+        <v>2364</v>
       </c>
     </row>
     <row r="41" spans="1:10">
       <c r="A41" s="4" t="s">
-        <v>2362</v>
+        <v>2365</v>
       </c>
       <c r="B41" s="4" t="s">
         <v>1137</v>
       </c>
       <c r="C41" s="4" t="s">
+        <v>2366</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F41" s="4" t="s">
+        <v>2368</v>
+      </c>
+      <c r="G41" s="4" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>2362</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>2363</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>2364</v>
-      </c>
-      <c r="E41" s="4" t="s">
-        <v>2212</v>
-      </c>
-      <c r="F41" s="4" t="s">
-        <v>2365</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>2180</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>2359</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>2360</v>
-      </c>
       <c r="J41" s="4" t="s">
-        <v>2366</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="42" spans="1:10">
       <c r="A42" s="4" t="s">
-        <v>2367</v>
+        <v>2370</v>
       </c>
       <c r="B42" s="4" t="s">
         <v>1148</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>2368</v>
+        <v>2371</v>
       </c>
       <c r="D42" s="4" t="s">
         <v>1153</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>2369</v>
+        <v>2372</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>2370</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="43" spans="1:10">
       <c r="A43" s="4" t="s">
-        <v>2371</v>
+        <v>2374</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>1159</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>2372</v>
+        <v>2375</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>2373</v>
+        <v>2376</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>2374</v>
+        <v>2377</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>2359</v>
+        <v>2362</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>2360</v>
+        <v>2363</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>2375</v>
+        <v>2378</v>
       </c>
     </row>
     <row r="44" spans="1:10">
       <c r="A44" s="4" t="s">
-        <v>2376</v>
+        <v>2379</v>
       </c>
       <c r="B44" s="4" t="s">
         <v>1173</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>2377</v>
+        <v>2380</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>2378</v>
+        <v>2381</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>2379</v>
+        <v>2382</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>2380</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="45" spans="1:10">
       <c r="A45" s="4" t="s">
-        <v>2381</v>
+        <v>2384</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>1191</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>2382</v>
+        <v>2385</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>2383</v>
+        <v>2386</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>2384</v>
+        <v>2387</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>2385</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="46" spans="1:10">
       <c r="A46" s="4" t="s">
-        <v>2386</v>
+        <v>2389</v>
       </c>
       <c r="B46" s="4" t="s">
         <v>1205</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>2387</v>
+        <v>2390</v>
       </c>
       <c r="D46" s="4" t="s">
         <v>1210</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>2388</v>
+        <v>2391</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>2389</v>
+        <v>2392</v>
       </c>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="4" t="s">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>1242</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>2391</v>
+        <v>2394</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>2392</v>
+        <v>2395</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>2394</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="48" spans="1:10">
       <c r="A48" s="4" t="s">
-        <v>2395</v>
+        <v>2398</v>
       </c>
       <c r="B48" s="4" t="s">
         <v>1257</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>2396</v>
+        <v>2399</v>
       </c>
       <c r="D48" s="4" t="s">
         <v>1267</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>2397</v>
+        <v>2400</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>2398</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="49" spans="1:10">
       <c r="A49" s="4" t="s">
-        <v>2399</v>
+        <v>2402</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>1277</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>2400</v>
+        <v>2403</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>1290</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>2401</v>
+        <v>2404</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>2402</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="50" spans="1:10">
       <c r="A50" s="4" t="s">
-        <v>2403</v>
+        <v>2406</v>
       </c>
       <c r="B50" s="4" t="s">
         <v>1298</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>2404</v>
+        <v>2407</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>1316</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>2405</v>
+        <v>2408</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>2406</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="51" spans="1:10">
       <c r="A51" s="4" t="s">
-        <v>2407</v>
+        <v>2410</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>1328</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>2408</v>
+        <v>2411</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>1334</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>2409</v>
+        <v>2412</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>2410</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="52" spans="1:10">
       <c r="A52" s="4" t="s">
-        <v>2411</v>
+        <v>2414</v>
       </c>
       <c r="B52" s="4" t="s">
         <v>1346</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>2412</v>
+        <v>2415</v>
       </c>
       <c r="D52" s="4" t="s">
         <v>1359</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>2413</v>
+        <v>2416</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>2414</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="53" spans="1:10">
       <c r="A53" s="4" t="s">
-        <v>2415</v>
+        <v>2418</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>1367</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>2416</v>
+        <v>2419</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>2417</v>
+        <v>2420</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>2418</v>
+        <v>2421</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>2419</v>
+        <v>2422</v>
       </c>
     </row>
     <row r="54" spans="1:10">
       <c r="A54" s="4" t="s">
-        <v>2420</v>
+        <v>2423</v>
       </c>
       <c r="B54" s="4" t="s">
         <v>1377</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>2421</v>
+        <v>2424</v>
       </c>
       <c r="D54" s="4" t="s">
         <v>1390</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>2422</v>
+        <v>2425</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>2423</v>
+        <v>2426</v>
       </c>
     </row>
     <row r="55" spans="1:10">
       <c r="A55" s="4" t="s">
-        <v>2424</v>
+        <v>2427</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>1398</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>2425</v>
+        <v>2428</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>2426</v>
+        <v>2429</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>2427</v>
+        <v>2430</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>2428</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="56" spans="1:10">
       <c r="A56" s="4" t="s">
-        <v>2429</v>
+        <v>2432</v>
       </c>
       <c r="B56" s="4" t="s">
         <v>1417</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>2430</v>
+        <v>2433</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>1426</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>2431</v>
+        <v>2434</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>2432</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="57" spans="1:10">
       <c r="A57" s="4" t="s">
-        <v>2433</v>
+        <v>2436</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>1432</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>2434</v>
+        <v>2437</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>1437</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>2435</v>
+        <v>2438</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>2436</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="58" spans="1:10">
       <c r="A58" s="4" t="s">
-        <v>2437</v>
+        <v>2440</v>
       </c>
       <c r="B58" s="4" t="s">
         <v>1446</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>2438</v>
+        <v>2441</v>
       </c>
       <c r="D58" s="4" t="s">
         <v>1463</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>2439</v>
+        <v>2442</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>2440</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="59" spans="1:10">
       <c r="A59" s="4" t="s">
-        <v>2441</v>
+        <v>2444</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>1468</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>2442</v>
+        <v>2445</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>1473</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>2443</v>
+        <v>2446</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>2444</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="60" spans="1:10">
       <c r="A60" s="4" t="s">
-        <v>2445</v>
+        <v>2448</v>
       </c>
       <c r="B60" s="4" t="s">
         <v>1490</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>2446</v>
+        <v>2449</v>
       </c>
       <c r="D60" s="4" t="s">
         <v>1499</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>2191</v>
+        <v>2194</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>2447</v>
+        <v>2450</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>2448</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="61" spans="1:10">
       <c r="A61" s="4" t="s">
-        <v>2449</v>
+        <v>2452</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>1519</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>2450</v>
+        <v>2453</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>1524</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>2451</v>
+        <v>2454</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>2452</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="62" spans="1:10">
       <c r="A62" s="4" t="s">
-        <v>2453</v>
+        <v>2456</v>
       </c>
       <c r="B62" s="4" t="s">
         <v>1532</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>2454</v>
+        <v>2457</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>1538</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>2251</v>
+        <v>2254</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>2455</v>
+        <v>2458</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>2456</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="63" spans="1:10">
       <c r="A63" s="4" t="s">
-        <v>2457</v>
+        <v>2460</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>1566</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>2458</v>
+        <v>2461</v>
       </c>
       <c r="D63" s="4" t="s">
         <v>1580</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>2459</v>
+        <v>2462</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>2460</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="64" spans="1:10">
       <c r="A64" s="4" t="s">
-        <v>2461</v>
+        <v>2464</v>
       </c>
       <c r="B64" s="4" t="s">
         <v>1588</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>2462</v>
+        <v>2465</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>1610</v>
+        <v>1613</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>2463</v>
+        <v>2466</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>2262</v>
+        <v>2265</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>2464</v>
+        <v>2467</v>
       </c>
     </row>
     <row r="65" spans="1:10">
       <c r="A65" s="4" t="s">
-        <v>2465</v>
+        <v>2468</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>1612</v>
+        <v>1615</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>2466</v>
+        <v>2469</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>2467</v>
+        <v>2470</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>2468</v>
+        <v>2471</v>
       </c>
     </row>
     <row r="66" spans="1:10">
       <c r="A66" s="4" t="s">
-        <v>2469</v>
+        <v>2472</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>2470</v>
+        <v>2473</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>2471</v>
+        <v>2474</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>2472</v>
+        <v>2475</v>
       </c>
     </row>
     <row r="67" spans="1:10">
       <c r="A67" s="4" t="s">
-        <v>2473</v>
+        <v>2476</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>2474</v>
+        <v>2477</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>2475</v>
+        <v>2478</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>2476</v>
+        <v>2479</v>
       </c>
     </row>
     <row r="68" spans="1:10">
       <c r="A68" s="4" t="s">
-        <v>2477</v>
+        <v>2480</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>2478</v>
+        <v>2481</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>2479</v>
+        <v>2482</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>2480</v>
+        <v>2483</v>
       </c>
     </row>
     <row r="69" spans="1:10">
       <c r="A69" s="4" t="s">
-        <v>2481</v>
+        <v>2484</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>2482</v>
+        <v>2485</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>2483</v>
+        <v>2486</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>2484</v>
+        <v>2487</v>
       </c>
     </row>
     <row r="70" spans="1:10">
       <c r="A70" s="4" t="s">
-        <v>2485</v>
+        <v>2488</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>2486</v>
+        <v>2489</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>2186</v>
+        <v>2189</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>2487</v>
+        <v>2490</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>2488</v>
+        <v>2491</v>
       </c>
     </row>
     <row r="71" spans="1:10">
       <c r="A71" s="4" t="s">
-        <v>2489</v>
+        <v>2492</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>2490</v>
+        <v>2493</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>2491</v>
+        <v>2494</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>2492</v>
+        <v>2495</v>
       </c>
     </row>
     <row r="72" spans="1:10">
       <c r="A72" s="4" t="s">
-        <v>2493</v>
+        <v>2496</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>2494</v>
+        <v>2497</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>2495</v>
+        <v>2498</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>2496</v>
+        <v>2499</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>2497</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="73" spans="1:10">
       <c r="A73" s="4" t="s">
-        <v>2498</v>
+        <v>2501</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>2499</v>
+        <v>2502</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>2500</v>
+        <v>2503</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>2501</v>
+        <v>2504</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>2502</v>
+        <v>2505</v>
       </c>
     </row>
     <row r="74" spans="1:10">
       <c r="A74" s="4" t="s">
-        <v>2503</v>
+        <v>2506</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>2504</v>
+        <v>2507</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>2505</v>
+        <v>2508</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>2506</v>
+        <v>2509</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="75" spans="1:10">
       <c r="A75" s="4" t="s">
-        <v>2508</v>
+        <v>2511</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>2509</v>
+        <v>2512</v>
       </c>
       <c r="D75" s="4" t="s">
+        <v>2513</v>
+      </c>
+      <c r="E75" s="4" t="s">
+        <v>2215</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>2514</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H75" s="4" t="s">
         <v>2510</v>
       </c>
-      <c r="E75" s="4" t="s">
-        <v>2212</v>
-      </c>
-      <c r="F75" s="4" t="s">
-        <v>2511</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>2180</v>
-      </c>
-      <c r="H75" s="4" t="s">
-        <v>2507</v>
-      </c>
       <c r="I75" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="76" spans="1:10">
       <c r="A76" s="4" t="s">
-        <v>2512</v>
+        <v>2515</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>2513</v>
+        <v>2516</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>2223</v>
+        <v>2226</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>2514</v>
+        <v>2517</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>2515</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="77" spans="1:10">
       <c r="A77" s="4" t="s">
-        <v>2516</v>
+        <v>2519</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>2517</v>
+        <v>2520</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>2518</v>
+        <v>2521</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>2519</v>
+        <v>2522</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>2520</v>
+        <v>2523</v>
       </c>
     </row>
     <row r="78" spans="1:10">
       <c r="A78" s="4" t="s">
-        <v>2521</v>
+        <v>2524</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>2522</v>
+        <v>2525</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>2523</v>
+        <v>2526</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>2524</v>
+        <v>2527</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>2525</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="79" spans="1:10">
       <c r="A79" s="4" t="s">
-        <v>2526</v>
+        <v>2529</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>2527</v>
+        <v>2530</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>2528</v>
+        <v>2531</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>2529</v>
+        <v>2532</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>2530</v>
+        <v>2533</v>
       </c>
     </row>
     <row r="80" spans="1:10">
       <c r="A80" s="4" t="s">
-        <v>2531</v>
+        <v>2534</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>2532</v>
+        <v>2535</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>2533</v>
+        <v>2536</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>2534</v>
+        <v>2537</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>2535</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="81" spans="1:10">
       <c r="A81" s="4" t="s">
-        <v>2536</v>
+        <v>2539</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>2537</v>
+        <v>2540</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>2538</v>
+        <v>2541</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>2539</v>
+        <v>2542</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>2540</v>
+        <v>2543</v>
       </c>
     </row>
     <row r="82" spans="1:10">
       <c r="A82" s="4" t="s">
-        <v>2541</v>
+        <v>2544</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>2542</v>
+        <v>2545</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>2237</v>
+        <v>2240</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>2543</v>
+        <v>2546</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>2544</v>
+        <v>2547</v>
       </c>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="4" t="s">
-        <v>2545</v>
+        <v>2548</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>2546</v>
+        <v>2549</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>2547</v>
+        <v>2550</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>2193</v>
+        <v>2196</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>2548</v>
+        <v>2551</v>
       </c>
     </row>
     <row r="84" spans="1:10">
       <c r="A84" s="4" t="s">
-        <v>2549</v>
+        <v>2552</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>2550</v>
+        <v>2553</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>2551</v>
+        <v>2554</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>2552</v>
+        <v>2555</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>2553</v>
+        <v>2556</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H84" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>2556</v>
+        <v>2559</v>
       </c>
     </row>
     <row r="85" spans="1:10">
       <c r="A85" s="4" t="s">
+        <v>2560</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>2035</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>2561</v>
+      </c>
+      <c r="D85" s="4" t="s">
+        <v>2562</v>
+      </c>
+      <c r="E85" s="4" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>2563</v>
+      </c>
+      <c r="G85" s="4" t="s">
         <v>2557</v>
       </c>
-      <c r="B85" s="4" t="s">
-        <v>2032</v>
-      </c>
-      <c r="C85" s="4" t="s">
+      <c r="H85" s="4" t="s">
+        <v>2564</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>2558</v>
-      </c>
-      <c r="D85" s="4" t="s">
-        <v>2559</v>
-      </c>
-      <c r="E85" s="4" t="s">
-        <v>2237</v>
-      </c>
-      <c r="F85" s="4" t="s">
-        <v>2560</v>
-      </c>
-      <c r="G85" s="4" t="s">
-        <v>2554</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>2561</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>2555</v>
       </c>
     </row>
     <row r="86" spans="1:10">
       <c r="A86" s="4" t="s">
-        <v>2562</v>
+        <v>2565</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>2563</v>
+        <v>2566</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>2564</v>
+        <v>2567</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>2565</v>
+        <v>2568</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>2566</v>
+        <v>2569</v>
       </c>
     </row>
     <row r="87" spans="1:10">
       <c r="A87" s="4" t="s">
-        <v>2567</v>
+        <v>2570</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>2568</v>
+        <v>2571</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>2569</v>
+        <v>2572</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>2570</v>
+        <v>2573</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>2571</v>
+        <v>2574</v>
       </c>
     </row>
     <row r="88" spans="1:10">
       <c r="A88" s="4" t="s">
-        <v>2572</v>
+        <v>2575</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>2573</v>
+        <v>2576</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>2574</v>
+        <v>2577</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>2198</v>
+        <v>2201</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>2575</v>
+        <v>2578</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H88" s="4" t="s">
-        <v>2181</v>
+        <v>2184</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>2576</v>
+        <v>2579</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>2577</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="89" spans="1:10">
       <c r="A89" s="4" t="s">
-        <v>2578</v>
+        <v>2581</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>2579</v>
+        <v>2582</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>2580</v>
+        <v>2583</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>2581</v>
+        <v>2584</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="90" spans="1:10">
       <c r="A90" s="4" t="s">
-        <v>2582</v>
+        <v>2585</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>2583</v>
+        <v>2586</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>2584</v>
+        <v>2587</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>2585</v>
+        <v>2588</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="91" spans="1:10">
       <c r="A91" s="4" t="s">
-        <v>2586</v>
+        <v>2589</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>2117</v>
+        <v>2120</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>2587</v>
+        <v>2590</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>2124</v>
+        <v>2127</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>2212</v>
+        <v>2215</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>2588</v>
+        <v>2591</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>2554</v>
+        <v>2557</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>2555</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="92" spans="1:10">
       <c r="A92" s="4" t="s">
-        <v>2589</v>
+        <v>2592</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>2130</v>
+        <v>2133</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>2590</v>
+        <v>2593</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>2137</v>
+        <v>2140</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>2591</v>
+        <v>2594</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="93" spans="1:10">
       <c r="A93" s="4" t="s">
-        <v>2592</v>
+        <v>2595</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>2139</v>
+        <v>2142</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>2593</v>
+        <v>2596</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>2142</v>
+        <v>2145</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>2357</v>
+        <v>2360</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>2594</v>
+        <v>2597</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>2507</v>
+        <v>2510</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>2182</v>
+        <v>2185</v>
       </c>
     </row>
     <row r="94" spans="1:10">
       <c r="A94" s="4" t="s">
-        <v>2595</v>
+        <v>2598</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>2148</v>
+        <v>2151</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>2596</v>
+        <v>2599</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>2151</v>
+        <v>2154</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>2147</v>
+        <v>2150</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="95" spans="1:10">
       <c r="A95" s="4" t="s">
+        <v>2603</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>2604</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>2157</v>
+      </c>
+      <c r="E95" s="4" t="s">
         <v>2600</v>
       </c>
-      <c r="B95" s="4" t="s">
-        <v>2153</v>
-      </c>
-      <c r="C95" s="4" t="s">
+      <c r="F95" s="4" t="s">
+        <v>2155</v>
+      </c>
+      <c r="G95" s="4" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H95" s="4" t="s">
         <v>2601</v>
       </c>
-      <c r="D95" s="4" t="s">
-        <v>2154</v>
-      </c>
-      <c r="E95" s="4" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>2152</v>
-      </c>
-      <c r="G95" s="4" t="s">
-        <v>2180</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>2598</v>
-      </c>
       <c r="I95" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="96" spans="1:10">
       <c r="A96" s="4" t="s">
+        <v>2605</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>2159</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>2606</v>
+      </c>
+      <c r="D96" s="4" t="s">
+        <v>2160</v>
+      </c>
+      <c r="E96" s="4" t="s">
+        <v>2600</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>2158</v>
+      </c>
+      <c r="G96" s="4" t="s">
+        <v>2183</v>
+      </c>
+      <c r="H96" s="4" t="s">
+        <v>2601</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>2602</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>2156</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>2603</v>
-      </c>
-      <c r="D96" s="4" t="s">
-        <v>2157</v>
-      </c>
-      <c r="E96" s="4" t="s">
-        <v>2597</v>
-      </c>
-      <c r="F96" s="4" t="s">
-        <v>2155</v>
-      </c>
-      <c r="G96" s="4" t="s">
-        <v>2180</v>
-      </c>
-      <c r="H96" s="4" t="s">
-        <v>2598</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>2599</v>
       </c>
     </row>
     <row r="97" spans="1:9">
       <c r="A97" s="4" t="s">
-        <v>2604</v>
+        <v>2607</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>2159</v>
+        <v>2162</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>2605</v>
+        <v>2608</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>2160</v>
+        <v>2163</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>2158</v>
+        <v>2161</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="98" spans="1:9">
       <c r="A98" s="4" t="s">
-        <v>2606</v>
+        <v>2609</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>2162</v>
+        <v>2165</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>2607</v>
+        <v>2610</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>2163</v>
+        <v>2166</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>2161</v>
+        <v>2164</v>
       </c>
       <c r="G98" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="99" spans="1:9">
       <c r="A99" s="4" t="s">
-        <v>2608</v>
+        <v>2611</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>2165</v>
+        <v>2168</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>2609</v>
+        <v>2612</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>2166</v>
+        <v>2169</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>2597</v>
+        <v>2600</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>2164</v>
+        <v>2167</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>2180</v>
+        <v>2183</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>2598</v>
+        <v>2601</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>2599</v>
+        <v>2602</v>
       </c>
     </row>
   </sheetData>

--- a/ForeKingHell-completion-tracker.xlsx
+++ b/ForeKingHell-completion-tracker.xlsx
@@ -21,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10704" uniqueCount="2613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10764" uniqueCount="2616">
   <si>
     <t>ForeKingHell · UI upgrade progress</t>
   </si>
   <si>
-    <t>Snapshot: 07 September 2026, 09:28 BST</t>
+    <t>Snapshot: 07 September 2026, 09:42 BST</t>
   </si>
   <si>
     <t>UI-first delivery: implemented UI is shown first below. Acceptance is tracked separately and remains pending until its checks pass. Filter Components or open Work touched for the exact changes and evidence. Source: ForeKingHell-completion-tracker.csv.</t>
@@ -4872,6 +4872,15 @@
   </si>
   <si>
     <t>Friends, requests and discovery navigation</t>
+  </si>
+  <si>
+    <t>Full shared Friends workspace, counted URL tabs and searchable distinct relationship states. Named confirmation before mutations, pending/error feedback, invitation preview/copy. Actual friends-browser.log PASS4.6m:1440x900,1280x800,1024x800 on both surfaces; cancel inert, accept/remove/request/cancel/block/unblock exact fixture rows, clipboard readback; zero pageerrors. Types/lint pass.</t>
+  </si>
+  <si>
+    <t>Same complete task at390x844,360x800,1023x800 both surfaces in same passing12view matrix. Selected scrollable tabs, full rows/action sheets, invitation copy verified. P64-workbench-390.png inspected under output/playwright/ui-upgrade/friends-browser.</t>
+  </si>
+  <si>
+    <t>Full acceptance outstanding: decline/duplicate/stale request and server-error browser fixtures, privacy/permission adversarial states, long identities, clipboard-denied/QR failure, Back/Forward and focus restoration after refreshed row removal, AT/zoom/theme/native keyboard/safe-area matrix. Local accessible compositions replace unavailable paid examples; no paid export claimed.</t>
   </si>
   <si>
     <t>Pending requests and accepted friendships remain distinct.</t>
@@ -8032,8 +8041,8 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L352" totalsRowShown="0">
-  <autoFilter ref="A1:L352"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Table2" displayName="Table2" ref="A1:L356" totalsRowShown="0">
+  <autoFilter ref="A1:L356"/>
   <tableColumns count="12">
     <tableColumn id="1" name="Component ID"/>
     <tableColumn id="2" name="Route"/>
@@ -8427,11 +8436,11 @@
       </c>
       <c r="B10" s="5">
         <f>COUNTIF(Components!E2:E493,"Implemented; partial verification")</f>
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C10" s="5">
         <f>COUNTIF(Components!F2:F493,"Implemented; partial verification")</f>
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8466,11 +8475,11 @@
       </c>
       <c r="B13" s="5">
         <f>COUNTIF(Components!E2:E493,"Not started")</f>
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C13" s="5">
         <f>COUNTIF(Components!F2:F493,"Not started")</f>
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -21962,16 +21971,25 @@
         <v>42</v>
       </c>
       <c r="E353" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F353" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G353" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H353" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="I353" s="4" t="s">
+        <v>1619</v>
       </c>
       <c r="J353" s="4" t="s">
-        <v>1617</v>
+        <v>1620</v>
       </c>
       <c r="K353" s="4" t="s">
-        <v>1618</v>
+        <v>1621</v>
       </c>
       <c r="L353" s="6" t="s">
         <v>141</v>
@@ -21979,28 +21997,37 @@
     </row>
     <row r="354" spans="1:12" ht="72" customHeight="1">
       <c r="A354" s="4" t="s">
-        <v>1619</v>
+        <v>1622</v>
       </c>
       <c r="B354" s="4" t="s">
         <v>1615</v>
       </c>
       <c r="C354" s="4" t="s">
-        <v>1620</v>
+        <v>1623</v>
       </c>
       <c r="D354" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E354" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F354" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G354" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H354" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="I354" s="4" t="s">
+        <v>1619</v>
       </c>
       <c r="J354" s="4" t="s">
-        <v>1621</v>
+        <v>1624</v>
       </c>
       <c r="K354" s="4" t="s">
-        <v>1622</v>
+        <v>1625</v>
       </c>
       <c r="L354" s="6" t="s">
         <v>147</v>
@@ -22008,28 +22035,37 @@
     </row>
     <row r="355" spans="1:12" ht="72" customHeight="1">
       <c r="A355" s="4" t="s">
-        <v>1623</v>
+        <v>1626</v>
       </c>
       <c r="B355" s="4" t="s">
         <v>1615</v>
       </c>
       <c r="C355" s="4" t="s">
-        <v>1624</v>
+        <v>1627</v>
       </c>
       <c r="D355" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E355" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F355" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G355" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H355" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="I355" s="4" t="s">
+        <v>1619</v>
       </c>
       <c r="J355" s="4" t="s">
-        <v>1625</v>
+        <v>1628</v>
       </c>
       <c r="K355" s="4" t="s">
-        <v>1626</v>
+        <v>1629</v>
       </c>
       <c r="L355" s="6" t="s">
         <v>103</v>
@@ -22037,28 +22073,37 @@
     </row>
     <row r="356" spans="1:12" ht="72" customHeight="1">
       <c r="A356" s="4" t="s">
-        <v>1627</v>
+        <v>1630</v>
       </c>
       <c r="B356" s="4" t="s">
         <v>1615</v>
       </c>
       <c r="C356" s="4" t="s">
-        <v>1628</v>
+        <v>1631</v>
       </c>
       <c r="D356" s="4" t="s">
         <v>42</v>
       </c>
       <c r="E356" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F356" s="4" t="s">
-        <v>9</v>
+        <v>33</v>
+      </c>
+      <c r="G356" s="4" t="s">
+        <v>1617</v>
+      </c>
+      <c r="H356" s="4" t="s">
+        <v>1618</v>
+      </c>
+      <c r="I356" s="4" t="s">
+        <v>1619</v>
       </c>
       <c r="J356" s="4" t="s">
-        <v>1629</v>
+        <v>1632</v>
       </c>
       <c r="K356" s="4" t="s">
-        <v>1630</v>
+        <v>1633</v>
       </c>
       <c r="L356" s="6" t="s">
         <v>518</v>
@@ -22066,13 +22111,13 @@
     </row>
     <row r="357" spans="1:12" ht="72" customHeight="1">
       <c r="A357" s="4" t="s">
-        <v>1631</v>
+        <v>1634</v>
       </c>
       <c r="B357" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="C357" s="4" t="s">
-        <v>1633</v>
+        <v>1636</v>
       </c>
       <c r="D357" s="4" t="s">
         <v>42</v>
@@ -22084,10 +22129,10 @@
         <v>9</v>
       </c>
       <c r="J357" s="4" t="s">
-        <v>1634</v>
+        <v>1637</v>
       </c>
       <c r="K357" s="4" t="s">
-        <v>1635</v>
+        <v>1638</v>
       </c>
       <c r="L357" s="6" t="s">
         <v>141</v>
@@ -22095,13 +22140,13 @@
     </row>
     <row r="358" spans="1:12" ht="72" customHeight="1">
       <c r="A358" s="4" t="s">
-        <v>1636</v>
+        <v>1639</v>
       </c>
       <c r="B358" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="C358" s="4" t="s">
-        <v>1637</v>
+        <v>1640</v>
       </c>
       <c r="D358" s="4" t="s">
         <v>42</v>
@@ -22113,10 +22158,10 @@
         <v>9</v>
       </c>
       <c r="J358" s="4" t="s">
-        <v>1638</v>
+        <v>1641</v>
       </c>
       <c r="K358" s="4" t="s">
-        <v>1639</v>
+        <v>1642</v>
       </c>
       <c r="L358" s="6" t="s">
         <v>165</v>
@@ -22124,13 +22169,13 @@
     </row>
     <row r="359" spans="1:12" ht="72" customHeight="1">
       <c r="A359" s="4" t="s">
-        <v>1640</v>
+        <v>1643</v>
       </c>
       <c r="B359" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="C359" s="4" t="s">
-        <v>1641</v>
+        <v>1644</v>
       </c>
       <c r="D359" s="4" t="s">
         <v>42</v>
@@ -22142,10 +22187,10 @@
         <v>9</v>
       </c>
       <c r="J359" s="4" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K359" s="4" t="s">
         <v>1642</v>
-      </c>
-      <c r="K359" s="4" t="s">
-        <v>1639</v>
       </c>
       <c r="L359" s="6" t="s">
         <v>165</v>
@@ -22153,13 +22198,13 @@
     </row>
     <row r="360" spans="1:12" ht="72" customHeight="1">
       <c r="A360" s="4" t="s">
-        <v>1643</v>
+        <v>1646</v>
       </c>
       <c r="B360" s="4" t="s">
-        <v>1632</v>
+        <v>1635</v>
       </c>
       <c r="C360" s="4" t="s">
-        <v>1644</v>
+        <v>1647</v>
       </c>
       <c r="D360" s="4" t="s">
         <v>42</v>
@@ -22171,10 +22216,10 @@
         <v>9</v>
       </c>
       <c r="J360" s="4" t="s">
-        <v>1645</v>
+        <v>1648</v>
       </c>
       <c r="K360" s="4" t="s">
-        <v>1646</v>
+        <v>1649</v>
       </c>
       <c r="L360" s="6" t="s">
         <v>518</v>
@@ -22182,13 +22227,13 @@
     </row>
     <row r="361" spans="1:12" ht="72" customHeight="1">
       <c r="A361" s="4" t="s">
-        <v>1647</v>
+        <v>1650</v>
       </c>
       <c r="B361" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C361" s="4" t="s">
-        <v>1649</v>
+        <v>1652</v>
       </c>
       <c r="D361" s="4" t="s">
         <v>42</v>
@@ -22200,10 +22245,10 @@
         <v>9</v>
       </c>
       <c r="J361" s="4" t="s">
-        <v>1650</v>
+        <v>1653</v>
       </c>
       <c r="K361" s="4" t="s">
-        <v>1651</v>
+        <v>1654</v>
       </c>
       <c r="L361" s="6" t="s">
         <v>141</v>
@@ -22211,13 +22256,13 @@
     </row>
     <row r="362" spans="1:12" ht="72" customHeight="1">
       <c r="A362" s="4" t="s">
-        <v>1652</v>
+        <v>1655</v>
       </c>
       <c r="B362" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C362" s="4" t="s">
-        <v>1653</v>
+        <v>1656</v>
       </c>
       <c r="D362" s="4" t="s">
         <v>42</v>
@@ -22229,10 +22274,10 @@
         <v>9</v>
       </c>
       <c r="J362" s="4" t="s">
-        <v>1654</v>
+        <v>1657</v>
       </c>
       <c r="K362" s="4" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="L362" s="6" t="s">
         <v>165</v>
@@ -22240,13 +22285,13 @@
     </row>
     <row r="363" spans="1:12" ht="72" customHeight="1">
       <c r="A363" s="4" t="s">
-        <v>1656</v>
+        <v>1659</v>
       </c>
       <c r="B363" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C363" s="4" t="s">
-        <v>1657</v>
+        <v>1660</v>
       </c>
       <c r="D363" s="4" t="s">
         <v>42</v>
@@ -22258,10 +22303,10 @@
         <v>9</v>
       </c>
       <c r="J363" s="4" t="s">
+        <v>1661</v>
+      </c>
+      <c r="K363" s="4" t="s">
         <v>1658</v>
-      </c>
-      <c r="K363" s="4" t="s">
-        <v>1655</v>
       </c>
       <c r="L363" s="6" t="s">
         <v>183</v>
@@ -22269,13 +22314,13 @@
     </row>
     <row r="364" spans="1:12" ht="72" customHeight="1">
       <c r="A364" s="4" t="s">
-        <v>1659</v>
+        <v>1662</v>
       </c>
       <c r="B364" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C364" s="4" t="s">
-        <v>1660</v>
+        <v>1663</v>
       </c>
       <c r="D364" s="4" t="s">
         <v>42</v>
@@ -22287,10 +22332,10 @@
         <v>9</v>
       </c>
       <c r="J364" s="4" t="s">
-        <v>1661</v>
+        <v>1664</v>
       </c>
       <c r="K364" s="4" t="s">
-        <v>1655</v>
+        <v>1658</v>
       </c>
       <c r="L364" s="6" t="s">
         <v>518</v>
@@ -22298,13 +22343,13 @@
     </row>
     <row r="365" spans="1:12" ht="72" customHeight="1">
       <c r="A365" s="4" t="s">
-        <v>1662</v>
+        <v>1665</v>
       </c>
       <c r="B365" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C365" s="4" t="s">
-        <v>1663</v>
+        <v>1666</v>
       </c>
       <c r="D365" s="4" t="s">
         <v>42</v>
@@ -22316,10 +22361,10 @@
         <v>9</v>
       </c>
       <c r="J365" s="4" t="s">
-        <v>1664</v>
+        <v>1667</v>
       </c>
       <c r="K365" s="4" t="s">
-        <v>1665</v>
+        <v>1668</v>
       </c>
       <c r="L365" s="6" t="s">
         <v>88</v>
@@ -22327,13 +22372,13 @@
     </row>
     <row r="366" spans="1:12" ht="72" customHeight="1">
       <c r="A366" s="4" t="s">
-        <v>1666</v>
+        <v>1669</v>
       </c>
       <c r="B366" s="4" t="s">
-        <v>1648</v>
+        <v>1651</v>
       </c>
       <c r="C366" s="4" t="s">
-        <v>1667</v>
+        <v>1670</v>
       </c>
       <c r="D366" s="4" t="s">
         <v>42</v>
@@ -22345,10 +22390,10 @@
         <v>9</v>
       </c>
       <c r="J366" s="4" t="s">
-        <v>1668</v>
+        <v>1671</v>
       </c>
       <c r="K366" s="4" t="s">
-        <v>1669</v>
+        <v>1672</v>
       </c>
       <c r="L366" s="6" t="s">
         <v>103</v>
@@ -22356,13 +22401,13 @@
     </row>
     <row r="367" spans="1:12" ht="72" customHeight="1">
       <c r="A367" s="4" t="s">
-        <v>1670</v>
+        <v>1673</v>
       </c>
       <c r="B367" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C367" s="4" t="s">
-        <v>1672</v>
+        <v>1675</v>
       </c>
       <c r="D367" s="4" t="s">
         <v>42</v>
@@ -22374,10 +22419,10 @@
         <v>9</v>
       </c>
       <c r="J367" s="4" t="s">
-        <v>1673</v>
+        <v>1676</v>
       </c>
       <c r="K367" s="4" t="s">
-        <v>1674</v>
+        <v>1677</v>
       </c>
       <c r="L367" s="6" t="s">
         <v>147</v>
@@ -22385,13 +22430,13 @@
     </row>
     <row r="368" spans="1:12" ht="72" customHeight="1">
       <c r="A368" s="4" t="s">
-        <v>1675</v>
+        <v>1678</v>
       </c>
       <c r="B368" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C368" s="4" t="s">
-        <v>1676</v>
+        <v>1679</v>
       </c>
       <c r="D368" s="4" t="s">
         <v>42</v>
@@ -22403,10 +22448,10 @@
         <v>9</v>
       </c>
       <c r="J368" s="4" t="s">
-        <v>1677</v>
+        <v>1680</v>
       </c>
       <c r="K368" s="4" t="s">
-        <v>1678</v>
+        <v>1681</v>
       </c>
       <c r="L368" s="6" t="s">
         <v>183</v>
@@ -22414,13 +22459,13 @@
     </row>
     <row r="369" spans="1:12" ht="72" customHeight="1">
       <c r="A369" s="4" t="s">
-        <v>1679</v>
+        <v>1682</v>
       </c>
       <c r="B369" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C369" s="4" t="s">
-        <v>1680</v>
+        <v>1683</v>
       </c>
       <c r="D369" s="4" t="s">
         <v>42</v>
@@ -22432,10 +22477,10 @@
         <v>9</v>
       </c>
       <c r="J369" s="4" t="s">
-        <v>1681</v>
+        <v>1684</v>
       </c>
       <c r="K369" s="4" t="s">
-        <v>1682</v>
+        <v>1685</v>
       </c>
       <c r="L369" s="6" t="s">
         <v>518</v>
@@ -22443,13 +22488,13 @@
     </row>
     <row r="370" spans="1:12" ht="72" customHeight="1">
       <c r="A370" s="4" t="s">
-        <v>1683</v>
+        <v>1686</v>
       </c>
       <c r="B370" s="4" t="s">
-        <v>1671</v>
+        <v>1674</v>
       </c>
       <c r="C370" s="4" t="s">
-        <v>1684</v>
+        <v>1687</v>
       </c>
       <c r="D370" s="4" t="s">
         <v>42</v>
@@ -22461,10 +22506,10 @@
         <v>9</v>
       </c>
       <c r="J370" s="4" t="s">
-        <v>1685</v>
+        <v>1688</v>
       </c>
       <c r="K370" s="4" t="s">
-        <v>1686</v>
+        <v>1689</v>
       </c>
       <c r="L370" s="6" t="s">
         <v>165</v>
@@ -22472,13 +22517,13 @@
     </row>
     <row r="371" spans="1:12" ht="72" customHeight="1">
       <c r="A371" s="4" t="s">
-        <v>1687</v>
+        <v>1690</v>
       </c>
       <c r="B371" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C371" s="4" t="s">
-        <v>1689</v>
+        <v>1692</v>
       </c>
       <c r="D371" s="4" t="s">
         <v>42</v>
@@ -22490,10 +22535,10 @@
         <v>9</v>
       </c>
       <c r="J371" s="4" t="s">
-        <v>1690</v>
+        <v>1693</v>
       </c>
       <c r="K371" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="L371" s="6" t="s">
         <v>518</v>
@@ -22501,13 +22546,13 @@
     </row>
     <row r="372" spans="1:12" ht="72" customHeight="1">
       <c r="A372" s="4" t="s">
-        <v>1692</v>
+        <v>1695</v>
       </c>
       <c r="B372" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C372" s="4" t="s">
-        <v>1693</v>
+        <v>1696</v>
       </c>
       <c r="D372" s="4" t="s">
         <v>42</v>
@@ -22519,10 +22564,10 @@
         <v>9</v>
       </c>
       <c r="J372" s="4" t="s">
-        <v>1694</v>
+        <v>1697</v>
       </c>
       <c r="K372" s="4" t="s">
-        <v>1695</v>
+        <v>1698</v>
       </c>
       <c r="L372" s="6" t="s">
         <v>165</v>
@@ -22530,13 +22575,13 @@
     </row>
     <row r="373" spans="1:12" ht="72" customHeight="1">
       <c r="A373" s="4" t="s">
-        <v>1696</v>
+        <v>1699</v>
       </c>
       <c r="B373" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C373" s="4" t="s">
-        <v>1697</v>
+        <v>1700</v>
       </c>
       <c r="D373" s="4" t="s">
         <v>42</v>
@@ -22548,10 +22593,10 @@
         <v>9</v>
       </c>
       <c r="J373" s="4" t="s">
-        <v>1698</v>
+        <v>1701</v>
       </c>
       <c r="K373" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="L373" s="6" t="s">
         <v>518</v>
@@ -22559,13 +22604,13 @@
     </row>
     <row r="374" spans="1:12" ht="72" customHeight="1">
       <c r="A374" s="4" t="s">
-        <v>1699</v>
+        <v>1702</v>
       </c>
       <c r="B374" s="4" t="s">
-        <v>1688</v>
+        <v>1691</v>
       </c>
       <c r="C374" s="4" t="s">
-        <v>1700</v>
+        <v>1703</v>
       </c>
       <c r="D374" s="4" t="s">
         <v>42</v>
@@ -22577,10 +22622,10 @@
         <v>9</v>
       </c>
       <c r="J374" s="4" t="s">
-        <v>1701</v>
+        <v>1704</v>
       </c>
       <c r="K374" s="4" t="s">
-        <v>1691</v>
+        <v>1694</v>
       </c>
       <c r="L374" s="6" t="s">
         <v>88</v>
@@ -22588,13 +22633,13 @@
     </row>
     <row r="375" spans="1:12" ht="72" customHeight="1">
       <c r="A375" s="4" t="s">
-        <v>1702</v>
+        <v>1705</v>
       </c>
       <c r="B375" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C375" s="4" t="s">
-        <v>1704</v>
+        <v>1707</v>
       </c>
       <c r="D375" s="4" t="s">
         <v>42</v>
@@ -22606,10 +22651,10 @@
         <v>9</v>
       </c>
       <c r="J375" s="4" t="s">
-        <v>1705</v>
+        <v>1708</v>
       </c>
       <c r="K375" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="L375" s="6" t="s">
         <v>66</v>
@@ -22617,13 +22662,13 @@
     </row>
     <row r="376" spans="1:12" ht="72" customHeight="1">
       <c r="A376" s="4" t="s">
-        <v>1707</v>
+        <v>1710</v>
       </c>
       <c r="B376" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C376" s="4" t="s">
-        <v>1708</v>
+        <v>1711</v>
       </c>
       <c r="D376" s="4" t="s">
         <v>42</v>
@@ -22635,10 +22680,10 @@
         <v>9</v>
       </c>
       <c r="J376" s="4" t="s">
-        <v>1709</v>
+        <v>1712</v>
       </c>
       <c r="K376" s="4" t="s">
-        <v>1710</v>
+        <v>1713</v>
       </c>
       <c r="L376" s="6" t="s">
         <v>141</v>
@@ -22646,13 +22691,13 @@
     </row>
     <row r="377" spans="1:12" ht="72" customHeight="1">
       <c r="A377" s="4" t="s">
-        <v>1711</v>
+        <v>1714</v>
       </c>
       <c r="B377" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C377" s="4" t="s">
-        <v>1712</v>
+        <v>1715</v>
       </c>
       <c r="D377" s="4" t="s">
         <v>42</v>
@@ -22664,10 +22709,10 @@
         <v>9</v>
       </c>
       <c r="J377" s="4" t="s">
-        <v>1713</v>
+        <v>1716</v>
       </c>
       <c r="K377" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="L377" s="6" t="s">
         <v>159</v>
@@ -22675,13 +22720,13 @@
     </row>
     <row r="378" spans="1:12" ht="72" customHeight="1">
       <c r="A378" s="4" t="s">
-        <v>1714</v>
+        <v>1717</v>
       </c>
       <c r="B378" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C378" s="4" t="s">
-        <v>1715</v>
+        <v>1718</v>
       </c>
       <c r="D378" s="4" t="s">
         <v>42</v>
@@ -22693,10 +22738,10 @@
         <v>9</v>
       </c>
       <c r="J378" s="4" t="s">
-        <v>1716</v>
+        <v>1719</v>
       </c>
       <c r="K378" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="L378" s="6" t="s">
         <v>165</v>
@@ -22704,13 +22749,13 @@
     </row>
     <row r="379" spans="1:12" ht="72" customHeight="1">
       <c r="A379" s="4" t="s">
-        <v>1717</v>
+        <v>1720</v>
       </c>
       <c r="B379" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C379" s="4" t="s">
-        <v>1718</v>
+        <v>1721</v>
       </c>
       <c r="D379" s="4" t="s">
         <v>42</v>
@@ -22722,10 +22767,10 @@
         <v>9</v>
       </c>
       <c r="J379" s="4" t="s">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="K379" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="L379" s="6" t="s">
         <v>88</v>
@@ -22733,13 +22778,13 @@
     </row>
     <row r="380" spans="1:12" ht="72" customHeight="1">
       <c r="A380" s="4" t="s">
-        <v>1720</v>
+        <v>1723</v>
       </c>
       <c r="B380" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C380" s="4" t="s">
-        <v>1721</v>
+        <v>1724</v>
       </c>
       <c r="D380" s="4" t="s">
         <v>42</v>
@@ -22751,10 +22796,10 @@
         <v>9</v>
       </c>
       <c r="J380" s="4" t="s">
-        <v>1722</v>
+        <v>1725</v>
       </c>
       <c r="K380" s="4" t="s">
-        <v>1723</v>
+        <v>1726</v>
       </c>
       <c r="L380" s="6" t="s">
         <v>518</v>
@@ -22762,13 +22807,13 @@
     </row>
     <row r="381" spans="1:12" ht="72" customHeight="1">
       <c r="A381" s="4" t="s">
-        <v>1724</v>
+        <v>1727</v>
       </c>
       <c r="B381" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C381" s="4" t="s">
-        <v>1725</v>
+        <v>1728</v>
       </c>
       <c r="D381" s="4" t="s">
         <v>42</v>
@@ -22780,10 +22825,10 @@
         <v>9</v>
       </c>
       <c r="J381" s="4" t="s">
-        <v>1726</v>
+        <v>1729</v>
       </c>
       <c r="K381" s="4" t="s">
-        <v>1727</v>
+        <v>1730</v>
       </c>
       <c r="L381" s="6" t="s">
         <v>1045</v>
@@ -22791,13 +22836,13 @@
     </row>
     <row r="382" spans="1:12" ht="72" customHeight="1">
       <c r="A382" s="4" t="s">
-        <v>1728</v>
+        <v>1731</v>
       </c>
       <c r="B382" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C382" s="4" t="s">
-        <v>1729</v>
+        <v>1732</v>
       </c>
       <c r="D382" s="4" t="s">
         <v>42</v>
@@ -22809,24 +22854,24 @@
         <v>9</v>
       </c>
       <c r="J382" s="4" t="s">
-        <v>1730</v>
+        <v>1733</v>
       </c>
       <c r="K382" s="4" t="s">
-        <v>1706</v>
+        <v>1709</v>
       </c>
       <c r="L382" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="383" spans="1:12" ht="72" customHeight="1">
       <c r="A383" s="4" t="s">
-        <v>1732</v>
+        <v>1735</v>
       </c>
       <c r="B383" s="4" t="s">
-        <v>1703</v>
+        <v>1706</v>
       </c>
       <c r="C383" s="4" t="s">
-        <v>1733</v>
+        <v>1736</v>
       </c>
       <c r="D383" s="4" t="s">
         <v>42</v>
@@ -22838,10 +22883,10 @@
         <v>9</v>
       </c>
       <c r="J383" s="4" t="s">
-        <v>1734</v>
+        <v>1737</v>
       </c>
       <c r="K383" s="4" t="s">
-        <v>1735</v>
+        <v>1738</v>
       </c>
       <c r="L383" s="6" t="s">
         <v>103</v>
@@ -22849,13 +22894,13 @@
     </row>
     <row r="384" spans="1:12" ht="72" customHeight="1">
       <c r="A384" s="4" t="s">
-        <v>1736</v>
+        <v>1739</v>
       </c>
       <c r="B384" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="C384" s="4" t="s">
-        <v>1738</v>
+        <v>1741</v>
       </c>
       <c r="D384" s="4" t="s">
         <v>42</v>
@@ -22867,10 +22912,10 @@
         <v>9</v>
       </c>
       <c r="J384" s="4" t="s">
-        <v>1739</v>
+        <v>1742</v>
       </c>
       <c r="K384" s="4" t="s">
-        <v>1740</v>
+        <v>1743</v>
       </c>
       <c r="L384" s="6" t="s">
         <v>66</v>
@@ -22878,13 +22923,13 @@
     </row>
     <row r="385" spans="1:12" ht="72" customHeight="1">
       <c r="A385" s="4" t="s">
-        <v>1741</v>
+        <v>1744</v>
       </c>
       <c r="B385" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="C385" s="4" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="D385" s="4" t="s">
         <v>42</v>
@@ -22896,10 +22941,10 @@
         <v>9</v>
       </c>
       <c r="J385" s="4" t="s">
-        <v>1743</v>
+        <v>1746</v>
       </c>
       <c r="K385" s="4" t="s">
-        <v>1744</v>
+        <v>1747</v>
       </c>
       <c r="L385" s="6" t="s">
         <v>103</v>
@@ -22907,13 +22952,13 @@
     </row>
     <row r="386" spans="1:12" ht="72" customHeight="1">
       <c r="A386" s="4" t="s">
-        <v>1745</v>
+        <v>1748</v>
       </c>
       <c r="B386" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="C386" s="4" t="s">
-        <v>1746</v>
+        <v>1749</v>
       </c>
       <c r="D386" s="4" t="s">
         <v>42</v>
@@ -22925,10 +22970,10 @@
         <v>9</v>
       </c>
       <c r="J386" s="4" t="s">
+        <v>1750</v>
+      </c>
+      <c r="K386" s="4" t="s">
         <v>1747</v>
-      </c>
-      <c r="K386" s="4" t="s">
-        <v>1744</v>
       </c>
       <c r="L386" s="6" t="s">
         <v>88</v>
@@ -22936,13 +22981,13 @@
     </row>
     <row r="387" spans="1:12" ht="72" customHeight="1">
       <c r="A387" s="4" t="s">
-        <v>1748</v>
+        <v>1751</v>
       </c>
       <c r="B387" s="4" t="s">
-        <v>1737</v>
+        <v>1740</v>
       </c>
       <c r="C387" s="4" t="s">
-        <v>1749</v>
+        <v>1752</v>
       </c>
       <c r="D387" s="4" t="s">
         <v>42</v>
@@ -22954,10 +22999,10 @@
         <v>9</v>
       </c>
       <c r="J387" s="4" t="s">
-        <v>1750</v>
+        <v>1753</v>
       </c>
       <c r="K387" s="4" t="s">
-        <v>1751</v>
+        <v>1754</v>
       </c>
       <c r="L387" s="6" t="s">
         <v>183</v>
@@ -22965,13 +23010,13 @@
     </row>
     <row r="388" spans="1:12" ht="72" customHeight="1">
       <c r="A388" s="4" t="s">
-        <v>1752</v>
+        <v>1755</v>
       </c>
       <c r="B388" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C388" s="4" t="s">
-        <v>1754</v>
+        <v>1757</v>
       </c>
       <c r="D388" s="4" t="s">
         <v>42</v>
@@ -22983,10 +23028,10 @@
         <v>9</v>
       </c>
       <c r="J388" s="4" t="s">
-        <v>1755</v>
+        <v>1758</v>
       </c>
       <c r="K388" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L388" s="6" t="s">
         <v>47</v>
@@ -22994,13 +23039,13 @@
     </row>
     <row r="389" spans="1:12" ht="72" customHeight="1">
       <c r="A389" s="4" t="s">
-        <v>1757</v>
+        <v>1760</v>
       </c>
       <c r="B389" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C389" s="4" t="s">
-        <v>1758</v>
+        <v>1761</v>
       </c>
       <c r="D389" s="4" t="s">
         <v>42</v>
@@ -23012,10 +23057,10 @@
         <v>9</v>
       </c>
       <c r="J389" s="4" t="s">
+        <v>1762</v>
+      </c>
+      <c r="K389" s="4" t="s">
         <v>1759</v>
-      </c>
-      <c r="K389" s="4" t="s">
-        <v>1756</v>
       </c>
       <c r="L389" s="6" t="s">
         <v>518</v>
@@ -23023,13 +23068,13 @@
     </row>
     <row r="390" spans="1:12" ht="72" customHeight="1">
       <c r="A390" s="4" t="s">
-        <v>1760</v>
+        <v>1763</v>
       </c>
       <c r="B390" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C390" s="4" t="s">
-        <v>1761</v>
+        <v>1764</v>
       </c>
       <c r="D390" s="4" t="s">
         <v>42</v>
@@ -23041,24 +23086,24 @@
         <v>9</v>
       </c>
       <c r="J390" s="4" t="s">
-        <v>1762</v>
+        <v>1765</v>
       </c>
       <c r="K390" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L390" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="391" spans="1:12" ht="72" customHeight="1">
       <c r="A391" s="4" t="s">
-        <v>1763</v>
+        <v>1766</v>
       </c>
       <c r="B391" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C391" s="4" t="s">
-        <v>1764</v>
+        <v>1767</v>
       </c>
       <c r="D391" s="4" t="s">
         <v>42</v>
@@ -23070,10 +23115,10 @@
         <v>9</v>
       </c>
       <c r="J391" s="4" t="s">
-        <v>1765</v>
+        <v>1768</v>
       </c>
       <c r="K391" s="4" t="s">
-        <v>1766</v>
+        <v>1769</v>
       </c>
       <c r="L391" s="6" t="s">
         <v>518</v>
@@ -23081,13 +23126,13 @@
     </row>
     <row r="392" spans="1:12" ht="72" customHeight="1">
       <c r="A392" s="4" t="s">
-        <v>1767</v>
+        <v>1770</v>
       </c>
       <c r="B392" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C392" s="4" t="s">
-        <v>1768</v>
+        <v>1771</v>
       </c>
       <c r="D392" s="4" t="s">
         <v>42</v>
@@ -23099,24 +23144,24 @@
         <v>9</v>
       </c>
       <c r="J392" s="4" t="s">
-        <v>1769</v>
+        <v>1772</v>
       </c>
       <c r="K392" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L392" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="393" spans="1:12" ht="72" customHeight="1">
       <c r="A393" s="4" t="s">
-        <v>1770</v>
+        <v>1773</v>
       </c>
       <c r="B393" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C393" s="4" t="s">
-        <v>1771</v>
+        <v>1774</v>
       </c>
       <c r="D393" s="4" t="s">
         <v>42</v>
@@ -23128,10 +23173,10 @@
         <v>9</v>
       </c>
       <c r="J393" s="4" t="s">
-        <v>1772</v>
+        <v>1775</v>
       </c>
       <c r="K393" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L393" s="6" t="s">
         <v>88</v>
@@ -23139,13 +23184,13 @@
     </row>
     <row r="394" spans="1:12" ht="72" customHeight="1">
       <c r="A394" s="4" t="s">
-        <v>1773</v>
+        <v>1776</v>
       </c>
       <c r="B394" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C394" s="4" t="s">
-        <v>1774</v>
+        <v>1777</v>
       </c>
       <c r="D394" s="4" t="s">
         <v>42</v>
@@ -23157,10 +23202,10 @@
         <v>9</v>
       </c>
       <c r="J394" s="4" t="s">
-        <v>1775</v>
+        <v>1778</v>
       </c>
       <c r="K394" s="4" t="s">
-        <v>1776</v>
+        <v>1779</v>
       </c>
       <c r="L394" s="6" t="s">
         <v>518</v>
@@ -23168,13 +23213,13 @@
     </row>
     <row r="395" spans="1:12" ht="72" customHeight="1">
       <c r="A395" s="4" t="s">
-        <v>1777</v>
+        <v>1780</v>
       </c>
       <c r="B395" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C395" s="4" t="s">
-        <v>1778</v>
+        <v>1781</v>
       </c>
       <c r="D395" s="4" t="s">
         <v>42</v>
@@ -23186,24 +23231,24 @@
         <v>9</v>
       </c>
       <c r="J395" s="4" t="s">
-        <v>1779</v>
+        <v>1782</v>
       </c>
       <c r="K395" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L395" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="396" spans="1:12" ht="72" customHeight="1">
       <c r="A396" s="4" t="s">
-        <v>1780</v>
+        <v>1783</v>
       </c>
       <c r="B396" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C396" s="4" t="s">
-        <v>1781</v>
+        <v>1784</v>
       </c>
       <c r="D396" s="4" t="s">
         <v>42</v>
@@ -23215,10 +23260,10 @@
         <v>9</v>
       </c>
       <c r="J396" s="4" t="s">
-        <v>1782</v>
+        <v>1785</v>
       </c>
       <c r="K396" s="4" t="s">
-        <v>1783</v>
+        <v>1786</v>
       </c>
       <c r="L396" s="6" t="s">
         <v>165</v>
@@ -23226,13 +23271,13 @@
     </row>
     <row r="397" spans="1:12" ht="72" customHeight="1">
       <c r="A397" s="4" t="s">
-        <v>1784</v>
+        <v>1787</v>
       </c>
       <c r="B397" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C397" s="4" t="s">
-        <v>1785</v>
+        <v>1788</v>
       </c>
       <c r="D397" s="4" t="s">
         <v>42</v>
@@ -23244,10 +23289,10 @@
         <v>9</v>
       </c>
       <c r="J397" s="4" t="s">
-        <v>1786</v>
+        <v>1789</v>
       </c>
       <c r="K397" s="4" t="s">
-        <v>1787</v>
+        <v>1790</v>
       </c>
       <c r="L397" s="6" t="s">
         <v>165</v>
@@ -23255,13 +23300,13 @@
     </row>
     <row r="398" spans="1:12" ht="72" customHeight="1">
       <c r="A398" s="4" t="s">
-        <v>1788</v>
+        <v>1791</v>
       </c>
       <c r="B398" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C398" s="4" t="s">
-        <v>1789</v>
+        <v>1792</v>
       </c>
       <c r="D398" s="4" t="s">
         <v>42</v>
@@ -23273,10 +23318,10 @@
         <v>9</v>
       </c>
       <c r="J398" s="4" t="s">
-        <v>1790</v>
+        <v>1793</v>
       </c>
       <c r="K398" s="4" t="s">
-        <v>1756</v>
+        <v>1759</v>
       </c>
       <c r="L398" s="6" t="s">
         <v>165</v>
@@ -23284,13 +23329,13 @@
     </row>
     <row r="399" spans="1:12" ht="72" customHeight="1">
       <c r="A399" s="4" t="s">
-        <v>1791</v>
+        <v>1794</v>
       </c>
       <c r="B399" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C399" s="4" t="s">
-        <v>1792</v>
+        <v>1795</v>
       </c>
       <c r="D399" s="4" t="s">
         <v>42</v>
@@ -23302,10 +23347,10 @@
         <v>9</v>
       </c>
       <c r="J399" s="4" t="s">
-        <v>1793</v>
+        <v>1796</v>
       </c>
       <c r="K399" s="4" t="s">
-        <v>1794</v>
+        <v>1797</v>
       </c>
       <c r="L399" s="6" t="s">
         <v>116</v>
@@ -23313,13 +23358,13 @@
     </row>
     <row r="400" spans="1:12" ht="72" customHeight="1">
       <c r="A400" s="4" t="s">
-        <v>1795</v>
+        <v>1798</v>
       </c>
       <c r="B400" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C400" s="4" t="s">
-        <v>1796</v>
+        <v>1799</v>
       </c>
       <c r="D400" s="4" t="s">
         <v>42</v>
@@ -23331,10 +23376,10 @@
         <v>9</v>
       </c>
       <c r="J400" s="4" t="s">
-        <v>1797</v>
+        <v>1800</v>
       </c>
       <c r="K400" s="4" t="s">
-        <v>1798</v>
+        <v>1801</v>
       </c>
       <c r="L400" s="6" t="s">
         <v>103</v>
@@ -23342,13 +23387,13 @@
     </row>
     <row r="401" spans="1:12" ht="72" customHeight="1">
       <c r="A401" s="4" t="s">
-        <v>1799</v>
+        <v>1802</v>
       </c>
       <c r="B401" s="4" t="s">
-        <v>1753</v>
+        <v>1756</v>
       </c>
       <c r="C401" s="4" t="s">
-        <v>1800</v>
+        <v>1803</v>
       </c>
       <c r="D401" s="4" t="s">
         <v>42</v>
@@ -23360,10 +23405,10 @@
         <v>9</v>
       </c>
       <c r="J401" s="4" t="s">
+        <v>1804</v>
+      </c>
+      <c r="K401" s="4" t="s">
         <v>1801</v>
-      </c>
-      <c r="K401" s="4" t="s">
-        <v>1798</v>
       </c>
       <c r="L401" s="6" t="s">
         <v>103</v>
@@ -23371,13 +23416,13 @@
     </row>
     <row r="402" spans="1:12" ht="72" customHeight="1">
       <c r="A402" s="4" t="s">
-        <v>1802</v>
+        <v>1805</v>
       </c>
       <c r="B402" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="C402" s="4" t="s">
-        <v>1804</v>
+        <v>1807</v>
       </c>
       <c r="D402" s="4" t="s">
         <v>42</v>
@@ -23389,10 +23434,10 @@
         <v>9</v>
       </c>
       <c r="J402" s="4" t="s">
-        <v>1805</v>
+        <v>1808</v>
       </c>
       <c r="K402" s="4" t="s">
-        <v>1806</v>
+        <v>1809</v>
       </c>
       <c r="L402" s="6" t="s">
         <v>518</v>
@@ -23400,13 +23445,13 @@
     </row>
     <row r="403" spans="1:12" ht="72" customHeight="1">
       <c r="A403" s="4" t="s">
-        <v>1807</v>
+        <v>1810</v>
       </c>
       <c r="B403" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="C403" s="4" t="s">
-        <v>1808</v>
+        <v>1811</v>
       </c>
       <c r="D403" s="4" t="s">
         <v>42</v>
@@ -23418,24 +23463,24 @@
         <v>9</v>
       </c>
       <c r="J403" s="4" t="s">
-        <v>1809</v>
+        <v>1812</v>
       </c>
       <c r="K403" s="4" t="s">
-        <v>1810</v>
+        <v>1813</v>
       </c>
       <c r="L403" s="6" t="s">
-        <v>1731</v>
+        <v>1734</v>
       </c>
     </row>
     <row r="404" spans="1:12" ht="72" customHeight="1">
       <c r="A404" s="4" t="s">
-        <v>1811</v>
+        <v>1814</v>
       </c>
       <c r="B404" s="4" t="s">
-        <v>1803</v>
+        <v>1806</v>
       </c>
       <c r="C404" s="4" t="s">
-        <v>1812</v>
+        <v>1815</v>
       </c>
       <c r="D404" s="4" t="s">
         <v>42</v>
@@ -23447,10 +23492,10 @@
         <v>9</v>
       </c>
       <c r="J404" s="4" t="s">
-        <v>1813</v>
+        <v>1816</v>
       </c>
       <c r="K404" s="4" t="s">
-        <v>1814</v>
+        <v>1817</v>
       </c>
       <c r="L404" s="6" t="s">
         <v>116</v>
@@ -23458,13 +23503,13 @@
     </row>
     <row r="405" spans="1:12" ht="72" customHeight="1">
       <c r="A405" s="4" t="s">
-        <v>1815</v>
+        <v>1818</v>
       </c>
       <c r="B405" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C405" s="4" t="s">
-        <v>1817</v>
+        <v>1820</v>
       </c>
       <c r="D405" s="4" t="s">
         <v>42</v>
@@ -23476,10 +23521,10 @@
         <v>9</v>
       </c>
       <c r="J405" s="4" t="s">
-        <v>1818</v>
+        <v>1821</v>
       </c>
       <c r="K405" s="4" t="s">
-        <v>1819</v>
+        <v>1822</v>
       </c>
       <c r="L405" s="6" t="s">
         <v>39</v>
@@ -23487,13 +23532,13 @@
     </row>
     <row r="406" spans="1:12" ht="72" customHeight="1">
       <c r="A406" s="4" t="s">
-        <v>1820</v>
+        <v>1823</v>
       </c>
       <c r="B406" s="4" t="s">
-        <v>1816</v>
+        <v>1819</v>
       </c>
       <c r="C406" s="4" t="s">
-        <v>1821</v>
+        <v>1824</v>
       </c>
       <c r="D406" s="4" t="s">
         <v>42</v>
@@ -23505,10 +23550,10 @@
         <v>9</v>
       </c>
       <c r="J406" s="4" t="s">
-        <v>1822</v>
+        <v>1825</v>
       </c>
       <c r="K406" s="4" t="s">
-        <v>1823</v>
+        <v>1826</v>
       </c>
       <c r="L406" s="6" t="s">
         <v>103</v>
@@ -23516,13 +23561,13 @@
     </row>
     <row r="407" spans="1:12" ht="72" customHeight="1">
       <c r="A407" s="4" t="s">
-        <v>1824</v>
+        <v>1827</v>
       </c>
       <c r="B407" s="4" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="C407" s="4" t="s">
-        <v>1826</v>
+        <v>1829</v>
       </c>
       <c r="D407" s="4" t="s">
         <v>42</v>
@@ -23534,10 +23579,10 @@
         <v>9</v>
       </c>
       <c r="J407" s="4" t="s">
-        <v>1827</v>
+        <v>1830</v>
       </c>
       <c r="K407" s="4" t="s">
-        <v>1828</v>
+        <v>1831</v>
       </c>
       <c r="L407" s="6" t="s">
         <v>39</v>
@@ -23545,13 +23590,13 @@
     </row>
     <row r="408" spans="1:12" ht="72" customHeight="1">
       <c r="A408" s="4" t="s">
-        <v>1829</v>
+        <v>1832</v>
       </c>
       <c r="B408" s="4" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="C408" s="4" t="s">
-        <v>1830</v>
+        <v>1833</v>
       </c>
       <c r="D408" s="4" t="s">
         <v>42</v>
@@ -23563,10 +23608,10 @@
         <v>9</v>
       </c>
       <c r="J408" s="4" t="s">
+        <v>1834</v>
+      </c>
+      <c r="K408" s="4" t="s">
         <v>1831</v>
-      </c>
-      <c r="K408" s="4" t="s">
-        <v>1828</v>
       </c>
       <c r="L408" s="6" t="s">
         <v>159</v>
@@ -23574,13 +23619,13 @@
     </row>
     <row r="409" spans="1:12" ht="72" customHeight="1">
       <c r="A409" s="4" t="s">
-        <v>1832</v>
+        <v>1835</v>
       </c>
       <c r="B409" s="4" t="s">
-        <v>1825</v>
+        <v>1828</v>
       </c>
       <c r="C409" s="4" t="s">
-        <v>1833</v>
+        <v>1836</v>
       </c>
       <c r="D409" s="4" t="s">
         <v>42</v>
@@ -23592,10 +23637,10 @@
         <v>9</v>
       </c>
       <c r="J409" s="4" t="s">
-        <v>1834</v>
+        <v>1837</v>
       </c>
       <c r="K409" s="4" t="s">
-        <v>1835</v>
+        <v>1838</v>
       </c>
       <c r="L409" s="6" t="s">
         <v>88</v>
@@ -23603,13 +23648,13 @@
     </row>
     <row r="410" spans="1:12" ht="72" customHeight="1">
       <c r="A410" s="4" t="s">
-        <v>1836</v>
+        <v>1839</v>
       </c>
       <c r="B410" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C410" s="4" t="s">
-        <v>1838</v>
+        <v>1841</v>
       </c>
       <c r="D410" s="4" t="s">
         <v>42</v>
@@ -23621,10 +23666,10 @@
         <v>9</v>
       </c>
       <c r="J410" s="4" t="s">
-        <v>1839</v>
+        <v>1842</v>
       </c>
       <c r="K410" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="L410" s="6" t="s">
         <v>159</v>
@@ -23632,13 +23677,13 @@
     </row>
     <row r="411" spans="1:12" ht="72" customHeight="1">
       <c r="A411" s="4" t="s">
-        <v>1841</v>
+        <v>1844</v>
       </c>
       <c r="B411" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C411" s="4" t="s">
-        <v>1842</v>
+        <v>1845</v>
       </c>
       <c r="D411" s="4" t="s">
         <v>42</v>
@@ -23650,24 +23695,24 @@
         <v>9</v>
       </c>
       <c r="J411" s="4" t="s">
-        <v>1843</v>
+        <v>1846</v>
       </c>
       <c r="K411" s="4" t="s">
-        <v>1844</v>
+        <v>1847</v>
       </c>
       <c r="L411" s="6" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="412" spans="1:12" ht="72" customHeight="1">
       <c r="A412" s="4" t="s">
-        <v>1846</v>
+        <v>1849</v>
       </c>
       <c r="B412" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C412" s="4" t="s">
-        <v>1847</v>
+        <v>1850</v>
       </c>
       <c r="D412" s="4" t="s">
         <v>42</v>
@@ -23679,10 +23724,10 @@
         <v>9</v>
       </c>
       <c r="J412" s="4" t="s">
-        <v>1848</v>
+        <v>1851</v>
       </c>
       <c r="K412" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="L412" s="6" t="s">
         <v>518</v>
@@ -23690,13 +23735,13 @@
     </row>
     <row r="413" spans="1:12" ht="72" customHeight="1">
       <c r="A413" s="4" t="s">
-        <v>1849</v>
+        <v>1852</v>
       </c>
       <c r="B413" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C413" s="4" t="s">
-        <v>1850</v>
+        <v>1853</v>
       </c>
       <c r="D413" s="4" t="s">
         <v>42</v>
@@ -23708,10 +23753,10 @@
         <v>9</v>
       </c>
       <c r="J413" s="4" t="s">
-        <v>1851</v>
+        <v>1854</v>
       </c>
       <c r="K413" s="4" t="s">
-        <v>1852</v>
+        <v>1855</v>
       </c>
       <c r="L413" s="6" t="s">
         <v>103</v>
@@ -23719,13 +23764,13 @@
     </row>
     <row r="414" spans="1:12" ht="72" customHeight="1">
       <c r="A414" s="4" t="s">
-        <v>1853</v>
+        <v>1856</v>
       </c>
       <c r="B414" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C414" s="4" t="s">
-        <v>1854</v>
+        <v>1857</v>
       </c>
       <c r="D414" s="4" t="s">
         <v>42</v>
@@ -23737,10 +23782,10 @@
         <v>9</v>
       </c>
       <c r="J414" s="4" t="s">
-        <v>1855</v>
+        <v>1858</v>
       </c>
       <c r="K414" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="L414" s="6" t="s">
         <v>88</v>
@@ -23748,13 +23793,13 @@
     </row>
     <row r="415" spans="1:12" ht="72" customHeight="1">
       <c r="A415" s="4" t="s">
-        <v>1856</v>
+        <v>1859</v>
       </c>
       <c r="B415" s="4" t="s">
-        <v>1837</v>
+        <v>1840</v>
       </c>
       <c r="C415" s="4" t="s">
-        <v>1857</v>
+        <v>1860</v>
       </c>
       <c r="D415" s="4" t="s">
         <v>42</v>
@@ -23766,10 +23811,10 @@
         <v>9</v>
       </c>
       <c r="J415" s="4" t="s">
-        <v>1858</v>
+        <v>1861</v>
       </c>
       <c r="K415" s="4" t="s">
-        <v>1840</v>
+        <v>1843</v>
       </c>
       <c r="L415" s="6" t="s">
         <v>307</v>
@@ -23777,13 +23822,13 @@
     </row>
     <row r="416" spans="1:12" ht="72" customHeight="1">
       <c r="A416" s="4" t="s">
-        <v>1859</v>
+        <v>1862</v>
       </c>
       <c r="B416" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C416" s="4" t="s">
-        <v>1861</v>
+        <v>1864</v>
       </c>
       <c r="D416" s="4" t="s">
         <v>42</v>
@@ -23795,10 +23840,10 @@
         <v>9</v>
       </c>
       <c r="J416" s="4" t="s">
-        <v>1862</v>
+        <v>1865</v>
       </c>
       <c r="K416" s="4" t="s">
-        <v>1863</v>
+        <v>1866</v>
       </c>
       <c r="L416" s="6" t="s">
         <v>47</v>
@@ -23806,13 +23851,13 @@
     </row>
     <row r="417" spans="1:12" ht="72" customHeight="1">
       <c r="A417" s="4" t="s">
-        <v>1864</v>
+        <v>1867</v>
       </c>
       <c r="B417" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C417" s="4" t="s">
-        <v>1865</v>
+        <v>1868</v>
       </c>
       <c r="D417" s="4" t="s">
         <v>42</v>
@@ -23824,10 +23869,10 @@
         <v>9</v>
       </c>
       <c r="J417" s="4" t="s">
-        <v>1866</v>
+        <v>1869</v>
       </c>
       <c r="K417" s="4" t="s">
-        <v>1867</v>
+        <v>1870</v>
       </c>
       <c r="L417" s="6" t="s">
         <v>159</v>
@@ -23835,13 +23880,13 @@
     </row>
     <row r="418" spans="1:12" ht="72" customHeight="1">
       <c r="A418" s="4" t="s">
-        <v>1868</v>
+        <v>1871</v>
       </c>
       <c r="B418" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C418" s="4" t="s">
-        <v>1869</v>
+        <v>1872</v>
       </c>
       <c r="D418" s="4" t="s">
         <v>42</v>
@@ -23853,10 +23898,10 @@
         <v>9</v>
       </c>
       <c r="J418" s="4" t="s">
+        <v>1873</v>
+      </c>
+      <c r="K418" s="4" t="s">
         <v>1870</v>
-      </c>
-      <c r="K418" s="4" t="s">
-        <v>1867</v>
       </c>
       <c r="L418" s="6" t="s">
         <v>88</v>
@@ -23864,13 +23909,13 @@
     </row>
     <row r="419" spans="1:12" ht="72" customHeight="1">
       <c r="A419" s="4" t="s">
-        <v>1871</v>
+        <v>1874</v>
       </c>
       <c r="B419" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C419" s="4" t="s">
-        <v>1872</v>
+        <v>1875</v>
       </c>
       <c r="D419" s="4" t="s">
         <v>42</v>
@@ -23882,10 +23927,10 @@
         <v>9</v>
       </c>
       <c r="J419" s="4" t="s">
-        <v>1873</v>
+        <v>1876</v>
       </c>
       <c r="K419" s="4" t="s">
-        <v>1874</v>
+        <v>1877</v>
       </c>
       <c r="L419" s="6" t="s">
         <v>183</v>
@@ -23893,13 +23938,13 @@
     </row>
     <row r="420" spans="1:12" ht="72" customHeight="1">
       <c r="A420" s="4" t="s">
-        <v>1875</v>
+        <v>1878</v>
       </c>
       <c r="B420" s="4" t="s">
-        <v>1860</v>
+        <v>1863</v>
       </c>
       <c r="C420" s="4" t="s">
-        <v>1876</v>
+        <v>1879</v>
       </c>
       <c r="D420" s="4" t="s">
         <v>42</v>
@@ -23911,10 +23956,10 @@
         <v>9</v>
       </c>
       <c r="J420" s="4" t="s">
-        <v>1877</v>
+        <v>1880</v>
       </c>
       <c r="K420" s="4" t="s">
-        <v>1878</v>
+        <v>1881</v>
       </c>
       <c r="L420" s="6" t="s">
         <v>165</v>
@@ -23922,13 +23967,13 @@
     </row>
     <row r="421" spans="1:12" ht="72" customHeight="1">
       <c r="A421" s="4" t="s">
-        <v>1879</v>
+        <v>1882</v>
       </c>
       <c r="B421" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="C421" s="4" t="s">
-        <v>1881</v>
+        <v>1884</v>
       </c>
       <c r="D421" s="4" t="s">
         <v>42</v>
@@ -23940,10 +23985,10 @@
         <v>9</v>
       </c>
       <c r="J421" s="4" t="s">
-        <v>1882</v>
+        <v>1885</v>
       </c>
       <c r="K421" s="4" t="s">
-        <v>1883</v>
+        <v>1886</v>
       </c>
       <c r="L421" s="6" t="s">
         <v>147</v>
@@ -23951,13 +23996,13 @@
     </row>
     <row r="422" spans="1:12" ht="72" customHeight="1">
       <c r="A422" s="4" t="s">
-        <v>1884</v>
+        <v>1887</v>
       </c>
       <c r="B422" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="C422" s="4" t="s">
-        <v>1885</v>
+        <v>1888</v>
       </c>
       <c r="D422" s="4" t="s">
         <v>42</v>
@@ -23969,10 +24014,10 @@
         <v>9</v>
       </c>
       <c r="J422" s="4" t="s">
-        <v>1886</v>
+        <v>1889</v>
       </c>
       <c r="K422" s="4" t="s">
-        <v>1887</v>
+        <v>1890</v>
       </c>
       <c r="L422" s="6" t="s">
         <v>88</v>
@@ -23980,13 +24025,13 @@
     </row>
     <row r="423" spans="1:12" ht="72" customHeight="1">
       <c r="A423" s="4" t="s">
-        <v>1888</v>
+        <v>1891</v>
       </c>
       <c r="B423" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="C423" s="4" t="s">
-        <v>1889</v>
+        <v>1892</v>
       </c>
       <c r="D423" s="4" t="s">
         <v>42</v>
@@ -23998,10 +24043,10 @@
         <v>9</v>
       </c>
       <c r="J423" s="4" t="s">
-        <v>1890</v>
+        <v>1893</v>
       </c>
       <c r="K423" s="4" t="s">
-        <v>1891</v>
+        <v>1894</v>
       </c>
       <c r="L423" s="6" t="s">
         <v>103</v>
@@ -24009,13 +24054,13 @@
     </row>
     <row r="424" spans="1:12" ht="72" customHeight="1">
       <c r="A424" s="4" t="s">
-        <v>1892</v>
+        <v>1895</v>
       </c>
       <c r="B424" s="4" t="s">
-        <v>1880</v>
+        <v>1883</v>
       </c>
       <c r="C424" s="4" t="s">
-        <v>1893</v>
+        <v>1896</v>
       </c>
       <c r="D424" s="4" t="s">
         <v>42</v>
@@ -24027,10 +24072,10 @@
         <v>9</v>
       </c>
       <c r="J424" s="4" t="s">
-        <v>1894</v>
+        <v>1897</v>
       </c>
       <c r="K424" s="4" t="s">
-        <v>1895</v>
+        <v>1898</v>
       </c>
       <c r="L424" s="6" t="s">
         <v>116</v>
@@ -24038,13 +24083,13 @@
     </row>
     <row r="425" spans="1:12" ht="72" customHeight="1">
       <c r="A425" s="4" t="s">
-        <v>1896</v>
+        <v>1899</v>
       </c>
       <c r="B425" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C425" s="4" t="s">
-        <v>1898</v>
+        <v>1901</v>
       </c>
       <c r="D425" s="4" t="s">
         <v>42</v>
@@ -24056,10 +24101,10 @@
         <v>9</v>
       </c>
       <c r="J425" s="4" t="s">
-        <v>1899</v>
+        <v>1902</v>
       </c>
       <c r="K425" s="4" t="s">
-        <v>1900</v>
+        <v>1903</v>
       </c>
       <c r="L425" s="6" t="s">
         <v>147</v>
@@ -24067,13 +24112,13 @@
     </row>
     <row r="426" spans="1:12" ht="72" customHeight="1">
       <c r="A426" s="4" t="s">
-        <v>1901</v>
+        <v>1904</v>
       </c>
       <c r="B426" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C426" s="4" t="s">
-        <v>1902</v>
+        <v>1905</v>
       </c>
       <c r="D426" s="4" t="s">
         <v>42</v>
@@ -24085,10 +24130,10 @@
         <v>9</v>
       </c>
       <c r="J426" s="4" t="s">
-        <v>1903</v>
+        <v>1906</v>
       </c>
       <c r="K426" s="4" t="s">
-        <v>1904</v>
+        <v>1907</v>
       </c>
       <c r="L426" s="6" t="s">
         <v>88</v>
@@ -24096,13 +24141,13 @@
     </row>
     <row r="427" spans="1:12" ht="72" customHeight="1">
       <c r="A427" s="4" t="s">
-        <v>1905</v>
+        <v>1908</v>
       </c>
       <c r="B427" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C427" s="4" t="s">
-        <v>1906</v>
+        <v>1909</v>
       </c>
       <c r="D427" s="4" t="s">
         <v>42</v>
@@ -24114,10 +24159,10 @@
         <v>9</v>
       </c>
       <c r="J427" s="4" t="s">
+        <v>1910</v>
+      </c>
+      <c r="K427" s="4" t="s">
         <v>1907</v>
-      </c>
-      <c r="K427" s="4" t="s">
-        <v>1904</v>
       </c>
       <c r="L427" s="6" t="s">
         <v>88</v>
@@ -24125,13 +24170,13 @@
     </row>
     <row r="428" spans="1:12" ht="72" customHeight="1">
       <c r="A428" s="4" t="s">
-        <v>1908</v>
+        <v>1911</v>
       </c>
       <c r="B428" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C428" s="4" t="s">
-        <v>1909</v>
+        <v>1912</v>
       </c>
       <c r="D428" s="4" t="s">
         <v>42</v>
@@ -24143,10 +24188,10 @@
         <v>9</v>
       </c>
       <c r="J428" s="4" t="s">
-        <v>1910</v>
+        <v>1913</v>
       </c>
       <c r="K428" s="4" t="s">
-        <v>1911</v>
+        <v>1914</v>
       </c>
       <c r="L428" s="6" t="s">
         <v>103</v>
@@ -24154,13 +24199,13 @@
     </row>
     <row r="429" spans="1:12" ht="72" customHeight="1">
       <c r="A429" s="4" t="s">
-        <v>1912</v>
+        <v>1915</v>
       </c>
       <c r="B429" s="4" t="s">
-        <v>1897</v>
+        <v>1900</v>
       </c>
       <c r="C429" s="4" t="s">
-        <v>1913</v>
+        <v>1916</v>
       </c>
       <c r="D429" s="4" t="s">
         <v>42</v>
@@ -24172,10 +24217,10 @@
         <v>9</v>
       </c>
       <c r="J429" s="4" t="s">
-        <v>1914</v>
+        <v>1917</v>
       </c>
       <c r="K429" s="4" t="s">
-        <v>1915</v>
+        <v>1918</v>
       </c>
       <c r="L429" s="6" t="s">
         <v>183</v>
@@ -24183,13 +24228,13 @@
     </row>
     <row r="430" spans="1:12" ht="72" customHeight="1">
       <c r="A430" s="4" t="s">
-        <v>1916</v>
+        <v>1919</v>
       </c>
       <c r="B430" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="C430" s="4" t="s">
-        <v>1918</v>
+        <v>1921</v>
       </c>
       <c r="D430" s="4" t="s">
         <v>42</v>
@@ -24201,10 +24246,10 @@
         <v>9</v>
       </c>
       <c r="J430" s="4" t="s">
-        <v>1919</v>
+        <v>1922</v>
       </c>
       <c r="K430" s="4" t="s">
-        <v>1920</v>
+        <v>1923</v>
       </c>
       <c r="L430" s="6" t="s">
         <v>159</v>
@@ -24212,13 +24257,13 @@
     </row>
     <row r="431" spans="1:12" ht="72" customHeight="1">
       <c r="A431" s="4" t="s">
-        <v>1921</v>
+        <v>1924</v>
       </c>
       <c r="B431" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="C431" s="4" t="s">
-        <v>1922</v>
+        <v>1925</v>
       </c>
       <c r="D431" s="4" t="s">
         <v>42</v>
@@ -24230,10 +24275,10 @@
         <v>9</v>
       </c>
       <c r="J431" s="4" t="s">
-        <v>1923</v>
+        <v>1926</v>
       </c>
       <c r="K431" s="4" t="s">
-        <v>1924</v>
+        <v>1927</v>
       </c>
       <c r="L431" s="6" t="s">
         <v>103</v>
@@ -24241,13 +24286,13 @@
     </row>
     <row r="432" spans="1:12" ht="72" customHeight="1">
       <c r="A432" s="4" t="s">
-        <v>1925</v>
+        <v>1928</v>
       </c>
       <c r="B432" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="C432" s="4" t="s">
-        <v>1926</v>
+        <v>1929</v>
       </c>
       <c r="D432" s="4" t="s">
         <v>42</v>
@@ -24259,10 +24304,10 @@
         <v>9</v>
       </c>
       <c r="J432" s="4" t="s">
-        <v>1927</v>
+        <v>1930</v>
       </c>
       <c r="K432" s="4" t="s">
-        <v>1928</v>
+        <v>1931</v>
       </c>
       <c r="L432" s="6" t="s">
         <v>88</v>
@@ -24270,13 +24315,13 @@
     </row>
     <row r="433" spans="1:12" ht="72" customHeight="1">
       <c r="A433" s="4" t="s">
-        <v>1929</v>
+        <v>1932</v>
       </c>
       <c r="B433" s="4" t="s">
-        <v>1917</v>
+        <v>1920</v>
       </c>
       <c r="C433" s="4" t="s">
-        <v>1930</v>
+        <v>1933</v>
       </c>
       <c r="D433" s="4" t="s">
         <v>42</v>
@@ -24288,10 +24333,10 @@
         <v>9</v>
       </c>
       <c r="J433" s="4" t="s">
-        <v>1931</v>
+        <v>1934</v>
       </c>
       <c r="K433" s="4" t="s">
-        <v>1932</v>
+        <v>1935</v>
       </c>
       <c r="L433" s="6" t="s">
         <v>183</v>
@@ -24299,13 +24344,13 @@
     </row>
     <row r="434" spans="1:12" ht="72" customHeight="1">
       <c r="A434" s="4" t="s">
-        <v>1933</v>
+        <v>1936</v>
       </c>
       <c r="B434" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="C434" s="4" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="D434" s="4" t="s">
         <v>42</v>
@@ -24317,10 +24362,10 @@
         <v>9</v>
       </c>
       <c r="J434" s="4" t="s">
-        <v>1936</v>
+        <v>1939</v>
       </c>
       <c r="K434" s="4" t="s">
-        <v>1937</v>
+        <v>1940</v>
       </c>
       <c r="L434" s="6" t="s">
         <v>159</v>
@@ -24328,13 +24373,13 @@
     </row>
     <row r="435" spans="1:12" ht="72" customHeight="1">
       <c r="A435" s="4" t="s">
-        <v>1938</v>
+        <v>1941</v>
       </c>
       <c r="B435" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="C435" s="4" t="s">
-        <v>1939</v>
+        <v>1942</v>
       </c>
       <c r="D435" s="4" t="s">
         <v>42</v>
@@ -24346,10 +24391,10 @@
         <v>9</v>
       </c>
       <c r="J435" s="4" t="s">
-        <v>1940</v>
+        <v>1943</v>
       </c>
       <c r="K435" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="L435" s="6" t="s">
         <v>518</v>
@@ -24357,13 +24402,13 @@
     </row>
     <row r="436" spans="1:12" ht="72" customHeight="1">
       <c r="A436" s="4" t="s">
-        <v>1942</v>
+        <v>1945</v>
       </c>
       <c r="B436" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="C436" s="4" t="s">
-        <v>1943</v>
+        <v>1946</v>
       </c>
       <c r="D436" s="4" t="s">
         <v>42</v>
@@ -24375,10 +24420,10 @@
         <v>9</v>
       </c>
       <c r="J436" s="4" t="s">
-        <v>1944</v>
+        <v>1947</v>
       </c>
       <c r="K436" s="4" t="s">
-        <v>1945</v>
+        <v>1948</v>
       </c>
       <c r="L436" s="6" t="s">
         <v>88</v>
@@ -24386,13 +24431,13 @@
     </row>
     <row r="437" spans="1:12" ht="72" customHeight="1">
       <c r="A437" s="4" t="s">
-        <v>1946</v>
+        <v>1949</v>
       </c>
       <c r="B437" s="4" t="s">
-        <v>1934</v>
+        <v>1937</v>
       </c>
       <c r="C437" s="4" t="s">
-        <v>1947</v>
+        <v>1950</v>
       </c>
       <c r="D437" s="4" t="s">
         <v>42</v>
@@ -24404,10 +24449,10 @@
         <v>9</v>
       </c>
       <c r="J437" s="4" t="s">
-        <v>1948</v>
+        <v>1951</v>
       </c>
       <c r="K437" s="4" t="s">
-        <v>1941</v>
+        <v>1944</v>
       </c>
       <c r="L437" s="6" t="s">
         <v>103</v>
@@ -24415,13 +24460,13 @@
     </row>
     <row r="438" spans="1:12" ht="72" customHeight="1">
       <c r="A438" s="4" t="s">
-        <v>1949</v>
+        <v>1952</v>
       </c>
       <c r="B438" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="C438" s="4" t="s">
-        <v>1951</v>
+        <v>1954</v>
       </c>
       <c r="D438" s="4" t="s">
         <v>42</v>
@@ -24433,10 +24478,10 @@
         <v>9</v>
       </c>
       <c r="J438" s="4" t="s">
-        <v>1952</v>
+        <v>1955</v>
       </c>
       <c r="K438" s="4" t="s">
-        <v>1953</v>
+        <v>1956</v>
       </c>
       <c r="L438" s="6" t="s">
         <v>159</v>
@@ -24444,13 +24489,13 @@
     </row>
     <row r="439" spans="1:12" ht="72" customHeight="1">
       <c r="A439" s="4" t="s">
-        <v>1954</v>
+        <v>1957</v>
       </c>
       <c r="B439" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="C439" s="4" t="s">
-        <v>1955</v>
+        <v>1958</v>
       </c>
       <c r="D439" s="4" t="s">
         <v>42</v>
@@ -24462,10 +24507,10 @@
         <v>9</v>
       </c>
       <c r="J439" s="4" t="s">
+        <v>1959</v>
+      </c>
+      <c r="K439" s="4" t="s">
         <v>1956</v>
-      </c>
-      <c r="K439" s="4" t="s">
-        <v>1953</v>
       </c>
       <c r="L439" s="6" t="s">
         <v>88</v>
@@ -24473,13 +24518,13 @@
     </row>
     <row r="440" spans="1:12" ht="72" customHeight="1">
       <c r="A440" s="4" t="s">
-        <v>1957</v>
+        <v>1960</v>
       </c>
       <c r="B440" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="C440" s="4" t="s">
-        <v>1958</v>
+        <v>1961</v>
       </c>
       <c r="D440" s="4" t="s">
         <v>42</v>
@@ -24491,10 +24536,10 @@
         <v>9</v>
       </c>
       <c r="J440" s="4" t="s">
-        <v>1959</v>
+        <v>1962</v>
       </c>
       <c r="K440" s="4" t="s">
-        <v>1960</v>
+        <v>1963</v>
       </c>
       <c r="L440" s="6" t="s">
         <v>103</v>
@@ -24502,13 +24547,13 @@
     </row>
     <row r="441" spans="1:12" ht="72" customHeight="1">
       <c r="A441" s="4" t="s">
-        <v>1961</v>
+        <v>1964</v>
       </c>
       <c r="B441" s="4" t="s">
-        <v>1950</v>
+        <v>1953</v>
       </c>
       <c r="C441" s="4" t="s">
-        <v>1962</v>
+        <v>1965</v>
       </c>
       <c r="D441" s="4" t="s">
         <v>42</v>
@@ -24520,10 +24565,10 @@
         <v>9</v>
       </c>
       <c r="J441" s="4" t="s">
-        <v>1963</v>
+        <v>1966</v>
       </c>
       <c r="K441" s="4" t="s">
-        <v>1964</v>
+        <v>1967</v>
       </c>
       <c r="L441" s="6" t="s">
         <v>183</v>
@@ -24531,13 +24576,13 @@
     </row>
     <row r="442" spans="1:12" ht="72" customHeight="1">
       <c r="A442" s="4" t="s">
-        <v>1965</v>
+        <v>1968</v>
       </c>
       <c r="B442" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C442" s="4" t="s">
-        <v>1967</v>
+        <v>1970</v>
       </c>
       <c r="D442" s="4" t="s">
         <v>42</v>
@@ -24549,10 +24594,10 @@
         <v>9</v>
       </c>
       <c r="J442" s="4" t="s">
-        <v>1968</v>
+        <v>1971</v>
       </c>
       <c r="K442" s="4" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="L442" s="6" t="s">
         <v>159</v>
@@ -24560,13 +24605,13 @@
     </row>
     <row r="443" spans="1:12" ht="72" customHeight="1">
       <c r="A443" s="4" t="s">
-        <v>1970</v>
+        <v>1973</v>
       </c>
       <c r="B443" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C443" s="4" t="s">
-        <v>1971</v>
+        <v>1974</v>
       </c>
       <c r="D443" s="4" t="s">
         <v>42</v>
@@ -24578,10 +24623,10 @@
         <v>9</v>
       </c>
       <c r="J443" s="4" t="s">
-        <v>1972</v>
+        <v>1975</v>
       </c>
       <c r="K443" s="4" t="s">
-        <v>1973</v>
+        <v>1976</v>
       </c>
       <c r="L443" s="6" t="s">
         <v>518</v>
@@ -24589,13 +24634,13 @@
     </row>
     <row r="444" spans="1:12" ht="72" customHeight="1">
       <c r="A444" s="4" t="s">
-        <v>1974</v>
+        <v>1977</v>
       </c>
       <c r="B444" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C444" s="4" t="s">
-        <v>1975</v>
+        <v>1978</v>
       </c>
       <c r="D444" s="4" t="s">
         <v>42</v>
@@ -24607,10 +24652,10 @@
         <v>9</v>
       </c>
       <c r="J444" s="4" t="s">
-        <v>1976</v>
+        <v>1979</v>
       </c>
       <c r="K444" s="4" t="s">
-        <v>1977</v>
+        <v>1980</v>
       </c>
       <c r="L444" s="6" t="s">
         <v>518</v>
@@ -24618,13 +24663,13 @@
     </row>
     <row r="445" spans="1:12" ht="72" customHeight="1">
       <c r="A445" s="4" t="s">
-        <v>1978</v>
+        <v>1981</v>
       </c>
       <c r="B445" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C445" s="4" t="s">
-        <v>1979</v>
+        <v>1982</v>
       </c>
       <c r="D445" s="4" t="s">
         <v>42</v>
@@ -24636,10 +24681,10 @@
         <v>9</v>
       </c>
       <c r="J445" s="4" t="s">
-        <v>1980</v>
+        <v>1983</v>
       </c>
       <c r="K445" s="4" t="s">
-        <v>1981</v>
+        <v>1984</v>
       </c>
       <c r="L445" s="6" t="s">
         <v>165</v>
@@ -24647,13 +24692,13 @@
     </row>
     <row r="446" spans="1:12" ht="72" customHeight="1">
       <c r="A446" s="4" t="s">
-        <v>1982</v>
+        <v>1985</v>
       </c>
       <c r="B446" s="4" t="s">
-        <v>1966</v>
+        <v>1969</v>
       </c>
       <c r="C446" s="4" t="s">
-        <v>1983</v>
+        <v>1986</v>
       </c>
       <c r="D446" s="4" t="s">
         <v>42</v>
@@ -24665,10 +24710,10 @@
         <v>9</v>
       </c>
       <c r="J446" s="4" t="s">
-        <v>1984</v>
+        <v>1987</v>
       </c>
       <c r="K446" s="4" t="s">
-        <v>1969</v>
+        <v>1972</v>
       </c>
       <c r="L446" s="6" t="s">
         <v>88</v>
@@ -24676,13 +24721,13 @@
     </row>
     <row r="447" spans="1:12" ht="72" customHeight="1">
       <c r="A447" s="4" t="s">
-        <v>1985</v>
+        <v>1988</v>
       </c>
       <c r="B447" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C447" s="4" t="s">
-        <v>1987</v>
+        <v>1990</v>
       </c>
       <c r="D447" s="4" t="s">
         <v>42</v>
@@ -24694,10 +24739,10 @@
         <v>9</v>
       </c>
       <c r="J447" s="4" t="s">
-        <v>1988</v>
+        <v>1991</v>
       </c>
       <c r="K447" s="4" t="s">
-        <v>1989</v>
+        <v>1992</v>
       </c>
       <c r="L447" s="6" t="s">
         <v>47</v>
@@ -24705,13 +24750,13 @@
     </row>
     <row r="448" spans="1:12" ht="72" customHeight="1">
       <c r="A448" s="4" t="s">
-        <v>1990</v>
+        <v>1993</v>
       </c>
       <c r="B448" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C448" s="4" t="s">
-        <v>1991</v>
+        <v>1994</v>
       </c>
       <c r="D448" s="4" t="s">
         <v>42</v>
@@ -24723,10 +24768,10 @@
         <v>9</v>
       </c>
       <c r="J448" s="4" t="s">
-        <v>1992</v>
+        <v>1995</v>
       </c>
       <c r="K448" s="4" t="s">
-        <v>1993</v>
+        <v>1996</v>
       </c>
       <c r="L448" s="6" t="s">
         <v>39</v>
@@ -24734,13 +24779,13 @@
     </row>
     <row r="449" spans="1:12" ht="72" customHeight="1">
       <c r="A449" s="4" t="s">
-        <v>1994</v>
+        <v>1997</v>
       </c>
       <c r="B449" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C449" s="4" t="s">
-        <v>1995</v>
+        <v>1998</v>
       </c>
       <c r="D449" s="4" t="s">
         <v>42</v>
@@ -24752,10 +24797,10 @@
         <v>9</v>
       </c>
       <c r="J449" s="4" t="s">
-        <v>1996</v>
+        <v>1999</v>
       </c>
       <c r="K449" s="4" t="s">
-        <v>1997</v>
+        <v>2000</v>
       </c>
       <c r="L449" s="6" t="s">
         <v>307</v>
@@ -24763,13 +24808,13 @@
     </row>
     <row r="450" spans="1:12" ht="72" customHeight="1">
       <c r="A450" s="4" t="s">
-        <v>1998</v>
+        <v>2001</v>
       </c>
       <c r="B450" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C450" s="4" t="s">
-        <v>1999</v>
+        <v>2002</v>
       </c>
       <c r="D450" s="4" t="s">
         <v>42</v>
@@ -24781,10 +24826,10 @@
         <v>9</v>
       </c>
       <c r="J450" s="4" t="s">
-        <v>2000</v>
+        <v>2003</v>
       </c>
       <c r="K450" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="L450" s="6" t="s">
         <v>307</v>
@@ -24792,13 +24837,13 @@
     </row>
     <row r="451" spans="1:12" ht="72" customHeight="1">
       <c r="A451" s="4" t="s">
-        <v>2002</v>
+        <v>2005</v>
       </c>
       <c r="B451" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C451" s="4" t="s">
-        <v>2003</v>
+        <v>2006</v>
       </c>
       <c r="D451" s="4" t="s">
         <v>42</v>
@@ -24810,10 +24855,10 @@
         <v>9</v>
       </c>
       <c r="J451" s="4" t="s">
-        <v>2004</v>
+        <v>2007</v>
       </c>
       <c r="K451" s="4" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="L451" s="6" t="s">
         <v>95</v>
@@ -24821,13 +24866,13 @@
     </row>
     <row r="452" spans="1:12" ht="72" customHeight="1">
       <c r="A452" s="4" t="s">
-        <v>2006</v>
+        <v>2009</v>
       </c>
       <c r="B452" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C452" s="4" t="s">
-        <v>2007</v>
+        <v>2010</v>
       </c>
       <c r="D452" s="4" t="s">
         <v>42</v>
@@ -24839,10 +24884,10 @@
         <v>9</v>
       </c>
       <c r="J452" s="4" t="s">
-        <v>2008</v>
+        <v>2011</v>
       </c>
       <c r="K452" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="L452" s="6" t="s">
         <v>307</v>
@@ -24850,13 +24895,13 @@
     </row>
     <row r="453" spans="1:12" ht="72" customHeight="1">
       <c r="A453" s="4" t="s">
-        <v>2009</v>
+        <v>2012</v>
       </c>
       <c r="B453" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C453" s="4" t="s">
-        <v>2010</v>
+        <v>2013</v>
       </c>
       <c r="D453" s="4" t="s">
         <v>42</v>
@@ -24868,10 +24913,10 @@
         <v>9</v>
       </c>
       <c r="J453" s="4" t="s">
-        <v>2011</v>
+        <v>2014</v>
       </c>
       <c r="K453" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="L453" s="6" t="s">
         <v>165</v>
@@ -24879,13 +24924,13 @@
     </row>
     <row r="454" spans="1:12" ht="72" customHeight="1">
       <c r="A454" s="4" t="s">
-        <v>2012</v>
+        <v>2015</v>
       </c>
       <c r="B454" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C454" s="4" t="s">
-        <v>2013</v>
+        <v>2016</v>
       </c>
       <c r="D454" s="4" t="s">
         <v>42</v>
@@ -24897,10 +24942,10 @@
         <v>9</v>
       </c>
       <c r="J454" s="4" t="s">
-        <v>2014</v>
+        <v>2017</v>
       </c>
       <c r="K454" s="4" t="s">
-        <v>2001</v>
+        <v>2004</v>
       </c>
       <c r="L454" s="6" t="s">
         <v>165</v>
@@ -24908,13 +24953,13 @@
     </row>
     <row r="455" spans="1:12" ht="72" customHeight="1">
       <c r="A455" s="4" t="s">
-        <v>2015</v>
+        <v>2018</v>
       </c>
       <c r="B455" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C455" s="4" t="s">
-        <v>2016</v>
+        <v>2019</v>
       </c>
       <c r="D455" s="4" t="s">
         <v>42</v>
@@ -24926,10 +24971,10 @@
         <v>9</v>
       </c>
       <c r="J455" s="4" t="s">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="K455" s="4" t="s">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="L455" s="6" t="s">
         <v>307</v>
@@ -24937,13 +24982,13 @@
     </row>
     <row r="456" spans="1:12" ht="72" customHeight="1">
       <c r="A456" s="4" t="s">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B456" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C456" s="4" t="s">
-        <v>2020</v>
+        <v>2023</v>
       </c>
       <c r="D456" s="4" t="s">
         <v>42</v>
@@ -24955,24 +25000,24 @@
         <v>9</v>
       </c>
       <c r="J456" s="4" t="s">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="K456" s="4" t="s">
-        <v>2022</v>
+        <v>2025</v>
       </c>
       <c r="L456" s="6" t="s">
-        <v>1845</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="457" spans="1:12" ht="72" customHeight="1">
       <c r="A457" s="4" t="s">
-        <v>2023</v>
+        <v>2026</v>
       </c>
       <c r="B457" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C457" s="4" t="s">
-        <v>2024</v>
+        <v>2027</v>
       </c>
       <c r="D457" s="4" t="s">
         <v>42</v>
@@ -24984,10 +25029,10 @@
         <v>9</v>
       </c>
       <c r="J457" s="4" t="s">
-        <v>2025</v>
+        <v>2028</v>
       </c>
       <c r="K457" s="4" t="s">
-        <v>2026</v>
+        <v>2029</v>
       </c>
       <c r="L457" s="6" t="s">
         <v>518</v>
@@ -24995,13 +25040,13 @@
     </row>
     <row r="458" spans="1:12" ht="72" customHeight="1">
       <c r="A458" s="4" t="s">
-        <v>2027</v>
+        <v>2030</v>
       </c>
       <c r="B458" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C458" s="4" t="s">
-        <v>2028</v>
+        <v>2031</v>
       </c>
       <c r="D458" s="4" t="s">
         <v>42</v>
@@ -25013,10 +25058,10 @@
         <v>9</v>
       </c>
       <c r="J458" s="4" t="s">
-        <v>2029</v>
+        <v>2032</v>
       </c>
       <c r="K458" s="4" t="s">
-        <v>2005</v>
+        <v>2008</v>
       </c>
       <c r="L458" s="6" t="s">
         <v>307</v>
@@ -25024,13 +25069,13 @@
     </row>
     <row r="459" spans="1:12" ht="72" customHeight="1">
       <c r="A459" s="4" t="s">
-        <v>2030</v>
+        <v>2033</v>
       </c>
       <c r="B459" s="4" t="s">
-        <v>1986</v>
+        <v>1989</v>
       </c>
       <c r="C459" s="4" t="s">
-        <v>2031</v>
+        <v>2034</v>
       </c>
       <c r="D459" s="4" t="s">
         <v>42</v>
@@ -25042,10 +25087,10 @@
         <v>9</v>
       </c>
       <c r="J459" s="4" t="s">
-        <v>2032</v>
+        <v>2035</v>
       </c>
       <c r="K459" s="4" t="s">
-        <v>2033</v>
+        <v>2036</v>
       </c>
       <c r="L459" s="6" t="s">
         <v>165</v>
@@ -25053,13 +25098,13 @@
     </row>
     <row r="460" spans="1:12" ht="72" customHeight="1">
       <c r="A460" s="4" t="s">
-        <v>2034</v>
+        <v>2037</v>
       </c>
       <c r="B460" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="C460" s="4" t="s">
-        <v>2036</v>
+        <v>2039</v>
       </c>
       <c r="D460" s="4" t="s">
         <v>42</v>
@@ -25071,10 +25116,10 @@
         <v>9</v>
       </c>
       <c r="J460" s="4" t="s">
-        <v>2037</v>
+        <v>2040</v>
       </c>
       <c r="K460" s="4" t="s">
-        <v>2038</v>
+        <v>2041</v>
       </c>
       <c r="L460" s="6" t="s">
         <v>39</v>
@@ -25082,13 +25127,13 @@
     </row>
     <row r="461" spans="1:12" ht="72" customHeight="1">
       <c r="A461" s="4" t="s">
-        <v>2039</v>
+        <v>2042</v>
       </c>
       <c r="B461" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="C461" s="4" t="s">
-        <v>2040</v>
+        <v>2043</v>
       </c>
       <c r="D461" s="4" t="s">
         <v>42</v>
@@ -25100,10 +25145,10 @@
         <v>9</v>
       </c>
       <c r="J461" s="4" t="s">
-        <v>2041</v>
+        <v>2044</v>
       </c>
       <c r="K461" s="4" t="s">
-        <v>2042</v>
+        <v>2045</v>
       </c>
       <c r="L461" s="6" t="s">
         <v>518</v>
@@ -25111,13 +25156,13 @@
     </row>
     <row r="462" spans="1:12" ht="72" customHeight="1">
       <c r="A462" s="4" t="s">
-        <v>2043</v>
+        <v>2046</v>
       </c>
       <c r="B462" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="C462" s="4" t="s">
-        <v>2044</v>
+        <v>2047</v>
       </c>
       <c r="D462" s="4" t="s">
         <v>42</v>
@@ -25129,10 +25174,10 @@
         <v>9</v>
       </c>
       <c r="J462" s="4" t="s">
-        <v>2045</v>
+        <v>2048</v>
       </c>
       <c r="K462" s="4" t="s">
-        <v>2046</v>
+        <v>2049</v>
       </c>
       <c r="L462" s="6" t="s">
         <v>116</v>
@@ -25140,13 +25185,13 @@
     </row>
     <row r="463" spans="1:12" ht="72" customHeight="1">
       <c r="A463" s="4" t="s">
-        <v>2047</v>
+        <v>2050</v>
       </c>
       <c r="B463" s="4" t="s">
-        <v>2035</v>
+        <v>2038</v>
       </c>
       <c r="C463" s="4" t="s">
-        <v>2048</v>
+        <v>2051</v>
       </c>
       <c r="D463" s="4" t="s">
         <v>42</v>
@@ -25158,10 +25203,10 @@
         <v>9</v>
       </c>
       <c r="J463" s="4" t="s">
-        <v>2049</v>
+        <v>2052</v>
       </c>
       <c r="K463" s="4" t="s">
-        <v>2050</v>
+        <v>2053</v>
       </c>
       <c r="L463" s="6" t="s">
         <v>307</v>
@@ -25169,13 +25214,13 @@
     </row>
     <row r="464" spans="1:12" ht="72" customHeight="1">
       <c r="A464" s="4" t="s">
-        <v>2051</v>
+        <v>2054</v>
       </c>
       <c r="B464" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="C464" s="4" t="s">
-        <v>2053</v>
+        <v>2056</v>
       </c>
       <c r="D464" s="4" t="s">
         <v>42</v>
@@ -25187,10 +25232,10 @@
         <v>9</v>
       </c>
       <c r="J464" s="4" t="s">
-        <v>2054</v>
+        <v>2057</v>
       </c>
       <c r="K464" s="4" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="L464" s="6" t="s">
         <v>39</v>
@@ -25198,13 +25243,13 @@
     </row>
     <row r="465" spans="1:12" ht="72" customHeight="1">
       <c r="A465" s="4" t="s">
-        <v>2056</v>
+        <v>2059</v>
       </c>
       <c r="B465" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="C465" s="4" t="s">
-        <v>2057</v>
+        <v>2060</v>
       </c>
       <c r="D465" s="4" t="s">
         <v>42</v>
@@ -25216,10 +25261,10 @@
         <v>9</v>
       </c>
       <c r="J465" s="4" t="s">
+        <v>2061</v>
+      </c>
+      <c r="K465" s="4" t="s">
         <v>2058</v>
-      </c>
-      <c r="K465" s="4" t="s">
-        <v>2055</v>
       </c>
       <c r="L465" s="6" t="s">
         <v>311</v>
@@ -25227,13 +25272,13 @@
     </row>
     <row r="466" spans="1:12" ht="72" customHeight="1">
       <c r="A466" s="4" t="s">
-        <v>2059</v>
+        <v>2062</v>
       </c>
       <c r="B466" s="4" t="s">
-        <v>2052</v>
+        <v>2055</v>
       </c>
       <c r="C466" s="4" t="s">
-        <v>2060</v>
+        <v>2063</v>
       </c>
       <c r="D466" s="4" t="s">
         <v>42</v>
@@ -25245,10 +25290,10 @@
         <v>9</v>
       </c>
       <c r="J466" s="4" t="s">
-        <v>2061</v>
+        <v>2064</v>
       </c>
       <c r="K466" s="4" t="s">
-        <v>2055</v>
+        <v>2058</v>
       </c>
       <c r="L466" s="6" t="s">
         <v>165</v>
@@ -25256,13 +25301,13 @@
     </row>
     <row r="467" spans="1:12" ht="72" customHeight="1">
       <c r="A467" s="4" t="s">
-        <v>2062</v>
+        <v>2065</v>
       </c>
       <c r="B467" s="4" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="C467" s="4" t="s">
-        <v>2064</v>
+        <v>2067</v>
       </c>
       <c r="D467" s="4" t="s">
         <v>42</v>
@@ -25274,10 +25319,10 @@
         <v>9</v>
       </c>
       <c r="J467" s="4" t="s">
-        <v>2065</v>
+        <v>2068</v>
       </c>
       <c r="K467" s="4" t="s">
-        <v>2066</v>
+        <v>2069</v>
       </c>
       <c r="L467" s="6" t="s">
         <v>39</v>
@@ -25285,13 +25330,13 @@
     </row>
     <row r="468" spans="1:12" ht="72" customHeight="1">
       <c r="A468" s="4" t="s">
-        <v>2067</v>
+        <v>2070</v>
       </c>
       <c r="B468" s="4" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="C468" s="4" t="s">
-        <v>2068</v>
+        <v>2071</v>
       </c>
       <c r="D468" s="4" t="s">
         <v>42</v>
@@ -25303,10 +25348,10 @@
         <v>9</v>
       </c>
       <c r="J468" s="4" t="s">
+        <v>2072</v>
+      </c>
+      <c r="K468" s="4" t="s">
         <v>2069</v>
-      </c>
-      <c r="K468" s="4" t="s">
-        <v>2066</v>
       </c>
       <c r="L468" s="6" t="s">
         <v>307</v>
@@ -25314,13 +25359,13 @@
     </row>
     <row r="469" spans="1:12" ht="72" customHeight="1">
       <c r="A469" s="4" t="s">
-        <v>2070</v>
+        <v>2073</v>
       </c>
       <c r="B469" s="4" t="s">
-        <v>2063</v>
+        <v>2066</v>
       </c>
       <c r="C469" s="4" t="s">
-        <v>2071</v>
+        <v>2074</v>
       </c>
       <c r="D469" s="4" t="s">
         <v>42</v>
@@ -25332,10 +25377,10 @@
         <v>9</v>
       </c>
       <c r="J469" s="4" t="s">
-        <v>2072</v>
+        <v>2075</v>
       </c>
       <c r="K469" s="4" t="s">
-        <v>2073</v>
+        <v>2076</v>
       </c>
       <c r="L469" s="6" t="s">
         <v>165</v>
@@ -25343,13 +25388,13 @@
     </row>
     <row r="470" spans="1:12" ht="72" customHeight="1">
       <c r="A470" s="4" t="s">
-        <v>2074</v>
+        <v>2077</v>
       </c>
       <c r="B470" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="C470" s="4" t="s">
-        <v>2076</v>
+        <v>2079</v>
       </c>
       <c r="D470" s="4" t="s">
         <v>42</v>
@@ -25361,10 +25406,10 @@
         <v>9</v>
       </c>
       <c r="J470" s="4" t="s">
-        <v>2077</v>
+        <v>2080</v>
       </c>
       <c r="K470" s="4" t="s">
-        <v>2078</v>
+        <v>2081</v>
       </c>
       <c r="L470" s="6" t="s">
         <v>116</v>
@@ -25372,13 +25417,13 @@
     </row>
     <row r="471" spans="1:12" ht="72" customHeight="1">
       <c r="A471" s="4" t="s">
-        <v>2079</v>
+        <v>2082</v>
       </c>
       <c r="B471" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="C471" s="4" t="s">
-        <v>2080</v>
+        <v>2083</v>
       </c>
       <c r="D471" s="4" t="s">
         <v>42</v>
@@ -25390,10 +25435,10 @@
         <v>9</v>
       </c>
       <c r="J471" s="4" t="s">
-        <v>2081</v>
+        <v>2084</v>
       </c>
       <c r="K471" s="4" t="s">
-        <v>2082</v>
+        <v>2085</v>
       </c>
       <c r="L471" s="6" t="s">
         <v>311</v>
@@ -25401,13 +25446,13 @@
     </row>
     <row r="472" spans="1:12" ht="72" customHeight="1">
       <c r="A472" s="4" t="s">
-        <v>2083</v>
+        <v>2086</v>
       </c>
       <c r="B472" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="C472" s="4" t="s">
-        <v>2084</v>
+        <v>2087</v>
       </c>
       <c r="D472" s="4" t="s">
         <v>42</v>
@@ -25419,10 +25464,10 @@
         <v>9</v>
       </c>
       <c r="J472" s="4" t="s">
-        <v>2085</v>
+        <v>2088</v>
       </c>
       <c r="K472" s="4" t="s">
-        <v>2086</v>
+        <v>2089</v>
       </c>
       <c r="L472" s="6" t="s">
         <v>95</v>
@@ -25430,13 +25475,13 @@
     </row>
     <row r="473" spans="1:12" ht="72" customHeight="1">
       <c r="A473" s="4" t="s">
-        <v>2087</v>
+        <v>2090</v>
       </c>
       <c r="B473" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="C473" s="4" t="s">
-        <v>2088</v>
+        <v>2091</v>
       </c>
       <c r="D473" s="4" t="s">
         <v>42</v>
@@ -25448,10 +25493,10 @@
         <v>9</v>
       </c>
       <c r="J473" s="4" t="s">
-        <v>2089</v>
+        <v>2092</v>
       </c>
       <c r="K473" s="4" t="s">
-        <v>2090</v>
+        <v>2093</v>
       </c>
       <c r="L473" s="6" t="s">
         <v>518</v>
@@ -25459,13 +25504,13 @@
     </row>
     <row r="474" spans="1:12" ht="72" customHeight="1">
       <c r="A474" s="4" t="s">
-        <v>2091</v>
+        <v>2094</v>
       </c>
       <c r="B474" s="4" t="s">
-        <v>2075</v>
+        <v>2078</v>
       </c>
       <c r="C474" s="4" t="s">
-        <v>2092</v>
+        <v>2095</v>
       </c>
       <c r="D474" s="4" t="s">
         <v>42</v>
@@ -25477,10 +25522,10 @@
         <v>9</v>
       </c>
       <c r="J474" s="4" t="s">
-        <v>2093</v>
+        <v>2096</v>
       </c>
       <c r="K474" s="4" t="s">
-        <v>2094</v>
+        <v>2097</v>
       </c>
       <c r="L474" s="6" t="s">
         <v>47</v>
@@ -25488,13 +25533,13 @@
     </row>
     <row r="475" spans="1:12" ht="72" customHeight="1">
       <c r="A475" s="4" t="s">
- 